--- a/docs/oc-mensuales/gas-licuado-de-petroleo/feb-2026.xlsx
+++ b/docs/oc-mensuales/gas-licuado-de-petroleo/feb-2026.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>616.28</v>
+        <v>618.85</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>601.34</v>
+        <v>599.2</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>1584.79</v>
+        <v>1579.15</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>1686.25</v>
+        <v>1680.25</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>5162.75</v>
+        <v>5144.37</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>476.06</v>
+        <v>474.36</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>1491.54</v>
+        <v>1486.23</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>495.32</v>
+        <v>493.55</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>5332.93</v>
+        <v>5313.94</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>1255.68</v>
+        <v>1251.21</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>3892.67</v>
+        <v>3878.81</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>243.04</v>
+        <v>242.18</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>469.99</v>
+        <v>468.32</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>56.24</v>
+        <v>56.04</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>542.53</v>
+        <v>540.6</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>353.06</v>
+        <v>351.8</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>1238.29</v>
+        <v>1233.88</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>137.76</v>
+        <v>137.27</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>445.89</v>
+        <v>444.31</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>5350.73</v>
+        <v>5331.68</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>1424.65</v>
+        <v>1419.58</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>2275.03</v>
+        <v>2266.93</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>1144.97</v>
+        <v>1140.89</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>3929.67</v>
+        <v>3915.68</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>690.89</v>
+        <v>688.4299999999999</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>1565.68</v>
+        <v>1560.11</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>8246.23</v>
+        <v>8216.870000000001</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>34514.8</v>
+        <v>34391.92</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>3420.27</v>
+        <v>3408.1</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>690.79</v>
+        <v>688.33</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>528.65</v>
+        <v>526.77</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>376.46</v>
+        <v>375.12</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>334.63</v>
+        <v>333.44</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>837.4</v>
+        <v>834.42</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>239.51</v>
+        <v>237.72</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>1076.22</v>
+        <v>1068.17</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>523.2</v>
+        <v>519.29</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>6514.48</v>
+        <v>6465.72</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>9186.389999999999</v>
+        <v>9117.639999999999</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>1098.08</v>
+        <v>1089.86</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>1466.62</v>
+        <v>1455.64</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>1523.5</v>
+        <v>1512.09</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>9755.559999999999</v>
+        <v>9682.549999999999</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>254.5</v>
+        <v>252.6</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>12655.4</v>
+        <v>12560.68</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>1151.32</v>
+        <v>1142.7</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>172.28</v>
+        <v>170.99</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>301.5</v>
+        <v>299.24</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>301.5</v>
+        <v>299.24</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>1108.52</v>
+        <v>1100.23</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>916.64</v>
+        <v>909.78</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>13925.47</v>
+        <v>13821.25</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>1234.38</v>
+        <v>1225.14</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>679.2</v>
+        <v>674.11</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>20198.74</v>
+        <v>20047.57</v>
       </c>
     </row>
     <row r="57">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>366.1</v>
+        <v>363.36</v>
       </c>
     </row>
     <row r="58">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>444.51</v>
+        <v>441.19</v>
       </c>
     </row>
     <row r="59">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>13091.24</v>
+        <v>12993.27</v>
       </c>
     </row>
     <row r="60">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>389.41</v>
+        <v>386.49</v>
       </c>
     </row>
     <row r="61">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>168.97</v>
+        <v>167.71</v>
       </c>
     </row>
     <row r="62">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>7200.55</v>
+        <v>7146.66</v>
       </c>
     </row>
     <row r="63">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>3322.08</v>
+        <v>3297.21</v>
       </c>
     </row>
     <row r="64">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>687.48</v>
+        <v>682.33</v>
       </c>
     </row>
     <row r="65">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>1358.39</v>
+        <v>1348.22</v>
       </c>
     </row>
     <row r="66">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>687.48</v>
+        <v>682.33</v>
       </c>
     </row>
     <row r="67">
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>1298.35</v>
+        <v>1288.63</v>
       </c>
     </row>
     <row r="68">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>2612.6</v>
+        <v>2593.04</v>
       </c>
     </row>
     <row r="69">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>403.1</v>
+        <v>400.08</v>
       </c>
     </row>
     <row r="70">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>767.55</v>
+        <v>761.8</v>
       </c>
     </row>
     <row r="71">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>921.0599999999999</v>
+        <v>914.16</v>
       </c>
     </row>
     <row r="72">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>147.44</v>
+        <v>146.33</v>
       </c>
     </row>
     <row r="73">
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>982.9</v>
+        <v>975.54</v>
       </c>
     </row>
     <row r="74">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>292.8</v>
+        <v>290.61</v>
       </c>
     </row>
     <row r="75">
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>8676.309999999999</v>
+        <v>8611.370000000001</v>
       </c>
     </row>
     <row r="76">
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>1592.41</v>
+        <v>1580.49</v>
       </c>
     </row>
     <row r="77">
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>619.14</v>
+        <v>614.51</v>
       </c>
     </row>
     <row r="78">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>431.12</v>
+        <v>432.37</v>
       </c>
     </row>
     <row r="79">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>1065.08</v>
+        <v>1068.17</v>
       </c>
     </row>
     <row r="80">
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>10397.6</v>
+        <v>10427.72</v>
       </c>
     </row>
     <row r="81">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>2807.06</v>
+        <v>2815.19</v>
       </c>
     </row>
     <row r="82">
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>922.38</v>
+        <v>925.05</v>
       </c>
     </row>
     <row r="83">
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>288.43</v>
+        <v>289.26</v>
       </c>
     </row>
     <row r="84">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>3681.24</v>
+        <v>3691.9</v>
       </c>
     </row>
     <row r="85">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>543.36</v>
+        <v>544.9299999999999</v>
       </c>
     </row>
     <row r="86">
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>11807.05</v>
+        <v>11841.26</v>
       </c>
     </row>
     <row r="87">
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>12115.39</v>
+        <v>12150.49</v>
       </c>
     </row>
     <row r="88">
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>5506.33</v>
+        <v>5522.28</v>
       </c>
     </row>
     <row r="89">
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>14618.89</v>
+        <v>14661.24</v>
       </c>
     </row>
     <row r="90">
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>2791.33</v>
+        <v>2799.41</v>
       </c>
     </row>
     <row r="91">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>495.32</v>
+        <v>496.75</v>
       </c>
     </row>
     <row r="92">
@@ -6059,7 +6059,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>15537.09</v>
+        <v>15582.1</v>
       </c>
     </row>
     <row r="93">
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>16588.24</v>
+        <v>16636.3</v>
       </c>
     </row>
     <row r="94">
@@ -6181,7 +6181,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>1887.91</v>
+        <v>1893.38</v>
       </c>
     </row>
     <row r="95">
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>950.58</v>
+        <v>953.33</v>
       </c>
     </row>
     <row r="96">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>11100.63</v>
+        <v>11132.78</v>
       </c>
     </row>
     <row r="97">
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>142.88</v>
+        <v>143.29</v>
       </c>
     </row>
     <row r="98">
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>995.26</v>
+        <v>998.14</v>
       </c>
     </row>
     <row r="99">
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>120.52</v>
+        <v>120.86</v>
       </c>
     </row>
     <row r="100">
@@ -6547,7 +6547,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>64.28</v>
+        <v>64.45999999999999</v>
       </c>
     </row>
     <row r="101">
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>1932.01</v>
+        <v>1937.61</v>
       </c>
     </row>
     <row r="102">
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>5197.94</v>
+        <v>5213</v>
       </c>
     </row>
     <row r="103">
@@ -6730,7 +6730,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>19765.05</v>
+        <v>19822.31</v>
       </c>
     </row>
     <row r="104">
@@ -6791,7 +6791,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>1098.25</v>
+        <v>1101.43</v>
       </c>
     </row>
     <row r="105">
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>460.53</v>
+        <v>461.86</v>
       </c>
     </row>
     <row r="106">
@@ -6913,7 +6913,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>1358.39</v>
+        <v>1362.33</v>
       </c>
     </row>
     <row r="107">
@@ -6974,7 +6974,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>13583.91</v>
+        <v>13623.26</v>
       </c>
     </row>
     <row r="108">
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>28002.17</v>
+        <v>28083.29</v>
       </c>
     </row>
     <row r="109">
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>733.03</v>
+        <v>735.16</v>
       </c>
     </row>
     <row r="110">
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>2646.35</v>
+        <v>2654.02</v>
       </c>
     </row>
     <row r="111">
@@ -7218,7 +7218,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>2487.38</v>
+        <v>2494.58</v>
       </c>
     </row>
     <row r="112">
@@ -7279,7 +7279,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>1918.86</v>
+        <v>1924.42</v>
       </c>
     </row>
     <row r="113">
@@ -7340,7 +7340,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>3227.97</v>
+        <v>3237.32</v>
       </c>
     </row>
     <row r="114">
@@ -7401,7 +7401,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>1535.09</v>
+        <v>1539.54</v>
       </c>
     </row>
     <row r="115">
@@ -7462,7 +7462,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>321.38</v>
+        <v>322.31</v>
       </c>
     </row>
     <row r="116">
@@ -7523,7 +7523,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>336.84</v>
+        <v>337.81</v>
       </c>
     </row>
     <row r="117">
@@ -7584,7 +7584,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>473.78</v>
+        <v>475.15</v>
       </c>
     </row>
     <row r="118">
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>144.54</v>
+        <v>144.95</v>
       </c>
     </row>
     <row r="119">
@@ -7706,7 +7706,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>2600.41</v>
+        <v>2607.94</v>
       </c>
     </row>
     <row r="120">
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>281.2</v>
+        <v>282.02</v>
       </c>
     </row>
     <row r="121">
@@ -7828,7 +7828,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>825.53</v>
+        <v>827.92</v>
       </c>
     </row>
     <row r="122">
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>2703.53</v>
+        <v>2711.36</v>
       </c>
     </row>
     <row r="123">
@@ -7950,7 +7950,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>279.13</v>
+        <v>279.94</v>
       </c>
     </row>
     <row r="124">
@@ -8011,7 +8011,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>325.65</v>
+        <v>326.6</v>
       </c>
     </row>
     <row r="125">
@@ -8072,7 +8072,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>1194.11</v>
+        <v>1197.57</v>
       </c>
     </row>
     <row r="126">
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>379.87</v>
+        <v>380.97</v>
       </c>
     </row>
     <row r="127">
@@ -8194,7 +8194,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>1000.16</v>
+        <v>1003.05</v>
       </c>
     </row>
     <row r="128">
@@ -8255,7 +8255,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>1263.14</v>
+        <v>1266.8</v>
       </c>
     </row>
     <row r="129">
@@ -8316,7 +8316,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>1967.8</v>
+        <v>1973.5</v>
       </c>
     </row>
     <row r="130">
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>905.59</v>
+        <v>908.22</v>
       </c>
     </row>
     <row r="131">
@@ -8438,7 +8438,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>481.79</v>
+        <v>483.18</v>
       </c>
     </row>
     <row r="132">
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>393.56</v>
+        <v>394.7</v>
       </c>
     </row>
     <row r="133">
@@ -8560,7 +8560,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>17400.87</v>
+        <v>17490.76</v>
       </c>
     </row>
     <row r="134">
@@ -8621,7 +8621,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>258.43</v>
+        <v>259.76</v>
       </c>
     </row>
     <row r="135">
@@ -8682,7 +8682,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>861.42</v>
+        <v>865.87</v>
       </c>
     </row>
     <row r="136">
@@ -8743,7 +8743,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>1464.96</v>
+        <v>1472.53</v>
       </c>
     </row>
     <row r="137">
@@ -8804,7 +8804,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>444.51</v>
+        <v>446.81</v>
       </c>
     </row>
     <row r="138">
@@ -8865,7 +8865,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>1883.52</v>
+        <v>1893.25</v>
       </c>
     </row>
     <row r="139">
@@ -8926,7 +8926,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>3805.17</v>
+        <v>3824.83</v>
       </c>
     </row>
     <row r="140">
@@ -8987,7 +8987,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>85.73</v>
+        <v>86.17</v>
       </c>
     </row>
     <row r="141">
@@ -9048,7 +9048,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>5543.31</v>
+        <v>5571.95</v>
       </c>
     </row>
     <row r="142">
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>2222.57</v>
+        <v>2234.05</v>
       </c>
     </row>
     <row r="143">
@@ -9170,7 +9170,7 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>1358.39</v>
+        <v>1365.41</v>
       </c>
     </row>
     <row r="144">
@@ -9231,7 +9231,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>2035.1</v>
+        <v>2045.62</v>
       </c>
     </row>
     <row r="145">
@@ -9292,7 +9292,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>7459.59</v>
+        <v>7498.12</v>
       </c>
     </row>
     <row r="146">
@@ -9353,7 +9353,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>815.03</v>
+        <v>819.24</v>
       </c>
     </row>
     <row r="147">
@@ -9414,7 +9414,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>2108.61</v>
+        <v>2119.5</v>
       </c>
     </row>
     <row r="148">
@@ -9475,7 +9475,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>6803.76</v>
+        <v>6838.9</v>
       </c>
     </row>
     <row r="149">
@@ -9536,7 +9536,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>1778.88</v>
+        <v>1788.07</v>
       </c>
     </row>
     <row r="150">
@@ -9597,7 +9597,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>287.42</v>
+        <v>288.9</v>
       </c>
     </row>
     <row r="151">
@@ -9658,7 +9658,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>711.22</v>
+        <v>714.9</v>
       </c>
     </row>
     <row r="152">
@@ -9719,7 +9719,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>354.96</v>
+        <v>356.8</v>
       </c>
     </row>
     <row r="153">
@@ -9780,7 +9780,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>331.45</v>
+        <v>333.17</v>
       </c>
     </row>
     <row r="154">
@@ -9841,7 +9841,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>1211.64</v>
+        <v>1217.9</v>
       </c>
     </row>
     <row r="155">
@@ -9902,7 +9902,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>3013.15</v>
+        <v>3028.72</v>
       </c>
     </row>
     <row r="156">
@@ -9963,7 +9963,7 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>2153.55</v>
+        <v>2164.67</v>
       </c>
     </row>
     <row r="157">
@@ -10024,7 +10024,7 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>918.9400000000001</v>
+        <v>923.6900000000001</v>
       </c>
     </row>
     <row r="158">
@@ -10085,7 +10085,7 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>1918.86</v>
+        <v>1928.78</v>
       </c>
     </row>
     <row r="159">
@@ -10146,7 +10146,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>880.5</v>
+        <v>885.05</v>
       </c>
     </row>
     <row r="160">
@@ -10207,7 +10207,7 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>412.76</v>
+        <v>414.9</v>
       </c>
     </row>
     <row r="161">
@@ -10268,7 +10268,7 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>235.37</v>
+        <v>236.59</v>
       </c>
     </row>
     <row r="162">
@@ -10329,7 +10329,7 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>4418.91</v>
+        <v>4441.74</v>
       </c>
     </row>
     <row r="163">
@@ -10390,7 +10390,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>142.05</v>
+        <v>142.79</v>
       </c>
     </row>
     <row r="164">
@@ -10451,7 +10451,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>1164.93</v>
+        <v>1170.95</v>
       </c>
     </row>
     <row r="165">
@@ -10512,7 +10512,7 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>2694.75</v>
+        <v>2708.67</v>
       </c>
     </row>
     <row r="166">
@@ -10573,7 +10573,7 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>1537.31</v>
+        <v>1545.25</v>
       </c>
     </row>
     <row r="167">
@@ -10634,7 +10634,7 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>5764.88</v>
+        <v>5794.66</v>
       </c>
     </row>
     <row r="168">
@@ -10695,7 +10695,7 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>168.42</v>
+        <v>169.29</v>
       </c>
     </row>
     <row r="169">
@@ -10756,7 +10756,7 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>2543.84</v>
+        <v>2556.98</v>
       </c>
     </row>
     <row r="170">
@@ -10817,7 +10817,7 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>3953.94</v>
+        <v>3974.37</v>
       </c>
     </row>
     <row r="171">
@@ -10878,7 +10878,7 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>188.85</v>
+        <v>189.82</v>
       </c>
     </row>
     <row r="172">
@@ -10939,7 +10939,7 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>258.43</v>
+        <v>259.76</v>
       </c>
     </row>
     <row r="173">
@@ -11000,7 +11000,7 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>494.21</v>
+        <v>492.13</v>
       </c>
     </row>
     <row r="174">
@@ -11061,7 +11061,7 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>16167.26</v>
+        <v>16099.09</v>
       </c>
     </row>
     <row r="175">
@@ -11122,7 +11122,7 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>1196.87</v>
+        <v>1191.83</v>
       </c>
     </row>
     <row r="176">
@@ -11183,7 +11183,7 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>1217.58</v>
+        <v>1212.45</v>
       </c>
     </row>
     <row r="177">
@@ -11244,7 +11244,7 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>2597.51</v>
+        <v>2586.56</v>
       </c>
     </row>
     <row r="178">
@@ -11305,7 +11305,7 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>791.66</v>
+        <v>788.3200000000001</v>
       </c>
     </row>
     <row r="179">
@@ -11366,7 +11366,7 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>1290.75</v>
+        <v>1285.31</v>
       </c>
     </row>
     <row r="180">
@@ -11427,7 +11427,7 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>118.03</v>
+        <v>117.53</v>
       </c>
     </row>
     <row r="181">
@@ -11488,7 +11488,7 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>4238.07</v>
+        <v>4220.2</v>
       </c>
     </row>
     <row r="182">
@@ -11549,7 +11549,7 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>1898.14</v>
+        <v>1890.14</v>
       </c>
     </row>
     <row r="183">
@@ -11610,7 +11610,7 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>1968.06</v>
+        <v>1959.76</v>
       </c>
     </row>
     <row r="184">
@@ -11671,7 +11671,7 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>28246.66</v>
+        <v>28127.56</v>
       </c>
     </row>
     <row r="185">
@@ -11732,7 +11732,7 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>463.56</v>
+        <v>461.6</v>
       </c>
     </row>
     <row r="186">
@@ -11793,7 +11793,7 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>79.22</v>
+        <v>78.89</v>
       </c>
     </row>
     <row r="187">
@@ -11854,7 +11854,7 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>437.61</v>
+        <v>435.77</v>
       </c>
     </row>
     <row r="188">
@@ -11915,7 +11915,7 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>1082.61</v>
+        <v>1078.04</v>
       </c>
     </row>
     <row r="189">
@@ -11976,7 +11976,7 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>1000.09</v>
+        <v>995.87</v>
       </c>
     </row>
     <row r="190">
@@ -12037,7 +12037,7 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>3749.93</v>
+        <v>3734.12</v>
       </c>
     </row>
     <row r="191">
@@ -12102,7 +12102,7 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>104524.14</v>
+        <v>104083.43</v>
       </c>
     </row>
     <row r="192">
@@ -12163,7 +12163,7 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>527.62</v>
+        <v>525.39</v>
       </c>
     </row>
     <row r="193">
@@ -12224,7 +12224,7 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>14813.91</v>
+        <v>14751.45</v>
       </c>
     </row>
     <row r="194">
@@ -12285,7 +12285,7 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>3124.02</v>
+        <v>3110.85</v>
       </c>
     </row>
     <row r="195">
@@ -12346,7 +12346,7 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>806.2</v>
+        <v>802.8</v>
       </c>
     </row>
     <row r="196">
@@ -12407,7 +12407,7 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>101.88</v>
+        <v>101.45</v>
       </c>
     </row>
     <row r="197">
@@ -12468,7 +12468,7 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>642.1</v>
+        <v>639.39</v>
       </c>
     </row>
     <row r="198">
@@ -12529,7 +12529,7 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>6856.73</v>
+        <v>6827.82</v>
       </c>
     </row>
     <row r="199">
@@ -12590,7 +12590,7 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>729.53</v>
+        <v>731.53</v>
       </c>
     </row>
     <row r="200">
@@ -12651,7 +12651,7 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>508.57</v>
+        <v>509.96</v>
       </c>
     </row>
     <row r="201">
@@ -12712,7 +12712,7 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>1399.81</v>
+        <v>1403.65</v>
       </c>
     </row>
     <row r="202">
@@ -12773,7 +12773,7 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>1083.4</v>
+        <v>1086.37</v>
       </c>
     </row>
     <row r="203">
@@ -12834,7 +12834,7 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>832.88</v>
+        <v>835.17</v>
       </c>
     </row>
     <row r="204">
@@ -12895,7 +12895,7 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>6087.91</v>
+        <v>6104.62</v>
       </c>
     </row>
     <row r="205">
@@ -12956,7 +12956,7 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>822.1900000000001</v>
+        <v>824.4400000000001</v>
       </c>
     </row>
     <row r="206">
@@ -13017,7 +13017,7 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>283.27</v>
+        <v>284.05</v>
       </c>
     </row>
     <row r="207">
@@ -13078,7 +13078,7 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>400.09</v>
+        <v>401.19</v>
       </c>
     </row>
     <row r="208">
@@ -13139,7 +13139,7 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>135.42</v>
+        <v>135.8</v>
       </c>
     </row>
     <row r="209">
@@ -13200,7 +13200,7 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>10749.79</v>
+        <v>10779.3</v>
       </c>
     </row>
     <row r="210">
@@ -13261,7 +13261,7 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>6323.65</v>
+        <v>6341.01</v>
       </c>
     </row>
     <row r="211">
@@ -13322,7 +13322,7 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>200.65</v>
+        <v>201.2</v>
       </c>
     </row>
     <row r="212">
@@ -13383,7 +13383,7 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>315.99</v>
+        <v>316.86</v>
       </c>
     </row>
     <row r="213">
@@ -13444,7 +13444,7 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>1853.81</v>
+        <v>1858.9</v>
       </c>
     </row>
     <row r="214">
@@ -13505,7 +13505,7 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>428.59</v>
+        <v>429.76</v>
       </c>
     </row>
     <row r="215">
@@ -13566,7 +13566,7 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>345.95</v>
+        <v>346.9</v>
       </c>
     </row>
     <row r="216">
@@ -13627,7 +13627,7 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>6907.44</v>
+        <v>6926.41</v>
       </c>
     </row>
     <row r="217">
@@ -13688,7 +13688,7 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>25499.44</v>
+        <v>25569.45</v>
       </c>
     </row>
     <row r="218">
@@ -13749,7 +13749,7 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>3336.34</v>
+        <v>3345.5</v>
       </c>
     </row>
     <row r="219">
@@ -13810,7 +13810,7 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>905.1</v>
+        <v>907.58</v>
       </c>
     </row>
     <row r="220">
@@ -13871,7 +13871,7 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>2638.09</v>
+        <v>2645.34</v>
       </c>
     </row>
     <row r="221">
@@ -13932,7 +13932,7 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>1774.19</v>
+        <v>1779.06</v>
       </c>
     </row>
     <row r="222">
@@ -13993,7 +13993,7 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>112.5</v>
+        <v>112.81</v>
       </c>
     </row>
     <row r="223">
@@ -14054,7 +14054,7 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>352.93</v>
+        <v>353.9</v>
       </c>
     </row>
     <row r="224">
@@ -14115,7 +14115,7 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>363.52</v>
+        <v>364.52</v>
       </c>
     </row>
     <row r="225">
@@ -14176,7 +14176,7 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>5682.05</v>
+        <v>5697.65</v>
       </c>
     </row>
     <row r="226">
@@ -14237,7 +14237,7 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>14619.91</v>
+        <v>14660.05</v>
       </c>
     </row>
     <row r="227">
@@ -14298,7 +14298,7 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>4048.01</v>
+        <v>4059.12</v>
       </c>
     </row>
     <row r="228">
@@ -14359,7 +14359,7 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>1695.23</v>
+        <v>1699.88</v>
       </c>
     </row>
     <row r="229">
@@ -14420,7 +14420,7 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>4666.02</v>
+        <v>4678.83</v>
       </c>
     </row>
     <row r="230">
@@ -14481,7 +14481,7 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>188.44</v>
+        <v>188.95</v>
       </c>
     </row>
     <row r="231">
@@ -14542,7 +14542,7 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>4103.05</v>
+        <v>4114.31</v>
       </c>
     </row>
     <row r="232">
@@ -14603,7 +14603,7 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>4179.98</v>
+        <v>4191.46</v>
       </c>
     </row>
     <row r="233">
@@ -14664,7 +14664,7 @@
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>1017.14</v>
+        <v>1019.93</v>
       </c>
     </row>
     <row r="234">
@@ -14725,7 +14725,7 @@
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>95.92</v>
+        <v>96.19</v>
       </c>
     </row>
     <row r="235">
@@ -14786,7 +14786,7 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>7909.7</v>
+        <v>7931.42</v>
       </c>
     </row>
     <row r="236">
@@ -14847,7 +14847,7 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>376.87</v>
+        <v>377.91</v>
       </c>
     </row>
     <row r="237">
@@ -14908,7 +14908,7 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>474.88</v>
+        <v>476.19</v>
       </c>
     </row>
     <row r="238">
@@ -14969,7 +14969,7 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>3611.33</v>
+        <v>3621.25</v>
       </c>
     </row>
     <row r="239">
@@ -15030,7 +15030,7 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>1032.6</v>
+        <v>1035.43</v>
       </c>
     </row>
     <row r="240">
@@ -15091,7 +15091,7 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>5846.57</v>
+        <v>5899.75</v>
       </c>
     </row>
     <row r="241">
@@ -15152,7 +15152,7 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>611.28</v>
+        <v>616.84</v>
       </c>
     </row>
     <row r="242">
@@ -15213,7 +15213,7 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>228.61</v>
+        <v>230.69</v>
       </c>
     </row>
     <row r="243">
@@ -15274,7 +15274,7 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>1120.34</v>
+        <v>1130.53</v>
       </c>
     </row>
     <row r="244">
@@ -15335,7 +15335,7 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>3507.05</v>
+        <v>3538.95</v>
       </c>
     </row>
     <row r="245">
@@ -15396,7 +15396,7 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>121.14</v>
+        <v>122.24</v>
       </c>
     </row>
     <row r="246">
@@ -15457,7 +15457,7 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>7091.38</v>
+        <v>7155.88</v>
       </c>
     </row>
     <row r="247">
@@ -15518,7 +15518,7 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>1171.61</v>
+        <v>1182.27</v>
       </c>
     </row>
     <row r="248">
@@ -15579,7 +15579,7 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>1295.01</v>
+        <v>1306.79</v>
       </c>
     </row>
     <row r="249">
@@ -15640,7 +15640,7 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>1163.14</v>
+        <v>1173.72</v>
       </c>
     </row>
     <row r="250">
@@ -15701,7 +15701,7 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>11186.22</v>
+        <v>11287.97</v>
       </c>
     </row>
     <row r="251">
@@ -15762,7 +15762,7 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>2988.26</v>
+        <v>3015.44</v>
       </c>
     </row>
     <row r="252">
@@ -15823,7 +15823,7 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>5144.88</v>
+        <v>5191.68</v>
       </c>
     </row>
     <row r="253">
@@ -15884,7 +15884,7 @@
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>74.39</v>
+        <v>75.06999999999999</v>
       </c>
     </row>
     <row r="254">
@@ -15945,7 +15945,7 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>242.42</v>
+        <v>244.62</v>
       </c>
     </row>
     <row r="255">
@@ -16006,7 +16006,7 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>403.64</v>
+        <v>407.31</v>
       </c>
     </row>
     <row r="256">
@@ -16067,7 +16067,7 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>6762.12</v>
+        <v>6823.63</v>
       </c>
     </row>
     <row r="257">
@@ -16128,7 +16128,7 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>731.1</v>
+        <v>737.75</v>
       </c>
     </row>
     <row r="258">
@@ -16189,7 +16189,7 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>1316.98</v>
+        <v>1328.96</v>
       </c>
     </row>
     <row r="259">
@@ -16250,7 +16250,7 @@
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>563.1</v>
+        <v>568.22</v>
       </c>
     </row>
     <row r="260">
@@ -16311,7 +16311,7 @@
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>5474.15</v>
+        <v>5523.94</v>
       </c>
     </row>
     <row r="261">
@@ -16372,7 +16372,7 @@
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>3014.96</v>
+        <v>3042.39</v>
       </c>
     </row>
     <row r="262">
@@ -16433,7 +16433,7 @@
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>1059.52</v>
+        <v>1069.15</v>
       </c>
     </row>
     <row r="263">
@@ -16494,7 +16494,7 @@
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>4404.37</v>
+        <v>4444.44</v>
       </c>
     </row>
     <row r="264">
@@ -16555,7 +16555,7 @@
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>565.3099999999999</v>
+        <v>570.45</v>
       </c>
     </row>
     <row r="265">
@@ -16616,7 +16616,7 @@
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>249.31</v>
+        <v>251.58</v>
       </c>
     </row>
     <row r="266">
@@ -16677,7 +16677,7 @@
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>660.5599999999999</v>
+        <v>666.5700000000001</v>
       </c>
     </row>
     <row r="267">
@@ -16738,7 +16738,7 @@
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>210.59</v>
+        <v>212.51</v>
       </c>
     </row>
     <row r="268">
@@ -16799,7 +16799,7 @@
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>944.25</v>
+        <v>952.84</v>
       </c>
     </row>
     <row r="269">
@@ -16860,7 +16860,7 @@
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>2222.57</v>
+        <v>2242.79</v>
       </c>
     </row>
     <row r="270">
@@ -16921,7 +16921,7 @@
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>13921.02</v>
+        <v>14047.64</v>
       </c>
     </row>
     <row r="271">
@@ -16982,7 +16982,7 @@
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>165.66</v>
+        <v>167.16</v>
       </c>
     </row>
     <row r="272">
@@ -17043,7 +17043,7 @@
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>4639.3</v>
+        <v>4681.49</v>
       </c>
     </row>
     <row r="273">
@@ -17104,7 +17104,7 @@
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>474.88</v>
+        <v>479.2</v>
       </c>
     </row>
     <row r="274">
@@ -17165,7 +17165,7 @@
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>904.13</v>
+        <v>912.35</v>
       </c>
     </row>
     <row r="275">
@@ -17226,7 +17226,7 @@
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>4431.34</v>
+        <v>4471.64</v>
       </c>
     </row>
     <row r="276">
@@ -17287,7 +17287,7 @@
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>2261.22</v>
+        <v>2281.79</v>
       </c>
     </row>
     <row r="277">
@@ -17348,7 +17348,7 @@
         </is>
       </c>
       <c r="M277" s="2" t="n">
-        <v>137.5</v>
+        <v>138.75</v>
       </c>
     </row>
     <row r="278">
@@ -17409,7 +17409,7 @@
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>365.61</v>
+        <v>368.93</v>
       </c>
     </row>
     <row r="279">
@@ -17470,7 +17470,7 @@
         </is>
       </c>
       <c r="M279" s="2" t="n">
-        <v>99.39</v>
+        <v>100.3</v>
       </c>
     </row>
     <row r="280">
@@ -17531,7 +17531,7 @@
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>414.14</v>
+        <v>417.91</v>
       </c>
     </row>
     <row r="281">
@@ -17592,7 +17592,7 @@
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>552.5599999999999</v>
+        <v>557.58</v>
       </c>
     </row>
     <row r="282">
@@ -17653,7 +17653,7 @@
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>1714.55</v>
+        <v>1730.15</v>
       </c>
     </row>
     <row r="283">
@@ -17714,7 +17714,7 @@
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>636.98</v>
+        <v>642.78</v>
       </c>
     </row>
     <row r="284">
@@ -17775,7 +17775,7 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>1319.05</v>
+        <v>1331.04</v>
       </c>
     </row>
     <row r="285">
@@ -17836,7 +17836,7 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>522.37</v>
+        <v>527.12</v>
       </c>
     </row>
     <row r="286">
@@ -17897,7 +17897,7 @@
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>1306.48</v>
+        <v>1318.37</v>
       </c>
     </row>
     <row r="287">
@@ -17958,7 +17958,7 @@
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>8795.129999999999</v>
+        <v>8856.370000000001</v>
       </c>
     </row>
     <row r="288">
@@ -18019,7 +18019,7 @@
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>5162.99</v>
+        <v>5198.93</v>
       </c>
     </row>
     <row r="289">
@@ -18080,7 +18080,7 @@
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>324.69</v>
+        <v>326.95</v>
       </c>
     </row>
     <row r="290">
@@ -18141,7 +18141,7 @@
         </is>
       </c>
       <c r="M290" s="2" t="n">
-        <v>30147.08</v>
+        <v>30356.97</v>
       </c>
     </row>
     <row r="291">
@@ -18202,7 +18202,7 @@
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>584.3</v>
+        <v>588.37</v>
       </c>
     </row>
     <row r="292">
@@ -18263,7 +18263,7 @@
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>2014.55</v>
+        <v>2028.58</v>
       </c>
     </row>
     <row r="293">
@@ -18324,7 +18324,7 @@
         </is>
       </c>
       <c r="M293" s="2" t="n">
-        <v>3390.45</v>
+        <v>3414.06</v>
       </c>
     </row>
     <row r="294">
@@ -18385,7 +18385,7 @@
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>106.6</v>
+        <v>107.34</v>
       </c>
     </row>
     <row r="295">
@@ -18446,7 +18446,7 @@
         </is>
       </c>
       <c r="M295" s="2" t="n">
-        <v>1855.32</v>
+        <v>1868.24</v>
       </c>
     </row>
     <row r="296">
@@ -18507,7 +18507,7 @@
         </is>
       </c>
       <c r="M296" s="2" t="n">
-        <v>160.17</v>
+        <v>161.29</v>
       </c>
     </row>
     <row r="297">
@@ -18568,7 +18568,7 @@
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>1884.35</v>
+        <v>1897.47</v>
       </c>
     </row>
     <row r="298">
@@ -18629,7 +18629,7 @@
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>465.22</v>
+        <v>468.46</v>
       </c>
     </row>
     <row r="299">
@@ -18690,7 +18690,7 @@
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>23198.65</v>
+        <v>23360.16</v>
       </c>
     </row>
     <row r="300">
@@ -18751,7 +18751,7 @@
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>2042.03</v>
+        <v>2056.25</v>
       </c>
     </row>
     <row r="301">
@@ -18812,7 +18812,7 @@
         </is>
       </c>
       <c r="M301" s="2" t="n">
-        <v>376.59</v>
+        <v>379.22</v>
       </c>
     </row>
     <row r="302">
@@ -18873,7 +18873,7 @@
         </is>
       </c>
       <c r="M302" s="2" t="n">
-        <v>466.6</v>
+        <v>469.85</v>
       </c>
     </row>
     <row r="303">
@@ -18934,7 +18934,7 @@
         </is>
       </c>
       <c r="M303" s="2" t="n">
-        <v>137.08</v>
+        <v>138.04</v>
       </c>
     </row>
     <row r="304">
@@ -18995,7 +18995,7 @@
         </is>
       </c>
       <c r="M304" s="2" t="n">
-        <v>2778.64</v>
+        <v>2797.99</v>
       </c>
     </row>
     <row r="305">
@@ -19056,7 +19056,7 @@
         </is>
       </c>
       <c r="M305" s="2" t="n">
-        <v>494.21</v>
+        <v>497.65</v>
       </c>
     </row>
     <row r="306">
@@ -19117,7 +19117,7 @@
         </is>
       </c>
       <c r="M306" s="2" t="n">
-        <v>66.88</v>
+        <v>67.34999999999999</v>
       </c>
     </row>
     <row r="307">
@@ -19178,7 +19178,7 @@
         </is>
       </c>
       <c r="M307" s="2" t="n">
-        <v>395.37</v>
+        <v>398.12</v>
       </c>
     </row>
     <row r="308">
@@ -19239,7 +19239,7 @@
         </is>
       </c>
       <c r="M308" s="2" t="n">
-        <v>3736.29</v>
+        <v>3762.3</v>
       </c>
     </row>
     <row r="309">
@@ -19300,7 +19300,7 @@
         </is>
       </c>
       <c r="M309" s="2" t="n">
-        <v>10041.57</v>
+        <v>10111.48</v>
       </c>
     </row>
     <row r="310">
@@ -19361,7 +19361,7 @@
         </is>
       </c>
       <c r="M310" s="2" t="n">
-        <v>46.66</v>
+        <v>46.99</v>
       </c>
     </row>
     <row r="311">
@@ -19422,7 +19422,7 @@
         </is>
       </c>
       <c r="M311" s="2" t="n">
-        <v>974.76</v>
+        <v>981.54</v>
       </c>
     </row>
     <row r="312">
@@ -19483,7 +19483,7 @@
         </is>
       </c>
       <c r="M312" s="2" t="n">
-        <v>3025.41</v>
+        <v>3046.47</v>
       </c>
     </row>
     <row r="313">
@@ -19544,7 +19544,7 @@
         </is>
       </c>
       <c r="M313" s="2" t="n">
-        <v>496.97</v>
+        <v>500.43</v>
       </c>
     </row>
     <row r="314">
@@ -19605,7 +19605,7 @@
         </is>
       </c>
       <c r="M314" s="2" t="n">
-        <v>3230.32</v>
+        <v>3252.81</v>
       </c>
     </row>
     <row r="315">
@@ -19666,7 +19666,7 @@
         </is>
       </c>
       <c r="M315" s="2" t="n">
-        <v>508.57</v>
+        <v>512.11</v>
       </c>
     </row>
     <row r="316">
@@ -19727,7 +19727,7 @@
         </is>
       </c>
       <c r="M316" s="2" t="n">
-        <v>423.81</v>
+        <v>426.76</v>
       </c>
     </row>
     <row r="317">
@@ -19788,7 +19788,7 @@
         </is>
       </c>
       <c r="M317" s="2" t="n">
-        <v>236.75</v>
+        <v>238.4</v>
       </c>
     </row>
     <row r="318">
@@ -19849,7 +19849,7 @@
         </is>
       </c>
       <c r="M318" s="2" t="n">
-        <v>241.03</v>
+        <v>242.71</v>
       </c>
     </row>
     <row r="319">
@@ -19910,7 +19910,7 @@
         </is>
       </c>
       <c r="M319" s="2" t="n">
-        <v>79.42</v>
+        <v>79.97</v>
       </c>
     </row>
     <row r="320">
@@ -19971,7 +19971,7 @@
         </is>
       </c>
       <c r="M320" s="2" t="n">
-        <v>197.41</v>
+        <v>198.78</v>
       </c>
     </row>
     <row r="321">
@@ -20032,7 +20032,7 @@
         </is>
       </c>
       <c r="M321" s="2" t="n">
-        <v>2320.06</v>
+        <v>2336.21</v>
       </c>
     </row>
     <row r="322">
@@ -20093,7 +20093,7 @@
         </is>
       </c>
       <c r="M322" s="2" t="n">
-        <v>403.81</v>
+        <v>406.62</v>
       </c>
     </row>
     <row r="323">
@@ -20154,7 +20154,7 @@
         </is>
       </c>
       <c r="M323" s="2" t="n">
-        <v>627.04</v>
+        <v>631.4</v>
       </c>
     </row>
     <row r="324">
@@ -20215,7 +20215,7 @@
         </is>
       </c>
       <c r="M324" s="2" t="n">
-        <v>464.96</v>
+        <v>468.2</v>
       </c>
     </row>
     <row r="325">
@@ -20276,7 +20276,7 @@
         </is>
       </c>
       <c r="M325" s="2" t="n">
-        <v>4652.21</v>
+        <v>4684.6</v>
       </c>
     </row>
     <row r="326">
@@ -20337,7 +20337,7 @@
         </is>
       </c>
       <c r="M326" s="2" t="n">
-        <v>2428.74</v>
+        <v>2445.65</v>
       </c>
     </row>
     <row r="327">
@@ -20398,7 +20398,7 @@
         </is>
       </c>
       <c r="M327" s="2" t="n">
-        <v>170.38</v>
+        <v>171.56</v>
       </c>
     </row>
     <row r="328">
@@ -20459,7 +20459,7 @@
         </is>
       </c>
       <c r="M328" s="2" t="n">
-        <v>2987.8</v>
+        <v>3008.6</v>
       </c>
     </row>
     <row r="329">
@@ -20520,7 +20520,7 @@
         </is>
       </c>
       <c r="M329" s="2" t="n">
-        <v>174.35</v>
+        <v>175.56</v>
       </c>
     </row>
     <row r="330">
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="M330" s="2" t="n">
-        <v>924.49</v>
+        <v>930.92</v>
       </c>
     </row>
     <row r="331">
@@ -20642,7 +20642,7 @@
         </is>
       </c>
       <c r="M331" s="2" t="n">
-        <v>1088.12</v>
+        <v>1095.7</v>
       </c>
     </row>
     <row r="332">
@@ -20703,7 +20703,7 @@
         </is>
       </c>
       <c r="M332" s="2" t="n">
-        <v>699.35</v>
+        <v>704.22</v>
       </c>
     </row>
     <row r="333">
@@ -20764,7 +20764,7 @@
         </is>
       </c>
       <c r="M333" s="2" t="n">
-        <v>5587.58</v>
+        <v>5626.48</v>
       </c>
     </row>
     <row r="334">
@@ -20825,7 +20825,7 @@
         </is>
       </c>
       <c r="M334" s="2" t="n">
-        <v>784.24</v>
+        <v>789.7</v>
       </c>
     </row>
     <row r="335">
@@ -20886,7 +20886,7 @@
         </is>
       </c>
       <c r="M335" s="2" t="n">
-        <v>84.72</v>
+        <v>85.31</v>
       </c>
     </row>
     <row r="336">
@@ -20947,7 +20947,7 @@
         </is>
       </c>
       <c r="M336" s="2" t="n">
-        <v>19974.06</v>
+        <v>20113.12</v>
       </c>
     </row>
     <row r="337">
@@ -21008,7 +21008,7 @@
         </is>
       </c>
       <c r="M337" s="2" t="n">
-        <v>153.98</v>
+        <v>155.05</v>
       </c>
     </row>
     <row r="338">
@@ -21069,7 +21069,7 @@
         </is>
       </c>
       <c r="M338" s="2" t="n">
-        <v>396.14</v>
+        <v>398.9</v>
       </c>
     </row>
     <row r="339">
@@ -21130,7 +21130,7 @@
         </is>
       </c>
       <c r="M339" s="2" t="n">
-        <v>2597.51</v>
+        <v>2615.59</v>
       </c>
     </row>
     <row r="340">
@@ -21191,7 +21191,7 @@
         </is>
       </c>
       <c r="M340" s="2" t="n">
-        <v>1152.7</v>
+        <v>1160.72</v>
       </c>
     </row>
     <row r="341">
@@ -21252,7 +21252,7 @@
         </is>
       </c>
       <c r="M341" s="2" t="n">
-        <v>10531.46</v>
+        <v>10600.82</v>
       </c>
     </row>
     <row r="342">
@@ -21313,7 +21313,7 @@
         </is>
       </c>
       <c r="M342" s="2" t="n">
-        <v>706.2</v>
+        <v>710.85</v>
       </c>
     </row>
     <row r="343">
@@ -21374,7 +21374,7 @@
         </is>
       </c>
       <c r="M343" s="2" t="n">
-        <v>1275.56</v>
+        <v>1283.96</v>
       </c>
     </row>
     <row r="344">
@@ -21435,7 +21435,7 @@
         </is>
       </c>
       <c r="M344" s="2" t="n">
-        <v>286.53</v>
+        <v>288.41</v>
       </c>
     </row>
     <row r="345">
@@ -21496,7 +21496,7 @@
         </is>
       </c>
       <c r="M345" s="2" t="n">
-        <v>608.9299999999999</v>
+        <v>612.9400000000001</v>
       </c>
     </row>
     <row r="346">
@@ -21557,7 +21557,7 @@
         </is>
       </c>
       <c r="M346" s="2" t="n">
-        <v>101.88</v>
+        <v>102.55</v>
       </c>
     </row>
     <row r="347">
@@ -21618,7 +21618,7 @@
         </is>
       </c>
       <c r="M347" s="2" t="n">
-        <v>811.72</v>
+        <v>817.0700000000001</v>
       </c>
     </row>
     <row r="348">
@@ -21679,7 +21679,7 @@
         </is>
       </c>
       <c r="M348" s="2" t="n">
-        <v>1212.03</v>
+        <v>1220.01</v>
       </c>
     </row>
     <row r="349">
@@ -21740,7 +21740,7 @@
         </is>
       </c>
       <c r="M349" s="2" t="n">
-        <v>484.56</v>
+        <v>487.75</v>
       </c>
     </row>
     <row r="350">
@@ -21801,7 +21801,7 @@
         </is>
       </c>
       <c r="M350" s="2" t="n">
-        <v>1548.9</v>
+        <v>1559.1</v>
       </c>
     </row>
     <row r="351">
@@ -21862,7 +21862,7 @@
         </is>
       </c>
       <c r="M351" s="2" t="n">
-        <v>115.43</v>
+        <v>116.19</v>
       </c>
     </row>
     <row r="352">
@@ -21923,7 +21923,7 @@
         </is>
       </c>
       <c r="M352" s="2" t="n">
-        <v>30811.05</v>
+        <v>31013.97</v>
       </c>
     </row>
     <row r="353">
@@ -21984,7 +21984,7 @@
         </is>
       </c>
       <c r="M353" s="2" t="n">
-        <v>30860.42</v>
+        <v>31063.66</v>
       </c>
     </row>
     <row r="354">
@@ -22045,7 +22045,7 @@
         </is>
       </c>
       <c r="M354" s="2" t="n">
-        <v>229.93</v>
+        <v>231.45</v>
       </c>
     </row>
     <row r="355">
@@ -22106,7 +22106,7 @@
         </is>
       </c>
       <c r="M355" s="2" t="n">
-        <v>836.5700000000001</v>
+        <v>842.08</v>
       </c>
     </row>
     <row r="356">
@@ -22167,7 +22167,7 @@
         </is>
       </c>
       <c r="M356" s="2" t="n">
-        <v>197.62</v>
+        <v>198.92</v>
       </c>
     </row>
     <row r="357">
@@ -22228,7 +22228,7 @@
         </is>
       </c>
       <c r="M357" s="2" t="n">
-        <v>35036.82</v>
+        <v>35267.57</v>
       </c>
     </row>
     <row r="358">
@@ -22289,7 +22289,7 @@
         </is>
       </c>
       <c r="M358" s="2" t="n">
-        <v>1003.84</v>
+        <v>1010.45</v>
       </c>
     </row>
     <row r="359">
@@ -22350,7 +22350,7 @@
         </is>
       </c>
       <c r="M359" s="2" t="n">
-        <v>28920.06</v>
+        <v>29110.52</v>
       </c>
     </row>
     <row r="360">
@@ -22411,7 +22411,7 @@
         </is>
       </c>
       <c r="M360" s="2" t="n">
-        <v>390.95</v>
+        <v>393.53</v>
       </c>
     </row>
     <row r="361">
@@ -22472,7 +22472,7 @@
         </is>
       </c>
       <c r="M361" s="2" t="n">
-        <v>211.9</v>
+        <v>213.3</v>
       </c>
     </row>
     <row r="362">
@@ -22533,7 +22533,7 @@
         </is>
       </c>
       <c r="M362" s="2" t="n">
-        <v>423.67</v>
+        <v>426.46</v>
       </c>
     </row>
     <row r="363">
@@ -22594,7 +22594,7 @@
         </is>
       </c>
       <c r="M363" s="2" t="n">
-        <v>3818.95</v>
+        <v>3844.1</v>
       </c>
     </row>
     <row r="364">
@@ -22655,7 +22655,7 @@
         </is>
       </c>
       <c r="M364" s="2" t="n">
-        <v>847.61</v>
+        <v>853.2</v>
       </c>
     </row>
     <row r="365">
@@ -22716,7 +22716,7 @@
         </is>
       </c>
       <c r="M365" s="2" t="n">
-        <v>673.41</v>
+        <v>677.84</v>
       </c>
     </row>
     <row r="366">
@@ -22777,7 +22777,7 @@
         </is>
       </c>
       <c r="M366" s="2" t="n">
-        <v>2062.43</v>
+        <v>2076.02</v>
       </c>
     </row>
     <row r="367">
@@ -22838,7 +22838,7 @@
         </is>
       </c>
       <c r="M367" s="2" t="n">
-        <v>4638.22</v>
+        <v>4668.77</v>
       </c>
     </row>
     <row r="368">
@@ -22899,7 +22899,7 @@
         </is>
       </c>
       <c r="M368" s="2" t="n">
-        <v>1124.81</v>
+        <v>1132.22</v>
       </c>
     </row>
     <row r="369">
@@ -22960,7 +22960,7 @@
         </is>
       </c>
       <c r="M369" s="2" t="n">
-        <v>2568.39</v>
+        <v>2585.3</v>
       </c>
     </row>
     <row r="370">
@@ -23021,7 +23021,7 @@
         </is>
       </c>
       <c r="M370" s="2" t="n">
-        <v>904.49</v>
+        <v>910.45</v>
       </c>
     </row>
     <row r="371">
@@ -23082,7 +23082,7 @@
         </is>
       </c>
       <c r="M371" s="2" t="n">
-        <v>242.27</v>
+        <v>243.87</v>
       </c>
     </row>
     <row r="372">
@@ -23143,7 +23143,7 @@
         </is>
       </c>
       <c r="M372" s="2" t="n">
-        <v>1128.54</v>
+        <v>1135.97</v>
       </c>
     </row>
     <row r="373">
@@ -23204,7 +23204,7 @@
         </is>
       </c>
       <c r="M373" s="2" t="n">
-        <v>1635.87</v>
+        <v>1646.64</v>
       </c>
     </row>
     <row r="374">
@@ -23265,7 +23265,7 @@
         </is>
       </c>
       <c r="M374" s="2" t="n">
-        <v>343.39</v>
+        <v>345.65</v>
       </c>
     </row>
     <row r="375">
@@ -23326,7 +23326,7 @@
         </is>
       </c>
       <c r="M375" s="2" t="n">
-        <v>7131.55</v>
+        <v>7178.52</v>
       </c>
     </row>
     <row r="376">
@@ -23387,7 +23387,7 @@
         </is>
       </c>
       <c r="M376" s="2" t="n">
-        <v>1290.75</v>
+        <v>1299.25</v>
       </c>
     </row>
     <row r="377">
@@ -23448,7 +23448,7 @@
         </is>
       </c>
       <c r="M377" s="2" t="n">
-        <v>496.97</v>
+        <v>500.25</v>
       </c>
     </row>
     <row r="378">
@@ -23509,7 +23509,7 @@
         </is>
       </c>
       <c r="M378" s="2" t="n">
-        <v>125.29</v>
+        <v>126.11</v>
       </c>
     </row>
     <row r="379">
@@ -23570,7 +23570,7 @@
         </is>
       </c>
       <c r="M379" s="2" t="n">
-        <v>1712.26</v>
+        <v>1723.53</v>
       </c>
     </row>
     <row r="380">
@@ -23631,7 +23631,7 @@
         </is>
       </c>
       <c r="M380" s="2" t="n">
-        <v>1623.94</v>
+        <v>1634.63</v>
       </c>
     </row>
     <row r="381">
@@ -23692,7 +23692,7 @@
         </is>
       </c>
       <c r="M381" s="2" t="n">
-        <v>3043.95</v>
+        <v>3064</v>
       </c>
     </row>
     <row r="382">
@@ -23753,7 +23753,7 @@
         </is>
       </c>
       <c r="M382" s="2" t="n">
-        <v>7192.45</v>
+        <v>7239.82</v>
       </c>
     </row>
     <row r="383">
@@ -23814,7 +23814,7 @@
         </is>
       </c>
       <c r="M383" s="2" t="n">
-        <v>113.06</v>
+        <v>113.81</v>
       </c>
     </row>
     <row r="384">
@@ -23875,7 +23875,7 @@
         </is>
       </c>
       <c r="M384" s="2" t="n">
-        <v>441.33</v>
+        <v>444.23</v>
       </c>
     </row>
     <row r="385">
@@ -23936,7 +23936,7 @@
         </is>
       </c>
       <c r="M385" s="2" t="n">
-        <v>2858.49</v>
+        <v>2877.32</v>
       </c>
     </row>
     <row r="386">
@@ -23997,7 +23997,7 @@
         </is>
       </c>
       <c r="M386" s="2" t="n">
-        <v>1217.58</v>
+        <v>1225.6</v>
       </c>
     </row>
     <row r="387">
@@ -24058,7 +24058,7 @@
         </is>
       </c>
       <c r="M387" s="2" t="n">
-        <v>2835.37</v>
+        <v>2860.63</v>
       </c>
     </row>
     <row r="388">
@@ -24119,7 +24119,7 @@
         </is>
       </c>
       <c r="M388" s="2" t="n">
-        <v>1590.31</v>
+        <v>1604.48</v>
       </c>
     </row>
     <row r="389">
@@ -24180,7 +24180,7 @@
         </is>
       </c>
       <c r="M389" s="2" t="n">
-        <v>7389.68</v>
+        <v>7455.5</v>
       </c>
     </row>
     <row r="390">
@@ -24241,7 +24241,7 @@
         </is>
       </c>
       <c r="M390" s="2" t="n">
-        <v>445.62</v>
+        <v>449.59</v>
       </c>
     </row>
     <row r="391">
@@ -24302,7 +24302,7 @@
         </is>
       </c>
       <c r="M391" s="2" t="n">
-        <v>560.47</v>
+        <v>565.47</v>
       </c>
     </row>
     <row r="392">
@@ -24363,7 +24363,7 @@
         </is>
       </c>
       <c r="M392" s="2" t="n">
-        <v>573.08</v>
+        <v>578.1900000000001</v>
       </c>
     </row>
     <row r="393">
@@ -24424,7 +24424,7 @@
         </is>
       </c>
       <c r="M393" s="2" t="n">
-        <v>13920.98</v>
+        <v>14044.97</v>
       </c>
     </row>
     <row r="394">
@@ -24485,7 +24485,7 @@
         </is>
       </c>
       <c r="M394" s="2" t="n">
-        <v>11538.04</v>
+        <v>11640.8</v>
       </c>
     </row>
     <row r="395">
@@ -24546,7 +24546,7 @@
         </is>
       </c>
       <c r="M395" s="2" t="n">
-        <v>590.84</v>
+        <v>596.1</v>
       </c>
     </row>
     <row r="396">
@@ -24607,7 +24607,7 @@
         </is>
       </c>
       <c r="M396" s="2" t="n">
-        <v>1201.02</v>
+        <v>1211.71</v>
       </c>
     </row>
     <row r="397">
@@ -24668,7 +24668,7 @@
         </is>
       </c>
       <c r="M397" s="2" t="n">
-        <v>1441.22</v>
+        <v>1454.06</v>
       </c>
     </row>
     <row r="398">
@@ -24729,7 +24729,7 @@
         </is>
       </c>
       <c r="M398" s="2" t="n">
-        <v>257.8</v>
+        <v>260.1</v>
       </c>
     </row>
     <row r="399">
@@ -24790,7 +24790,7 @@
         </is>
       </c>
       <c r="M399" s="2" t="n">
-        <v>181.12</v>
+        <v>182.73</v>
       </c>
     </row>
     <row r="400">
@@ -24851,7 +24851,7 @@
         </is>
       </c>
       <c r="M400" s="2" t="n">
-        <v>137.91</v>
+        <v>139.14</v>
       </c>
     </row>
     <row r="401">
@@ -24912,7 +24912,7 @@
         </is>
       </c>
       <c r="M401" s="2" t="n">
-        <v>375.47</v>
+        <v>378.81</v>
       </c>
     </row>
     <row r="402">
@@ -24973,7 +24973,7 @@
         </is>
       </c>
       <c r="M402" s="2" t="n">
-        <v>697.83</v>
+        <v>704.05</v>
       </c>
     </row>
     <row r="403">
@@ -25034,7 +25034,7 @@
         </is>
       </c>
       <c r="M403" s="2" t="n">
-        <v>125.49</v>
+        <v>126.6</v>
       </c>
     </row>
     <row r="404">
@@ -25095,7 +25095,7 @@
         </is>
       </c>
       <c r="M404" s="2" t="n">
-        <v>2240</v>
+        <v>2259.95</v>
       </c>
     </row>
     <row r="405">
@@ -25156,7 +25156,7 @@
         </is>
       </c>
       <c r="M405" s="2" t="n">
-        <v>7904.62</v>
+        <v>7975.02</v>
       </c>
     </row>
     <row r="406">
@@ -25217,7 +25217,7 @@
         </is>
       </c>
       <c r="M406" s="2" t="n">
-        <v>4334.67</v>
+        <v>4373.28</v>
       </c>
     </row>
     <row r="407">
@@ -25278,7 +25278,7 @@
         </is>
       </c>
       <c r="M407" s="2" t="n">
-        <v>1202.67</v>
+        <v>1213.38</v>
       </c>
     </row>
     <row r="408">
@@ -25339,7 +25339,7 @@
         </is>
       </c>
       <c r="M408" s="2" t="n">
-        <v>484.41</v>
+        <v>488.72</v>
       </c>
     </row>
     <row r="409">
@@ -25400,7 +25400,7 @@
         </is>
       </c>
       <c r="M409" s="2" t="n">
-        <v>319.32</v>
+        <v>322.16</v>
       </c>
     </row>
     <row r="410">
@@ -25461,7 +25461,7 @@
         </is>
       </c>
       <c r="M410" s="2" t="n">
-        <v>125.49</v>
+        <v>126.6</v>
       </c>
     </row>
     <row r="411">
@@ -25522,7 +25522,7 @@
         </is>
       </c>
       <c r="M411" s="2" t="n">
-        <v>2388.61</v>
+        <v>2409.89</v>
       </c>
     </row>
     <row r="412">
@@ -25583,7 +25583,7 @@
         </is>
       </c>
       <c r="M412" s="2" t="n">
-        <v>509.4</v>
+        <v>513.9299999999999</v>
       </c>
     </row>
     <row r="413">
@@ -25644,7 +25644,7 @@
         </is>
       </c>
       <c r="M413" s="2" t="n">
-        <v>5485.28</v>
+        <v>5534.13</v>
       </c>
     </row>
     <row r="414">
@@ -25705,7 +25705,7 @@
         </is>
       </c>
       <c r="M414" s="2" t="n">
-        <v>337.86</v>
+        <v>340.87</v>
       </c>
     </row>
     <row r="415">
@@ -25766,7 +25766,7 @@
         </is>
       </c>
       <c r="M415" s="2" t="n">
-        <v>910.01</v>
+        <v>918.12</v>
       </c>
     </row>
     <row r="416">
@@ -25827,7 +25827,7 @@
         </is>
       </c>
       <c r="M416" s="2" t="n">
-        <v>319.5</v>
+        <v>322.34</v>
       </c>
     </row>
     <row r="417">
@@ -25888,7 +25888,7 @@
         </is>
       </c>
       <c r="M417" s="2" t="n">
-        <v>550.95</v>
+        <v>555.86</v>
       </c>
     </row>
     <row r="418">
@@ -25949,7 +25949,7 @@
         </is>
       </c>
       <c r="M418" s="2" t="n">
-        <v>495.43</v>
+        <v>499.84</v>
       </c>
     </row>
     <row r="419">
@@ -26010,7 +26010,7 @@
         </is>
       </c>
       <c r="M419" s="2" t="n">
-        <v>1162.67</v>
+        <v>1173.02</v>
       </c>
     </row>
     <row r="420">
@@ -26071,7 +26071,7 @@
         </is>
       </c>
       <c r="M420" s="2" t="n">
-        <v>1005.95</v>
+        <v>1014.91</v>
       </c>
     </row>
     <row r="421">
@@ -26132,7 +26132,7 @@
         </is>
       </c>
       <c r="M421" s="2" t="n">
-        <v>34451.91</v>
+        <v>34758.76</v>
       </c>
     </row>
     <row r="422">
@@ -26193,7 +26193,7 @@
         </is>
       </c>
       <c r="M422" s="2" t="n">
-        <v>146.61</v>
+        <v>147.91</v>
       </c>
     </row>
     <row r="423">
@@ -26254,7 +26254,7 @@
         </is>
       </c>
       <c r="M423" s="2" t="n">
-        <v>3738.89</v>
+        <v>3772.19</v>
       </c>
     </row>
     <row r="424">
@@ -26315,7 +26315,7 @@
         </is>
       </c>
       <c r="M424" s="2" t="n">
-        <v>586.4299999999999</v>
+        <v>591.65</v>
       </c>
     </row>
     <row r="425">
@@ -26376,7 +26376,7 @@
         </is>
       </c>
       <c r="M425" s="2" t="n">
-        <v>116.79</v>
+        <v>117.83</v>
       </c>
     </row>
     <row r="426">
@@ -26437,7 +26437,7 @@
         </is>
       </c>
       <c r="M426" s="2" t="n">
-        <v>1732.83</v>
+        <v>1748.27</v>
       </c>
     </row>
     <row r="427">
@@ -26498,7 +26498,7 @@
         </is>
       </c>
       <c r="M427" s="2" t="n">
-        <v>377.64</v>
+        <v>381.01</v>
       </c>
     </row>
     <row r="428">
@@ -26559,7 +26559,7 @@
         </is>
       </c>
       <c r="M428" s="2" t="n">
-        <v>303.29</v>
+        <v>305.99</v>
       </c>
     </row>
     <row r="429">
@@ -26620,7 +26620,7 @@
         </is>
       </c>
       <c r="M429" s="2" t="n">
-        <v>716.85</v>
+        <v>723.24</v>
       </c>
     </row>
     <row r="430">
@@ -26681,7 +26681,7 @@
         </is>
       </c>
       <c r="M430" s="2" t="n">
-        <v>225.02</v>
+        <v>224.63</v>
       </c>
     </row>
     <row r="431">
@@ -26742,7 +26742,7 @@
         </is>
       </c>
       <c r="M431" s="2" t="n">
-        <v>138.32</v>
+        <v>138.09</v>
       </c>
     </row>
     <row r="432">
@@ -26803,7 +26803,7 @@
         </is>
       </c>
       <c r="M432" s="2" t="n">
-        <v>3854.25</v>
+        <v>3847.65</v>
       </c>
     </row>
     <row r="433">
@@ -26864,7 +26864,7 @@
         </is>
       </c>
       <c r="M433" s="2" t="n">
-        <v>4949.02</v>
+        <v>4940.53</v>
       </c>
     </row>
     <row r="434">
@@ -26925,7 +26925,7 @@
         </is>
       </c>
       <c r="M434" s="2" t="n">
-        <v>228.84</v>
+        <v>228.45</v>
       </c>
     </row>
     <row r="435">
@@ -26986,7 +26986,7 @@
         </is>
       </c>
       <c r="M435" s="2" t="n">
-        <v>742.15</v>
+        <v>740.87</v>
       </c>
     </row>
     <row r="436">
@@ -27047,7 +27047,7 @@
         </is>
       </c>
       <c r="M436" s="2" t="n">
-        <v>4458.95</v>
+        <v>4451.3</v>
       </c>
     </row>
     <row r="437">
@@ -27108,7 +27108,7 @@
         </is>
       </c>
       <c r="M437" s="2" t="n">
-        <v>554.23</v>
+        <v>553.28</v>
       </c>
     </row>
     <row r="438">
@@ -27169,7 +27169,7 @@
         </is>
       </c>
       <c r="M438" s="2" t="n">
-        <v>116.79</v>
+        <v>116.59</v>
       </c>
     </row>
     <row r="439">
@@ -27230,7 +27230,7 @@
         </is>
       </c>
       <c r="M439" s="2" t="n">
-        <v>535.0700000000001</v>
+        <v>534.16</v>
       </c>
     </row>
     <row r="440">
@@ -27291,7 +27291,7 @@
         </is>
       </c>
       <c r="M440" s="2" t="n">
-        <v>535.0700000000001</v>
+        <v>534.16</v>
       </c>
     </row>
     <row r="441">
@@ -27352,7 +27352,7 @@
         </is>
       </c>
       <c r="M441" s="2" t="n">
-        <v>543.77</v>
+        <v>542.84</v>
       </c>
     </row>
     <row r="442">
@@ -27413,7 +27413,7 @@
         </is>
       </c>
       <c r="M442" s="2" t="n">
-        <v>1344.11</v>
+        <v>1341.81</v>
       </c>
     </row>
     <row r="443">
@@ -27474,7 +27474,7 @@
         </is>
       </c>
       <c r="M443" s="2" t="n">
-        <v>5056.69</v>
+        <v>5048.03</v>
       </c>
     </row>
     <row r="444">
@@ -27535,7 +27535,7 @@
         </is>
       </c>
       <c r="M444" s="2" t="n">
-        <v>2931.72</v>
+        <v>2926.7</v>
       </c>
     </row>
     <row r="445">
@@ -27596,7 +27596,7 @@
         </is>
       </c>
       <c r="M445" s="2" t="n">
-        <v>220.19</v>
+        <v>219.81</v>
       </c>
     </row>
     <row r="446">
@@ -27657,7 +27657,7 @@
         </is>
       </c>
       <c r="M446" s="2" t="n">
-        <v>400.34</v>
+        <v>399.65</v>
       </c>
     </row>
     <row r="447">
@@ -27718,7 +27718,7 @@
         </is>
       </c>
       <c r="M447" s="2" t="n">
-        <v>108.09</v>
+        <v>107.91</v>
       </c>
     </row>
     <row r="448">
@@ -27779,7 +27779,7 @@
         </is>
       </c>
       <c r="M448" s="2" t="n">
-        <v>4195.77</v>
+        <v>4188.58</v>
       </c>
     </row>
     <row r="449">
@@ -27840,7 +27840,7 @@
         </is>
       </c>
       <c r="M449" s="2" t="n">
-        <v>1374.96</v>
+        <v>1372.6</v>
       </c>
     </row>
     <row r="450">
@@ -27901,7 +27901,7 @@
         </is>
       </c>
       <c r="M450" s="2" t="n">
-        <v>438.61</v>
+        <v>437.86</v>
       </c>
     </row>
     <row r="451">
@@ -27962,7 +27962,7 @@
         </is>
       </c>
       <c r="M451" s="2" t="n">
-        <v>575.66</v>
+        <v>574.67</v>
       </c>
     </row>
     <row r="452">
@@ -28023,7 +28023,7 @@
         </is>
       </c>
       <c r="M452" s="2" t="n">
-        <v>3391.84</v>
+        <v>3386.02</v>
       </c>
     </row>
     <row r="453">
@@ -28084,7 +28084,7 @@
         </is>
       </c>
       <c r="M453" s="2" t="n">
-        <v>16151.6</v>
+        <v>16123.91</v>
       </c>
     </row>
     <row r="454">
@@ -28145,7 +28145,7 @@
         </is>
       </c>
       <c r="M454" s="2" t="n">
-        <v>23567.85</v>
+        <v>23527.46</v>
       </c>
     </row>
     <row r="455">
@@ -28206,7 +28206,7 @@
         </is>
       </c>
       <c r="M455" s="2" t="n">
-        <v>987.04</v>
+        <v>985.35</v>
       </c>
     </row>
     <row r="456">
@@ -28267,7 +28267,7 @@
         </is>
       </c>
       <c r="M456" s="2" t="n">
-        <v>1163.41</v>
+        <v>1161.41</v>
       </c>
     </row>
     <row r="457">
@@ -28328,7 +28328,7 @@
         </is>
       </c>
       <c r="M457" s="2" t="n">
-        <v>37684.3</v>
+        <v>37619.71</v>
       </c>
     </row>
     <row r="458">
@@ -28389,7 +28389,7 @@
         </is>
       </c>
       <c r="M458" s="2" t="n">
-        <v>741.59</v>
+        <v>740.3200000000001</v>
       </c>
     </row>
     <row r="459">
@@ -28450,7 +28450,7 @@
         </is>
       </c>
       <c r="M459" s="2" t="n">
-        <v>593.74</v>
+        <v>592.73</v>
       </c>
     </row>
     <row r="460">
@@ -28511,7 +28511,7 @@
         </is>
       </c>
       <c r="M460" s="2" t="n">
-        <v>5046.43</v>
+        <v>5037.78</v>
       </c>
     </row>
     <row r="461">
@@ -28572,7 +28572,7 @@
         </is>
       </c>
       <c r="M461" s="2" t="n">
-        <v>3218.02</v>
+        <v>3212.51</v>
       </c>
     </row>
     <row r="462">
@@ -28633,7 +28633,7 @@
         </is>
       </c>
       <c r="M462" s="2" t="n">
-        <v>755.8099999999999</v>
+        <v>754.52</v>
       </c>
     </row>
     <row r="463">
@@ -28694,7 +28694,7 @@
         </is>
       </c>
       <c r="M463" s="2" t="n">
-        <v>4456.43</v>
+        <v>4448.79</v>
       </c>
     </row>
     <row r="464">
@@ -28755,7 +28755,7 @@
         </is>
       </c>
       <c r="M464" s="2" t="n">
-        <v>27272.51</v>
+        <v>27225.77</v>
       </c>
     </row>
     <row r="465">
@@ -28816,7 +28816,7 @@
         </is>
       </c>
       <c r="M465" s="2" t="n">
-        <v>243.52</v>
+        <v>243.1</v>
       </c>
     </row>
     <row r="466">
@@ -28877,7 +28877,7 @@
         </is>
       </c>
       <c r="M466" s="2" t="n">
-        <v>155.72</v>
+        <v>155.45</v>
       </c>
     </row>
     <row r="467">
@@ -28938,7 +28938,7 @@
         </is>
       </c>
       <c r="M467" s="2" t="n">
-        <v>557.02</v>
+        <v>556.45</v>
       </c>
     </row>
     <row r="468">
@@ -28999,7 +28999,7 @@
         </is>
       </c>
       <c r="M468" s="2" t="n">
-        <v>14911.51</v>
+        <v>14896.13</v>
       </c>
     </row>
     <row r="469">
@@ -29060,7 +29060,7 @@
         </is>
       </c>
       <c r="M469" s="2" t="n">
-        <v>8269.620000000001</v>
+        <v>8261.09</v>
       </c>
     </row>
     <row r="470">
@@ -29121,7 +29121,7 @@
         </is>
       </c>
       <c r="M470" s="2" t="n">
-        <v>1055.77</v>
+        <v>1054.68</v>
       </c>
     </row>
     <row r="471">
@@ -29182,7 +29182,7 @@
         </is>
       </c>
       <c r="M471" s="2" t="n">
-        <v>216.04</v>
+        <v>215.82</v>
       </c>
     </row>
     <row r="472">
@@ -29243,7 +29243,7 @@
         </is>
       </c>
       <c r="M472" s="2" t="n">
-        <v>111.4</v>
+        <v>111.29</v>
       </c>
     </row>
     <row r="473">
@@ -29304,7 +29304,7 @@
         </is>
       </c>
       <c r="M473" s="2" t="n">
-        <v>2831.66</v>
+        <v>2828.74</v>
       </c>
     </row>
     <row r="474">
@@ -29365,7 +29365,7 @@
         </is>
       </c>
       <c r="M474" s="2" t="n">
-        <v>4916.43</v>
+        <v>4911.36</v>
       </c>
     </row>
     <row r="475">
@@ -29426,7 +29426,7 @@
         </is>
       </c>
       <c r="M475" s="2" t="n">
-        <v>6926.69</v>
+        <v>6919.54</v>
       </c>
     </row>
     <row r="476">
@@ -29487,7 +29487,7 @@
         </is>
       </c>
       <c r="M476" s="2" t="n">
-        <v>1598.87</v>
+        <v>1597.22</v>
       </c>
     </row>
     <row r="477">
@@ -29548,7 +29548,7 @@
         </is>
       </c>
       <c r="M477" s="2" t="n">
-        <v>1838.8</v>
+        <v>1836.9</v>
       </c>
     </row>
     <row r="478">
@@ -29609,7 +29609,7 @@
         </is>
       </c>
       <c r="M478" s="2" t="n">
-        <v>488.69</v>
+        <v>488.19</v>
       </c>
     </row>
     <row r="479">
@@ -29670,7 +29670,7 @@
         </is>
       </c>
       <c r="M479" s="2" t="n">
-        <v>5700.83</v>
+        <v>5694.95</v>
       </c>
     </row>
     <row r="480">
@@ -29731,7 +29731,7 @@
         </is>
       </c>
       <c r="M480" s="2" t="n">
-        <v>284.1</v>
+        <v>283.81</v>
       </c>
     </row>
     <row r="481">
@@ -29792,7 +29792,7 @@
         </is>
       </c>
       <c r="M481" s="2" t="n">
-        <v>556.61</v>
+        <v>556.03</v>
       </c>
     </row>
     <row r="482">
@@ -29853,7 +29853,7 @@
         </is>
       </c>
       <c r="M482" s="2" t="n">
-        <v>1021.55</v>
+        <v>1020.5</v>
       </c>
     </row>
     <row r="483">
@@ -29914,7 +29914,7 @@
         </is>
       </c>
       <c r="M483" s="2" t="n">
-        <v>2147.86</v>
+        <v>2145.64</v>
       </c>
     </row>
     <row r="484">
@@ -29975,7 +29975,7 @@
         </is>
       </c>
       <c r="M484" s="2" t="n">
-        <v>34939.36</v>
+        <v>34903.32</v>
       </c>
     </row>
     <row r="485">
@@ -30036,7 +30036,7 @@
         </is>
       </c>
       <c r="M485" s="2" t="n">
-        <v>592.8099999999999</v>
+        <v>592.1900000000001</v>
       </c>
     </row>
     <row r="486">
@@ -30097,7 +30097,7 @@
         </is>
       </c>
       <c r="M486" s="2" t="n">
-        <v>232.61</v>
+        <v>232.37</v>
       </c>
     </row>
     <row r="487">
@@ -30158,7 +30158,7 @@
         </is>
       </c>
       <c r="M487" s="2" t="n">
-        <v>9452.83</v>
+        <v>9443.08</v>
       </c>
     </row>
     <row r="488">
@@ -30219,7 +30219,7 @@
         </is>
       </c>
       <c r="M488" s="2" t="n">
-        <v>554.95</v>
+        <v>554.38</v>
       </c>
     </row>
     <row r="489">
@@ -30280,7 +30280,7 @@
         </is>
       </c>
       <c r="M489" s="2" t="n">
-        <v>285.7</v>
+        <v>285.4</v>
       </c>
     </row>
     <row r="490">
@@ -30341,7 +30341,7 @@
         </is>
       </c>
       <c r="M490" s="2" t="n">
-        <v>1284.19</v>
+        <v>1282.87</v>
       </c>
     </row>
     <row r="491">
@@ -30402,7 +30402,7 @@
         </is>
       </c>
       <c r="M491" s="2" t="n">
-        <v>1180.18</v>
+        <v>1178.97</v>
       </c>
     </row>
     <row r="492">
@@ -30463,7 +30463,7 @@
         </is>
       </c>
       <c r="M492" s="2" t="n">
-        <v>140.81</v>
+        <v>140.66</v>
       </c>
     </row>
     <row r="493">
@@ -30524,7 +30524,7 @@
         </is>
       </c>
       <c r="M493" s="2" t="n">
-        <v>2406.38</v>
+        <v>2403.9</v>
       </c>
     </row>
     <row r="494">
@@ -30585,7 +30585,7 @@
         </is>
       </c>
       <c r="M494" s="2" t="n">
-        <v>16382.69</v>
+        <v>16365.79</v>
       </c>
     </row>
     <row r="495">
@@ -30646,7 +30646,7 @@
         </is>
       </c>
       <c r="M495" s="2" t="n">
-        <v>571.39</v>
+        <v>570.8</v>
       </c>
     </row>
     <row r="496">
@@ -30707,7 +30707,7 @@
         </is>
       </c>
       <c r="M496" s="2" t="n">
-        <v>213.72</v>
+        <v>213.5</v>
       </c>
     </row>
     <row r="497">
@@ -30768,7 +30768,7 @@
         </is>
       </c>
       <c r="M497" s="2" t="n">
-        <v>156.21</v>
+        <v>156.05</v>
       </c>
     </row>
     <row r="498">
@@ -30829,7 +30829,7 @@
         </is>
       </c>
       <c r="M498" s="2" t="n">
-        <v>2076.93</v>
+        <v>2074.79</v>
       </c>
     </row>
     <row r="499">
@@ -30890,7 +30890,7 @@
         </is>
       </c>
       <c r="M499" s="2" t="n">
-        <v>1058.56</v>
+        <v>1057.47</v>
       </c>
     </row>
     <row r="500">
@@ -30951,7 +30951,7 @@
         </is>
       </c>
       <c r="M500" s="2" t="n">
-        <v>484.41</v>
+        <v>483.91</v>
       </c>
     </row>
     <row r="501">
@@ -31012,7 +31012,7 @@
         </is>
       </c>
       <c r="M501" s="2" t="n">
-        <v>76290.62</v>
+        <v>76211.92999999999</v>
       </c>
     </row>
     <row r="502">
@@ -31073,7 +31073,7 @@
         </is>
       </c>
       <c r="M502" s="2" t="n">
-        <v>1391.52</v>
+        <v>1390.09</v>
       </c>
     </row>
     <row r="503">
@@ -31134,7 +31134,7 @@
         </is>
       </c>
       <c r="M503" s="2" t="n">
-        <v>2451.73</v>
+        <v>2449.2</v>
       </c>
     </row>
     <row r="504">
@@ -31195,7 +31195,7 @@
         </is>
       </c>
       <c r="M504" s="2" t="n">
-        <v>1380.34</v>
+        <v>1370.45</v>
       </c>
     </row>
     <row r="505">
@@ -31256,7 +31256,7 @@
         </is>
       </c>
       <c r="M505" s="2" t="n">
-        <v>418.28</v>
+        <v>415.29</v>
       </c>
     </row>
     <row r="506">
@@ -31317,7 +31317,7 @@
         </is>
       </c>
       <c r="M506" s="2" t="n">
-        <v>233.3</v>
+        <v>231.63</v>
       </c>
     </row>
     <row r="507">
@@ -31378,7 +31378,7 @@
         </is>
       </c>
       <c r="M507" s="2" t="n">
-        <v>7265.84</v>
+        <v>7213.79</v>
       </c>
     </row>
     <row r="508">
@@ -31439,7 +31439,7 @@
         </is>
       </c>
       <c r="M508" s="2" t="n">
-        <v>1769.22</v>
+        <v>1756.55</v>
       </c>
     </row>
     <row r="509">
@@ -31500,7 +31500,7 @@
         </is>
       </c>
       <c r="M509" s="2" t="n">
-        <v>1299.72</v>
+        <v>1290.41</v>
       </c>
     </row>
     <row r="510">
@@ -31561,7 +31561,7 @@
         </is>
       </c>
       <c r="M510" s="2" t="n">
-        <v>163.45</v>
+        <v>162.28</v>
       </c>
     </row>
     <row r="511">
@@ -31622,7 +31622,7 @@
         </is>
       </c>
       <c r="M511" s="2" t="n">
-        <v>334.63</v>
+        <v>332.23</v>
       </c>
     </row>
     <row r="512">
@@ -31683,7 +31683,7 @@
         </is>
       </c>
       <c r="M512" s="2" t="n">
-        <v>1739.4</v>
+        <v>1726.94</v>
       </c>
     </row>
     <row r="513">
@@ -31744,7 +31744,7 @@
         </is>
       </c>
       <c r="M513" s="2" t="n">
-        <v>1039</v>
+        <v>1031.56</v>
       </c>
     </row>
     <row r="514">
@@ -31805,7 +31805,7 @@
         </is>
       </c>
       <c r="M514" s="2" t="n">
-        <v>3676.05</v>
+        <v>3649.71</v>
       </c>
     </row>
     <row r="515">
@@ -31866,7 +31866,7 @@
         </is>
       </c>
       <c r="M515" s="2" t="n">
-        <v>212.46</v>
+        <v>210.93</v>
       </c>
     </row>
     <row r="516">
@@ -31927,7 +31927,7 @@
         </is>
       </c>
       <c r="M516" s="2" t="n">
-        <v>1753.48</v>
+        <v>1740.92</v>
       </c>
     </row>
     <row r="517">
@@ -31988,7 +31988,7 @@
         </is>
       </c>
       <c r="M517" s="2" t="n">
-        <v>501.94</v>
+        <v>498.35</v>
       </c>
     </row>
     <row r="518">
@@ -32049,7 +32049,7 @@
         </is>
       </c>
       <c r="M518" s="2" t="n">
-        <v>5373.82</v>
+        <v>5335.33</v>
       </c>
     </row>
     <row r="519">
@@ -32110,7 +32110,7 @@
         </is>
       </c>
       <c r="M519" s="2" t="n">
-        <v>401.31</v>
+        <v>398.43</v>
       </c>
     </row>
     <row r="520">
@@ -32171,7 +32171,7 @@
         </is>
       </c>
       <c r="M520" s="2" t="n">
-        <v>2001.34</v>
+        <v>1987</v>
       </c>
     </row>
     <row r="521">
@@ -32232,7 +32232,7 @@
         </is>
       </c>
       <c r="M521" s="2" t="n">
-        <v>6290.84</v>
+        <v>6245.77</v>
       </c>
     </row>
     <row r="522">
@@ -32293,7 +32293,7 @@
         </is>
       </c>
       <c r="M522" s="2" t="n">
-        <v>169.8</v>
+        <v>168.58</v>
       </c>
     </row>
     <row r="523">
@@ -32354,7 +32354,7 @@
         </is>
       </c>
       <c r="M523" s="2" t="n">
-        <v>891.24</v>
+        <v>884.85</v>
       </c>
     </row>
     <row r="524">
@@ -32415,7 +32415,7 @@
         </is>
       </c>
       <c r="M524" s="2" t="n">
-        <v>445.62</v>
+        <v>442.43</v>
       </c>
     </row>
     <row r="525">
@@ -32476,7 +32476,7 @@
         </is>
       </c>
       <c r="M525" s="2" t="n">
-        <v>644.01</v>
+        <v>639.4</v>
       </c>
     </row>
     <row r="526">
@@ -32537,7 +32537,7 @@
         </is>
       </c>
       <c r="M526" s="2" t="n">
-        <v>423.42</v>
+        <v>420.39</v>
       </c>
     </row>
     <row r="527">
@@ -32598,7 +32598,7 @@
         </is>
       </c>
       <c r="M527" s="2" t="n">
-        <v>480.41</v>
+        <v>476.96</v>
       </c>
     </row>
     <row r="528">
@@ -32659,7 +32659,7 @@
         </is>
       </c>
       <c r="M528" s="2" t="n">
-        <v>215.91</v>
+        <v>214.36</v>
       </c>
     </row>
     <row r="529">
@@ -32720,7 +32720,7 @@
         </is>
       </c>
       <c r="M529" s="2" t="n">
-        <v>2009.29</v>
+        <v>1994.89</v>
       </c>
     </row>
     <row r="530">
@@ -32781,7 +32781,7 @@
         </is>
       </c>
       <c r="M530" s="2" t="n">
-        <v>432.3</v>
+        <v>429.2</v>
       </c>
     </row>
     <row r="531">
@@ -32842,7 +32842,7 @@
         </is>
       </c>
       <c r="M531" s="2" t="n">
-        <v>928.37</v>
+        <v>921.72</v>
       </c>
     </row>
     <row r="532">
@@ -32903,7 +32903,7 @@
         </is>
       </c>
       <c r="M532" s="2" t="n">
-        <v>864.6</v>
+        <v>858.41</v>
       </c>
     </row>
     <row r="533">
@@ -32964,7 +32964,7 @@
         </is>
       </c>
       <c r="M533" s="2" t="n">
-        <v>144.36</v>
+        <v>143.33</v>
       </c>
     </row>
     <row r="534">
@@ -33025,7 +33025,7 @@
         </is>
       </c>
       <c r="M534" s="2" t="n">
-        <v>26981.38</v>
+        <v>26788.09</v>
       </c>
     </row>
     <row r="535">
@@ -33086,7 +33086,7 @@
         </is>
       </c>
       <c r="M535" s="2" t="n">
-        <v>374.75</v>
+        <v>372.07</v>
       </c>
     </row>
     <row r="536">
@@ -33147,7 +33147,7 @@
         </is>
       </c>
       <c r="M536" s="2" t="n">
-        <v>15080.85</v>
+        <v>14972.82</v>
       </c>
     </row>
     <row r="537">
@@ -33208,7 +33208,7 @@
         </is>
       </c>
       <c r="M537" s="2" t="n">
-        <v>13920.61</v>
+        <v>13820.89</v>
       </c>
     </row>
     <row r="538">
@@ -33269,7 +33269,7 @@
         </is>
       </c>
       <c r="M538" s="2" t="n">
-        <v>10798.59</v>
+        <v>10721.23</v>
       </c>
     </row>
     <row r="539">
@@ -33330,7 +33330,7 @@
         </is>
       </c>
       <c r="M539" s="2" t="n">
-        <v>1509.61</v>
+        <v>1498.79</v>
       </c>
     </row>
     <row r="540">
@@ -33391,7 +33391,7 @@
         </is>
       </c>
       <c r="M540" s="2" t="n">
-        <v>1945.31</v>
+        <v>1931.38</v>
       </c>
     </row>
     <row r="541">
@@ -33452,7 +33452,7 @@
         </is>
       </c>
       <c r="M541" s="2" t="n">
-        <v>1032.6</v>
+        <v>1025.2</v>
       </c>
     </row>
     <row r="542">
@@ -33513,7 +33513,7 @@
         </is>
       </c>
       <c r="M542" s="2" t="n">
-        <v>753.74</v>
+        <v>748.34</v>
       </c>
     </row>
     <row r="543">
@@ -33574,7 +33574,7 @@
         </is>
       </c>
       <c r="M543" s="2" t="n">
-        <v>1014.65</v>
+        <v>1007.38</v>
       </c>
     </row>
     <row r="544">
@@ -33635,7 +33635,7 @@
         </is>
       </c>
       <c r="M544" s="2" t="n">
-        <v>608.79</v>
+        <v>604.4299999999999</v>
       </c>
     </row>
     <row r="545">
@@ -33696,7 +33696,7 @@
         </is>
       </c>
       <c r="M545" s="2" t="n">
-        <v>1558.31</v>
+        <v>1547.14</v>
       </c>
     </row>
     <row r="546">
@@ -33757,7 +33757,7 @@
         </is>
       </c>
       <c r="M546" s="2" t="n">
-        <v>1511.62</v>
+        <v>1500.79</v>
       </c>
     </row>
     <row r="547">
@@ -33818,7 +33818,7 @@
         </is>
       </c>
       <c r="M547" s="2" t="n">
-        <v>125.49</v>
+        <v>124.59</v>
       </c>
     </row>
     <row r="548">
@@ -33879,7 +33879,7 @@
         </is>
       </c>
       <c r="M548" s="2" t="n">
-        <v>1454.82</v>
+        <v>1444.4</v>
       </c>
     </row>
     <row r="549">
@@ -33940,7 +33940,7 @@
         </is>
       </c>
       <c r="M549" s="2" t="n">
-        <v>1270.27</v>
+        <v>1261.17</v>
       </c>
     </row>
     <row r="550">
@@ -34001,7 +34001,7 @@
         </is>
       </c>
       <c r="M550" s="2" t="n">
-        <v>1511.62</v>
+        <v>1500.79</v>
       </c>
     </row>
     <row r="551">
@@ -34062,7 +34062,7 @@
         </is>
       </c>
       <c r="M551" s="2" t="n">
-        <v>606.58</v>
+        <v>602.24</v>
       </c>
     </row>
     <row r="552">
@@ -34123,7 +34123,7 @@
         </is>
       </c>
       <c r="M552" s="2" t="n">
-        <v>1225.86</v>
+        <v>1217.08</v>
       </c>
     </row>
     <row r="553">
@@ -34184,7 +34184,7 @@
         </is>
       </c>
       <c r="M553" s="2" t="n">
-        <v>209.14</v>
+        <v>207.64</v>
       </c>
     </row>
     <row r="554">
@@ -34245,7 +34245,7 @@
         </is>
       </c>
       <c r="M554" s="2" t="n">
-        <v>3463.81</v>
+        <v>3439</v>
       </c>
     </row>
     <row r="555">
@@ -34306,7 +34306,7 @@
         </is>
       </c>
       <c r="M555" s="2" t="n">
-        <v>3479.85</v>
+        <v>3454.93</v>
       </c>
     </row>
     <row r="556">
@@ -34367,7 +34367,7 @@
         </is>
       </c>
       <c r="M556" s="2" t="n">
-        <v>832.9</v>
+        <v>826.9400000000001</v>
       </c>
     </row>
     <row r="557">
@@ -34428,7 +34428,7 @@
         </is>
       </c>
       <c r="M557" s="2" t="n">
-        <v>1270.27</v>
+        <v>1261.17</v>
       </c>
     </row>
     <row r="558">
@@ -34489,7 +34489,7 @@
         </is>
       </c>
       <c r="M558" s="2" t="n">
-        <v>1270.27</v>
+        <v>1261.17</v>
       </c>
     </row>
     <row r="559">
@@ -34550,7 +34550,7 @@
         </is>
       </c>
       <c r="M559" s="2" t="n">
-        <v>1270.27</v>
+        <v>1261.17</v>
       </c>
     </row>
     <row r="560">
@@ -34611,7 +34611,7 @@
         </is>
       </c>
       <c r="M560" s="2" t="n">
-        <v>316.96</v>
+        <v>314.69</v>
       </c>
     </row>
     <row r="561">
@@ -34672,7 +34672,7 @@
         </is>
       </c>
       <c r="M561" s="2" t="n">
-        <v>957.67</v>
+        <v>950.8</v>
       </c>
     </row>
     <row r="562">
@@ -34733,7 +34733,7 @@
         </is>
       </c>
       <c r="M562" s="2" t="n">
-        <v>871.1799999999999</v>
+        <v>869.9</v>
       </c>
     </row>
     <row r="563">
@@ -34794,7 +34794,7 @@
         </is>
       </c>
       <c r="M563" s="2" t="n">
-        <v>2580.67</v>
+        <v>2576.87</v>
       </c>
     </row>
     <row r="564">
@@ -34855,7 +34855,7 @@
         </is>
       </c>
       <c r="M564" s="2" t="n">
-        <v>4355.75</v>
+        <v>4349.35</v>
       </c>
     </row>
     <row r="565">
@@ -34916,7 +34916,7 @@
         </is>
       </c>
       <c r="M565" s="2" t="n">
-        <v>1185.69</v>
+        <v>1183.95</v>
       </c>
     </row>
     <row r="566">
@@ -34977,7 +34977,7 @@
         </is>
       </c>
       <c r="M566" s="2" t="n">
-        <v>627.4299999999999</v>
+        <v>626.5</v>
       </c>
     </row>
     <row r="567">
@@ -35038,7 +35038,7 @@
         </is>
       </c>
       <c r="M567" s="2" t="n">
-        <v>5138</v>
+        <v>5130.44</v>
       </c>
     </row>
     <row r="568">
@@ -35099,7 +35099,7 @@
         </is>
       </c>
       <c r="M568" s="2" t="n">
-        <v>133.77</v>
+        <v>133.57</v>
       </c>
     </row>
     <row r="569">
@@ -35160,7 +35160,7 @@
         </is>
       </c>
       <c r="M569" s="2" t="n">
-        <v>1201.02</v>
+        <v>1199.25</v>
       </c>
     </row>
     <row r="570">
@@ -35221,7 +35221,7 @@
         </is>
       </c>
       <c r="M570" s="2" t="n">
-        <v>513.26</v>
+        <v>512.51</v>
       </c>
     </row>
     <row r="571">
@@ -35282,7 +35282,7 @@
         </is>
       </c>
       <c r="M571" s="2" t="n">
-        <v>407.98</v>
+        <v>407.38</v>
       </c>
     </row>
     <row r="572">
@@ -35343,7 +35343,7 @@
         </is>
       </c>
       <c r="M572" s="2" t="n">
-        <v>792.67</v>
+        <v>791.5</v>
       </c>
     </row>
     <row r="573">
@@ -35404,7 +35404,7 @@
         </is>
       </c>
       <c r="M573" s="2" t="n">
-        <v>668.84</v>
+        <v>667.86</v>
       </c>
     </row>
     <row r="574">
@@ -35465,7 +35465,7 @@
         </is>
       </c>
       <c r="M574" s="2" t="n">
-        <v>530.1</v>
+        <v>529.3200000000001</v>
       </c>
     </row>
     <row r="575">
@@ -35526,7 +35526,7 @@
         </is>
       </c>
       <c r="M575" s="2" t="n">
-        <v>1159.33</v>
+        <v>1157.62</v>
       </c>
     </row>
     <row r="576">
@@ -35587,7 +35587,7 @@
         </is>
       </c>
       <c r="M576" s="2" t="n">
-        <v>1856.74</v>
+        <v>1854.01</v>
       </c>
     </row>
     <row r="577">
@@ -35648,7 +35648,7 @@
         </is>
       </c>
       <c r="M577" s="2" t="n">
-        <v>982.9</v>
+        <v>981.45</v>
       </c>
     </row>
     <row r="578">
@@ -35709,7 +35709,7 @@
         </is>
       </c>
       <c r="M578" s="2" t="n">
-        <v>938.49</v>
+        <v>937.11</v>
       </c>
     </row>
     <row r="579">
@@ -35770,7 +35770,7 @@
         </is>
       </c>
       <c r="M579" s="2" t="n">
-        <v>178.36</v>
+        <v>178.1</v>
       </c>
     </row>
     <row r="580">
@@ -35831,7 +35831,7 @@
         </is>
       </c>
       <c r="M580" s="2" t="n">
-        <v>38410.43</v>
+        <v>38353.93</v>
       </c>
     </row>
     <row r="581">
@@ -35892,7 +35892,7 @@
         </is>
       </c>
       <c r="M581" s="2" t="n">
-        <v>2896.84</v>
+        <v>2892.58</v>
       </c>
     </row>
     <row r="582">
@@ -35953,7 +35953,7 @@
         </is>
       </c>
       <c r="M582" s="2" t="n">
-        <v>2764.62</v>
+        <v>2760.55</v>
       </c>
     </row>
     <row r="583">
@@ -36014,7 +36014,7 @@
         </is>
       </c>
       <c r="M583" s="2" t="n">
-        <v>209.55</v>
+        <v>209.24</v>
       </c>
     </row>
     <row r="584">
@@ -36075,7 +36075,7 @@
         </is>
       </c>
       <c r="M584" s="2" t="n">
-        <v>8182.44</v>
+        <v>8170.4</v>
       </c>
     </row>
     <row r="585">
@@ -36136,7 +36136,7 @@
         </is>
       </c>
       <c r="M585" s="2" t="n">
-        <v>216.15</v>
+        <v>215.83</v>
       </c>
     </row>
     <row r="586">
@@ -36197,7 +36197,7 @@
         </is>
       </c>
       <c r="M586" s="2" t="n">
-        <v>1428.41</v>
+        <v>1426.31</v>
       </c>
     </row>
     <row r="587">
@@ -36258,7 +36258,7 @@
         </is>
       </c>
       <c r="M587" s="2" t="n">
-        <v>1295.44</v>
+        <v>1293.54</v>
       </c>
     </row>
     <row r="588">
@@ -36319,7 +36319,7 @@
         </is>
       </c>
       <c r="M588" s="2" t="n">
-        <v>1335.83</v>
+        <v>1333.86</v>
       </c>
     </row>
     <row r="589">
@@ -36380,7 +36380,7 @@
         </is>
       </c>
       <c r="M589" s="2" t="n">
-        <v>1159.94</v>
+        <v>1158.24</v>
       </c>
     </row>
     <row r="590">
@@ -36441,7 +36441,7 @@
         </is>
       </c>
       <c r="M590" s="2" t="n">
-        <v>169.04</v>
+        <v>168.79</v>
       </c>
     </row>
     <row r="591">
@@ -36502,7 +36502,7 @@
         </is>
       </c>
       <c r="M591" s="2" t="n">
-        <v>418.28</v>
+        <v>417.67</v>
       </c>
     </row>
     <row r="592">
@@ -36563,7 +36563,7 @@
         </is>
       </c>
       <c r="M592" s="2" t="n">
-        <v>220.19</v>
+        <v>219.86</v>
       </c>
     </row>
     <row r="593">
@@ -36624,7 +36624,7 @@
         </is>
       </c>
       <c r="M593" s="2" t="n">
-        <v>912.74</v>
+        <v>911.4</v>
       </c>
     </row>
     <row r="594">
@@ -36685,7 +36685,7 @@
         </is>
       </c>
       <c r="M594" s="2" t="n">
-        <v>162.01</v>
+        <v>161.77</v>
       </c>
     </row>
     <row r="595">
@@ -36746,7 +36746,7 @@
         </is>
       </c>
       <c r="M595" s="2" t="n">
-        <v>3943.62</v>
+        <v>3937.82</v>
       </c>
     </row>
     <row r="596">
@@ -36807,7 +36807,7 @@
         </is>
       </c>
       <c r="M596" s="2" t="n">
-        <v>1114.05</v>
+        <v>1112.41</v>
       </c>
     </row>
     <row r="597">
@@ -36868,7 +36868,7 @@
         </is>
       </c>
       <c r="M597" s="2" t="n">
-        <v>928.37</v>
+        <v>927.01</v>
       </c>
     </row>
     <row r="598">
@@ -36929,7 +36929,7 @@
         </is>
       </c>
       <c r="M598" s="2" t="n">
-        <v>1259.69</v>
+        <v>1257.83</v>
       </c>
     </row>
     <row r="599">
@@ -36990,7 +36990,7 @@
         </is>
       </c>
       <c r="M599" s="2" t="n">
-        <v>589.74</v>
+        <v>588.87</v>
       </c>
     </row>
     <row r="600">
@@ -37051,7 +37051,7 @@
         </is>
       </c>
       <c r="M600" s="2" t="n">
-        <v>491.45</v>
+        <v>488.77</v>
       </c>
     </row>
     <row r="601">
@@ -37112,7 +37112,7 @@
         </is>
       </c>
       <c r="M601" s="2" t="n">
-        <v>589.74</v>
+        <v>586.53</v>
       </c>
     </row>
     <row r="602">
@@ -37173,7 +37173,7 @@
         </is>
       </c>
       <c r="M602" s="2" t="n">
-        <v>309.72</v>
+        <v>308.04</v>
       </c>
     </row>
     <row r="603">
@@ -37234,7 +37234,7 @@
         </is>
       </c>
       <c r="M603" s="2" t="n">
-        <v>631.5700000000001</v>
+        <v>628.13</v>
       </c>
     </row>
     <row r="604">
@@ -37295,7 +37295,7 @@
         </is>
       </c>
       <c r="M604" s="2" t="n">
-        <v>1855.36</v>
+        <v>1845.26</v>
       </c>
     </row>
     <row r="605">
@@ -37356,7 +37356,7 @@
         </is>
       </c>
       <c r="M605" s="2" t="n">
-        <v>887.66</v>
+        <v>882.83</v>
       </c>
     </row>
     <row r="606">
@@ -37417,7 +37417,7 @@
         </is>
       </c>
       <c r="M606" s="2" t="n">
-        <v>726.6799999999999</v>
+        <v>722.73</v>
       </c>
     </row>
     <row r="607">
@@ -37478,7 +37478,7 @@
         </is>
       </c>
       <c r="M607" s="2" t="n">
-        <v>448.66</v>
+        <v>446.21</v>
       </c>
     </row>
     <row r="608">
@@ -37539,7 +37539,7 @@
         </is>
       </c>
       <c r="M608" s="2" t="n">
-        <v>3179.93</v>
+        <v>3162.62</v>
       </c>
     </row>
     <row r="609">
@@ -37600,7 +37600,7 @@
         </is>
       </c>
       <c r="M609" s="2" t="n">
-        <v>468.32</v>
+        <v>465.77</v>
       </c>
     </row>
     <row r="610">
@@ -37661,7 +37661,7 @@
         </is>
       </c>
       <c r="M610" s="2" t="n">
-        <v>345.95</v>
+        <v>344.06</v>
       </c>
     </row>
     <row r="611">
@@ -37722,7 +37722,7 @@
         </is>
       </c>
       <c r="M611" s="2" t="n">
-        <v>2760.78</v>
+        <v>2745.75</v>
       </c>
     </row>
     <row r="612">
@@ -37783,7 +37783,7 @@
         </is>
       </c>
       <c r="M612" s="2" t="n">
-        <v>1181.44</v>
+        <v>1175.01</v>
       </c>
     </row>
     <row r="613">
@@ -37844,7 +37844,7 @@
         </is>
       </c>
       <c r="M613" s="2" t="n">
-        <v>323.72</v>
+        <v>321.96</v>
       </c>
     </row>
     <row r="614">
@@ -37905,7 +37905,7 @@
         </is>
       </c>
       <c r="M614" s="2" t="n">
-        <v>2279.86</v>
+        <v>2267.44</v>
       </c>
     </row>
     <row r="615">
@@ -37966,7 +37966,7 @@
         </is>
       </c>
       <c r="M615" s="2" t="n">
-        <v>14338.79</v>
+        <v>14260.71</v>
       </c>
     </row>
     <row r="616">
@@ -38027,7 +38027,7 @@
         </is>
       </c>
       <c r="M616" s="2" t="n">
-        <v>234.68</v>
+        <v>233.4</v>
       </c>
     </row>
     <row r="617">
@@ -38088,7 +38088,7 @@
         </is>
       </c>
       <c r="M617" s="2" t="n">
-        <v>836.5700000000001</v>
+        <v>832.01</v>
       </c>
     </row>
     <row r="618">
@@ -38149,7 +38149,7 @@
         </is>
       </c>
       <c r="M618" s="2" t="n">
-        <v>368.86</v>
+        <v>366.86</v>
       </c>
     </row>
     <row r="619">
@@ -38210,7 +38210,7 @@
         </is>
       </c>
       <c r="M619" s="2" t="n">
-        <v>737.73</v>
+        <v>733.71</v>
       </c>
     </row>
     <row r="620">
@@ -38271,7 +38271,7 @@
         </is>
       </c>
       <c r="M620" s="2" t="n">
-        <v>955.55</v>
+        <v>950.35</v>
       </c>
     </row>
     <row r="621">
@@ -38332,7 +38332,7 @@
         </is>
       </c>
       <c r="M621" s="2" t="n">
-        <v>1856.74</v>
+        <v>1846.63</v>
       </c>
     </row>
     <row r="622">
@@ -38393,7 +38393,7 @@
         </is>
       </c>
       <c r="M622" s="2" t="n">
-        <v>786.87</v>
+        <v>782.59</v>
       </c>
     </row>
     <row r="623">
@@ -38454,7 +38454,7 @@
         </is>
       </c>
       <c r="M623" s="2" t="n">
-        <v>3969.98</v>
+        <v>3948.36</v>
       </c>
     </row>
     <row r="624">
@@ -38515,7 +38515,7 @@
         </is>
       </c>
       <c r="M624" s="2" t="n">
-        <v>1234.15</v>
+        <v>1227.43</v>
       </c>
     </row>
     <row r="625">
@@ -38576,7 +38576,7 @@
         </is>
       </c>
       <c r="M625" s="2" t="n">
-        <v>3081.23</v>
+        <v>3064.45</v>
       </c>
     </row>
     <row r="626">
@@ -38637,7 +38637,7 @@
         </is>
       </c>
       <c r="M626" s="2" t="n">
-        <v>1156.15</v>
+        <v>1149.85</v>
       </c>
     </row>
     <row r="627">
@@ -38698,7 +38698,7 @@
         </is>
       </c>
       <c r="M627" s="2" t="n">
-        <v>393.44</v>
+        <v>391.29</v>
       </c>
     </row>
     <row r="628">
@@ -38759,7 +38759,7 @@
         </is>
       </c>
       <c r="M628" s="2" t="n">
-        <v>800.41</v>
+        <v>795.6900000000001</v>
       </c>
     </row>
     <row r="629">
@@ -38820,7 +38820,7 @@
         </is>
       </c>
       <c r="M629" s="2" t="n">
-        <v>201.89</v>
+        <v>200.71</v>
       </c>
     </row>
     <row r="630">
@@ -38881,7 +38881,7 @@
         </is>
       </c>
       <c r="M630" s="2" t="n">
-        <v>101.33</v>
+        <v>100.73</v>
       </c>
     </row>
     <row r="631">
@@ -38942,7 +38942,7 @@
         </is>
       </c>
       <c r="M631" s="2" t="n">
-        <v>853.14</v>
+        <v>848.11</v>
       </c>
     </row>
     <row r="632">
@@ -39003,7 +39003,7 @@
         </is>
       </c>
       <c r="M632" s="2" t="n">
-        <v>4828.88</v>
+        <v>4800.42</v>
       </c>
     </row>
     <row r="633">
@@ -39064,7 +39064,7 @@
         </is>
       </c>
       <c r="M633" s="2" t="n">
-        <v>1372.83</v>
+        <v>1364.74</v>
       </c>
     </row>
     <row r="634">
@@ -39125,7 +39125,7 @@
         </is>
       </c>
       <c r="M634" s="2" t="n">
-        <v>521.8200000000001</v>
+        <v>518.75</v>
       </c>
     </row>
     <row r="635">
@@ -39186,7 +39186,7 @@
         </is>
       </c>
       <c r="M635" s="2" t="n">
-        <v>179.46</v>
+        <v>178.4</v>
       </c>
     </row>
     <row r="636">
@@ -39247,7 +39247,7 @@
         </is>
       </c>
       <c r="M636" s="2" t="n">
-        <v>3231.13</v>
+        <v>3212.09</v>
       </c>
     </row>
     <row r="637">
@@ -39308,7 +39308,7 @@
         </is>
       </c>
       <c r="M637" s="2" t="n">
-        <v>347.86</v>
+        <v>345.81</v>
       </c>
     </row>
     <row r="638">
@@ -39369,7 +39369,7 @@
         </is>
       </c>
       <c r="M638" s="2" t="n">
-        <v>7914.45</v>
+        <v>7867.81</v>
       </c>
     </row>
     <row r="639">
@@ -39430,7 +39430,7 @@
         </is>
       </c>
       <c r="M639" s="2" t="n">
-        <v>275.12</v>
+        <v>273.49</v>
       </c>
     </row>
     <row r="640">
@@ -39491,7 +39491,7 @@
         </is>
       </c>
       <c r="M640" s="2" t="n">
-        <v>126.31</v>
+        <v>125.57</v>
       </c>
     </row>
     <row r="641">
@@ -39552,7 +39552,7 @@
         </is>
       </c>
       <c r="M641" s="2" t="n">
-        <v>10730.39</v>
+        <v>10667.16</v>
       </c>
     </row>
     <row r="642">
@@ -39613,7 +39613,7 @@
         </is>
       </c>
       <c r="M642" s="2" t="n">
-        <v>5028.61</v>
+        <v>4998.97</v>
       </c>
     </row>
     <row r="643">
@@ -39674,7 +39674,7 @@
         </is>
       </c>
       <c r="M643" s="2" t="n">
-        <v>3364.92</v>
+        <v>3345.09</v>
       </c>
     </row>
     <row r="644">
@@ -39735,7 +39735,7 @@
         </is>
       </c>
       <c r="M644" s="2" t="n">
-        <v>3025.82</v>
+        <v>3007.99</v>
       </c>
     </row>
     <row r="645">
@@ -39796,7 +39796,7 @@
         </is>
       </c>
       <c r="M645" s="2" t="n">
-        <v>226.26</v>
+        <v>224.93</v>
       </c>
     </row>
     <row r="646">
@@ -39857,7 +39857,7 @@
         </is>
       </c>
       <c r="M646" s="2" t="n">
-        <v>283.27</v>
+        <v>281.6</v>
       </c>
     </row>
     <row r="647">
@@ -39918,7 +39918,7 @@
         </is>
       </c>
       <c r="M647" s="2" t="n">
-        <v>820</v>
+        <v>815.17</v>
       </c>
     </row>
     <row r="648">
@@ -39979,7 +39979,7 @@
         </is>
       </c>
       <c r="M648" s="2" t="n">
-        <v>1330.06</v>
+        <v>1322.23</v>
       </c>
     </row>
     <row r="649">
@@ -40040,7 +40040,7 @@
         </is>
       </c>
       <c r="M649" s="2" t="n">
-        <v>2824.51</v>
+        <v>2807.87</v>
       </c>
     </row>
     <row r="650">
@@ -40101,7 +40101,7 @@
         </is>
       </c>
       <c r="M650" s="2" t="n">
-        <v>328.55</v>
+        <v>326.62</v>
       </c>
     </row>
     <row r="651">
@@ -40162,7 +40162,7 @@
         </is>
       </c>
       <c r="M651" s="2" t="n">
-        <v>193.44</v>
+        <v>192.3</v>
       </c>
     </row>
     <row r="652">
@@ -40223,7 +40223,7 @@
         </is>
       </c>
       <c r="M652" s="2" t="n">
-        <v>1635.87</v>
+        <v>1626.23</v>
       </c>
     </row>
     <row r="653">
@@ -40284,7 +40284,7 @@
         </is>
       </c>
       <c r="M653" s="2" t="n">
-        <v>193.44</v>
+        <v>192.3</v>
       </c>
     </row>
     <row r="654">
@@ -40345,7 +40345,7 @@
         </is>
       </c>
       <c r="M654" s="2" t="n">
-        <v>193.44</v>
+        <v>192.3</v>
       </c>
     </row>
     <row r="655">
@@ -40406,7 +40406,7 @@
         </is>
       </c>
       <c r="M655" s="2" t="n">
-        <v>193.44</v>
+        <v>192.3</v>
       </c>
     </row>
     <row r="656">
@@ -40467,7 +40467,7 @@
         </is>
       </c>
       <c r="M656" s="2" t="n">
-        <v>193.44</v>
+        <v>192.3</v>
       </c>
     </row>
     <row r="657">
@@ -40528,7 +40528,7 @@
         </is>
       </c>
       <c r="M657" s="2" t="n">
-        <v>130.3</v>
+        <v>129.53</v>
       </c>
     </row>
     <row r="658">
@@ -40589,7 +40589,7 @@
         </is>
       </c>
       <c r="M658" s="2" t="n">
-        <v>208.99</v>
+        <v>207.75</v>
       </c>
     </row>
     <row r="659">
@@ -40650,7 +40650,7 @@
         </is>
       </c>
       <c r="M659" s="2" t="n">
-        <v>465.36</v>
+        <v>462.61</v>
       </c>
     </row>
     <row r="660">
@@ -40711,7 +40711,7 @@
         </is>
       </c>
       <c r="M660" s="2" t="n">
-        <v>5225.48</v>
+        <v>5194.69</v>
       </c>
     </row>
     <row r="661">
@@ -40772,7 +40772,7 @@
         </is>
       </c>
       <c r="M661" s="2" t="n">
-        <v>576.16</v>
+        <v>572.76</v>
       </c>
     </row>
     <row r="662">
@@ -40833,7 +40833,7 @@
         </is>
       </c>
       <c r="M662" s="2" t="n">
-        <v>113.68</v>
+        <v>113.01</v>
       </c>
     </row>
     <row r="663">
@@ -40894,7 +40894,7 @@
         </is>
       </c>
       <c r="M663" s="2" t="n">
-        <v>266.43</v>
+        <v>264.86</v>
       </c>
     </row>
     <row r="664">
@@ -40955,7 +40955,7 @@
         </is>
       </c>
       <c r="M664" s="2" t="n">
-        <v>1192.08</v>
+        <v>1185.06</v>
       </c>
     </row>
     <row r="665">
@@ -41016,7 +41016,7 @@
         </is>
       </c>
       <c r="M665" s="2" t="n">
-        <v>2077.34</v>
+        <v>2065.1</v>
       </c>
     </row>
     <row r="666">
@@ -41077,7 +41077,7 @@
         </is>
       </c>
       <c r="M666" s="2" t="n">
-        <v>164.55</v>
+        <v>163.58</v>
       </c>
     </row>
     <row r="667">
@@ -41138,7 +41138,7 @@
         </is>
       </c>
       <c r="M667" s="2" t="n">
-        <v>445.62</v>
+        <v>442.99</v>
       </c>
     </row>
     <row r="668">
@@ -41199,7 +41199,7 @@
         </is>
       </c>
       <c r="M668" s="2" t="n">
-        <v>1385.87</v>
+        <v>1377.45</v>
       </c>
     </row>
     <row r="669">
@@ -41260,7 +41260,7 @@
         </is>
       </c>
       <c r="M669" s="2" t="n">
-        <v>2832.74</v>
+        <v>2815.53</v>
       </c>
     </row>
     <row r="670">
@@ -41321,7 +41321,7 @@
         </is>
       </c>
       <c r="M670" s="2" t="n">
-        <v>18260.34</v>
+        <v>18149.38</v>
       </c>
     </row>
     <row r="671">
@@ -41382,7 +41382,7 @@
         </is>
       </c>
       <c r="M671" s="2" t="n">
-        <v>262.96</v>
+        <v>261.37</v>
       </c>
     </row>
     <row r="672">
@@ -41443,7 +41443,7 @@
         </is>
       </c>
       <c r="M672" s="2" t="n">
-        <v>159.86</v>
+        <v>158.89</v>
       </c>
     </row>
     <row r="673">
@@ -41504,7 +41504,7 @@
         </is>
       </c>
       <c r="M673" s="2" t="n">
-        <v>453.84</v>
+        <v>451.08</v>
       </c>
     </row>
     <row r="674">
@@ -41565,7 +41565,7 @@
         </is>
       </c>
       <c r="M674" s="2" t="n">
-        <v>128.38</v>
+        <v>127.6</v>
       </c>
     </row>
     <row r="675">
@@ -41626,7 +41626,7 @@
         </is>
       </c>
       <c r="M675" s="2" t="n">
-        <v>126.31</v>
+        <v>125.55</v>
       </c>
     </row>
     <row r="676">
@@ -41687,7 +41687,7 @@
         </is>
       </c>
       <c r="M676" s="2" t="n">
-        <v>130.87</v>
+        <v>130.07</v>
       </c>
     </row>
     <row r="677">
@@ -41748,7 +41748,7 @@
         </is>
       </c>
       <c r="M677" s="2" t="n">
-        <v>133.22</v>
+        <v>132.41</v>
       </c>
     </row>
     <row r="678">
@@ -41809,7 +41809,7 @@
         </is>
       </c>
       <c r="M678" s="2" t="n">
-        <v>148.63</v>
+        <v>147.73</v>
       </c>
     </row>
     <row r="679">
@@ -41870,7 +41870,7 @@
         </is>
       </c>
       <c r="M679" s="2" t="n">
-        <v>1906.59</v>
+        <v>1895.01</v>
       </c>
     </row>
     <row r="680">
@@ -41931,7 +41931,7 @@
         </is>
       </c>
       <c r="M680" s="2" t="n">
-        <v>403.72</v>
+        <v>401.27</v>
       </c>
     </row>
     <row r="681">
@@ -41992,7 +41992,7 @@
         </is>
       </c>
       <c r="M681" s="2" t="n">
-        <v>12763.35</v>
+        <v>12685.8</v>
       </c>
     </row>
     <row r="682">
@@ -42053,7 +42053,7 @@
         </is>
       </c>
       <c r="M682" s="2" t="n">
-        <v>443.4</v>
+        <v>440.7</v>
       </c>
     </row>
     <row r="683">
@@ -42114,7 +42114,7 @@
         </is>
       </c>
       <c r="M683" s="2" t="n">
-        <v>1437.91</v>
+        <v>1429.17</v>
       </c>
     </row>
     <row r="684">
@@ -42175,7 +42175,7 @@
         </is>
       </c>
       <c r="M684" s="2" t="n">
-        <v>2574.48</v>
+        <v>2558.84</v>
       </c>
     </row>
     <row r="685">
@@ -42236,7 +42236,7 @@
         </is>
       </c>
       <c r="M685" s="2" t="n">
-        <v>8835.950000000001</v>
+        <v>8782.25</v>
       </c>
     </row>
     <row r="686">
@@ -42297,7 +42297,7 @@
         </is>
       </c>
       <c r="M686" s="2" t="n">
-        <v>1503.34</v>
+        <v>1494.21</v>
       </c>
     </row>
     <row r="687">
@@ -42358,7 +42358,7 @@
         </is>
       </c>
       <c r="M687" s="2" t="n">
-        <v>1188.59</v>
+        <v>1181.37</v>
       </c>
     </row>
     <row r="688">
@@ -42419,7 +42419,7 @@
         </is>
       </c>
       <c r="M688" s="2" t="n">
-        <v>260.22</v>
+        <v>258.64</v>
       </c>
     </row>
     <row r="689">
@@ -42480,7 +42480,7 @@
         </is>
       </c>
       <c r="M689" s="2" t="n">
-        <v>1027.9</v>
+        <v>1021.66</v>
       </c>
     </row>
     <row r="690">
@@ -42541,7 +42541,7 @@
         </is>
       </c>
       <c r="M690" s="2" t="n">
-        <v>4234.2</v>
+        <v>4208.47</v>
       </c>
     </row>
     <row r="691">
@@ -42602,7 +42602,7 @@
         </is>
       </c>
       <c r="M691" s="2" t="n">
-        <v>128.38</v>
+        <v>127.6</v>
       </c>
     </row>
     <row r="692">
@@ -42663,7 +42663,7 @@
         </is>
       </c>
       <c r="M692" s="2" t="n">
-        <v>274.44</v>
+        <v>272.77</v>
       </c>
     </row>
     <row r="693">
@@ -42724,7 +42724,7 @@
         </is>
       </c>
       <c r="M693" s="2" t="n">
-        <v>472.12</v>
+        <v>469.25</v>
       </c>
     </row>
     <row r="694">
@@ -42785,7 +42785,7 @@
         </is>
       </c>
       <c r="M694" s="2" t="n">
-        <v>3716.8</v>
+        <v>3694.22</v>
       </c>
     </row>
     <row r="695">
@@ -42846,7 +42846,7 @@
         </is>
       </c>
       <c r="M695" s="2" t="n">
-        <v>784.11</v>
+        <v>779.35</v>
       </c>
     </row>
     <row r="696">
@@ -42907,7 +42907,7 @@
         </is>
       </c>
       <c r="M696" s="2" t="n">
-        <v>196.03</v>
+        <v>194.84</v>
       </c>
     </row>
     <row r="697">
@@ -42968,7 +42968,7 @@
         </is>
       </c>
       <c r="M697" s="2" t="n">
-        <v>3043.95</v>
+        <v>3025.46</v>
       </c>
     </row>
     <row r="698">
@@ -43029,7 +43029,7 @@
         </is>
       </c>
       <c r="M698" s="2" t="n">
-        <v>922.3</v>
+        <v>916.6900000000001</v>
       </c>
     </row>
     <row r="699">
@@ -43090,7 +43090,7 @@
         </is>
       </c>
       <c r="M699" s="2" t="n">
-        <v>806.2</v>
+        <v>801.3</v>
       </c>
     </row>
     <row r="700">
@@ -43151,7 +43151,7 @@
         </is>
       </c>
       <c r="M700" s="2" t="n">
-        <v>2021.02</v>
+        <v>2008.74</v>
       </c>
     </row>
     <row r="701">
@@ -43212,7 +43212,7 @@
         </is>
       </c>
       <c r="M701" s="2" t="n">
-        <v>140.39</v>
+        <v>139.54</v>
       </c>
     </row>
     <row r="702">
@@ -43273,7 +43273,7 @@
         </is>
       </c>
       <c r="M702" s="2" t="n">
-        <v>3535.09</v>
+        <v>3513.61</v>
       </c>
     </row>
     <row r="703">
@@ -43334,7 +43334,7 @@
         </is>
       </c>
       <c r="M703" s="2" t="n">
-        <v>259.34</v>
+        <v>258.34</v>
       </c>
     </row>
     <row r="704">
@@ -43395,7 +43395,7 @@
         </is>
       </c>
       <c r="M704" s="2" t="n">
-        <v>1568.22</v>
+        <v>1562.17</v>
       </c>
     </row>
     <row r="705">
@@ -43456,7 +43456,7 @@
         </is>
       </c>
       <c r="M705" s="2" t="n">
-        <v>468.35</v>
+        <v>466.55</v>
       </c>
     </row>
     <row r="706">
@@ -43517,7 +43517,7 @@
         </is>
       </c>
       <c r="M706" s="2" t="n">
-        <v>11980.84</v>
+        <v>11934.6</v>
       </c>
     </row>
     <row r="707">
@@ -43578,7 +43578,7 @@
         </is>
       </c>
       <c r="M707" s="2" t="n">
-        <v>2415.23</v>
+        <v>2405.91</v>
       </c>
     </row>
     <row r="708">
@@ -43639,7 +43639,7 @@
         </is>
       </c>
       <c r="M708" s="2" t="n">
-        <v>461.08</v>
+        <v>459.3</v>
       </c>
     </row>
     <row r="709">
@@ -43700,7 +43700,7 @@
         </is>
       </c>
       <c r="M709" s="2" t="n">
-        <v>427.14</v>
+        <v>425.49</v>
       </c>
     </row>
     <row r="710">
@@ -43761,7 +43761,7 @@
         </is>
       </c>
       <c r="M710" s="2" t="n">
-        <v>1894.71</v>
+        <v>1887.39</v>
       </c>
     </row>
     <row r="711">
@@ -43822,7 +43822,7 @@
         </is>
       </c>
       <c r="M711" s="2" t="n">
-        <v>1107.83</v>
+        <v>1103.56</v>
       </c>
     </row>
     <row r="712">
@@ -43883,7 +43883,7 @@
         </is>
       </c>
       <c r="M712" s="2" t="n">
-        <v>114.66</v>
+        <v>114.21</v>
       </c>
     </row>
     <row r="713">
@@ -43944,7 +43944,7 @@
         </is>
       </c>
       <c r="M713" s="2" t="n">
-        <v>1298.13</v>
+        <v>1293.12</v>
       </c>
     </row>
     <row r="714">
@@ -44005,7 +44005,7 @@
         </is>
       </c>
       <c r="M714" s="2" t="n">
-        <v>467.98</v>
+        <v>466.18</v>
       </c>
     </row>
     <row r="715">
@@ -44066,7 +44066,7 @@
         </is>
       </c>
       <c r="M715" s="2" t="n">
-        <v>594.3</v>
+        <v>592</v>
       </c>
     </row>
     <row r="716">
@@ -44127,7 +44127,7 @@
         </is>
       </c>
       <c r="M716" s="2" t="n">
-        <v>11586.21</v>
+        <v>11541.49</v>
       </c>
     </row>
     <row r="717">
@@ -44188,7 +44188,7 @@
         </is>
       </c>
       <c r="M717" s="2" t="n">
-        <v>897.3099999999999</v>
+        <v>893.85</v>
       </c>
     </row>
     <row r="718">
@@ -44249,7 +44249,7 @@
         </is>
       </c>
       <c r="M718" s="2" t="n">
-        <v>516.02</v>
+        <v>514.03</v>
       </c>
     </row>
     <row r="719">
@@ -44310,7 +44310,7 @@
         </is>
       </c>
       <c r="M719" s="2" t="n">
-        <v>36069.28</v>
+        <v>35930.07</v>
       </c>
     </row>
     <row r="720">
@@ -44371,7 +44371,7 @@
         </is>
       </c>
       <c r="M720" s="2" t="n">
-        <v>3731.42</v>
+        <v>3717.02</v>
       </c>
     </row>
     <row r="721">
@@ -44432,7 +44432,7 @@
         </is>
       </c>
       <c r="M721" s="2" t="n">
-        <v>66.91</v>
+        <v>66.65000000000001</v>
       </c>
     </row>
     <row r="722">
@@ -44493,7 +44493,7 @@
         </is>
       </c>
       <c r="M722" s="2" t="n">
-        <v>277.48</v>
+        <v>276.41</v>
       </c>
     </row>
     <row r="723">
@@ -44554,7 +44554,7 @@
         </is>
       </c>
       <c r="M723" s="2" t="n">
-        <v>356.58</v>
+        <v>355.2</v>
       </c>
     </row>
     <row r="724">
@@ -44615,7 +44615,7 @@
         </is>
       </c>
       <c r="M724" s="2" t="n">
-        <v>491.45</v>
+        <v>489.55</v>
       </c>
     </row>
     <row r="725">
@@ -44676,7 +44676,7 @@
         </is>
       </c>
       <c r="M725" s="2" t="n">
-        <v>12626.17</v>
+        <v>12577.43</v>
       </c>
     </row>
     <row r="726">
@@ -44737,7 +44737,7 @@
         </is>
       </c>
       <c r="M726" s="2" t="n">
-        <v>227.4</v>
+        <v>226.53</v>
       </c>
     </row>
     <row r="727">
@@ -44798,7 +44798,7 @@
         </is>
       </c>
       <c r="M727" s="2" t="n">
-        <v>27841.75</v>
+        <v>27734.29</v>
       </c>
     </row>
     <row r="728">
@@ -44859,7 +44859,7 @@
         </is>
       </c>
       <c r="M728" s="2" t="n">
-        <v>224.47</v>
+        <v>223.6</v>
       </c>
     </row>
     <row r="729">
@@ -44920,7 +44920,7 @@
         </is>
       </c>
       <c r="M729" s="2" t="n">
-        <v>2136.99</v>
+        <v>2128.74</v>
       </c>
     </row>
     <row r="730">
@@ -44981,7 +44981,7 @@
         </is>
       </c>
       <c r="M730" s="2" t="n">
-        <v>531.21</v>
+        <v>529.16</v>
       </c>
     </row>
     <row r="731">
@@ -45042,7 +45042,7 @@
         </is>
       </c>
       <c r="M731" s="2" t="n">
-        <v>50.53</v>
+        <v>50.33</v>
       </c>
     </row>
     <row r="732">
@@ -45103,7 +45103,7 @@
         </is>
       </c>
       <c r="M732" s="2" t="n">
-        <v>421.05</v>
+        <v>419.42</v>
       </c>
     </row>
     <row r="733">
@@ -45164,7 +45164,7 @@
         </is>
       </c>
       <c r="M733" s="2" t="n">
-        <v>1344.89</v>
+        <v>1339.7</v>
       </c>
     </row>
     <row r="734">
@@ -45225,7 +45225,7 @@
         </is>
       </c>
       <c r="M734" s="2" t="n">
-        <v>604.61</v>
+        <v>602.27</v>
       </c>
     </row>
     <row r="735">
@@ -45286,7 +45286,7 @@
         </is>
       </c>
       <c r="M735" s="2" t="n">
-        <v>42.38</v>
+        <v>42.22</v>
       </c>
     </row>
     <row r="736">
@@ -45347,7 +45347,7 @@
         </is>
       </c>
       <c r="M736" s="2" t="n">
-        <v>233.59</v>
+        <v>232.69</v>
       </c>
     </row>
     <row r="737">
@@ -45408,7 +45408,7 @@
         </is>
       </c>
       <c r="M737" s="2" t="n">
-        <v>292.8</v>
+        <v>291.67</v>
       </c>
     </row>
     <row r="738">
@@ -45469,7 +45469,7 @@
         </is>
       </c>
       <c r="M738" s="2" t="n">
-        <v>2180.05</v>
+        <v>2171.64</v>
       </c>
     </row>
     <row r="739">
@@ -45530,7 +45530,7 @@
         </is>
       </c>
       <c r="M739" s="2" t="n">
-        <v>37495.78</v>
+        <v>37351.06</v>
       </c>
     </row>
     <row r="740">
@@ -45591,7 +45591,7 @@
         </is>
       </c>
       <c r="M740" s="2" t="n">
-        <v>3479.85</v>
+        <v>3466.42</v>
       </c>
     </row>
     <row r="741">
@@ -45652,7 +45652,7 @@
         </is>
       </c>
       <c r="M741" s="2" t="n">
-        <v>102.16</v>
+        <v>101.76</v>
       </c>
     </row>
     <row r="742">
@@ -45713,7 +45713,7 @@
         </is>
       </c>
       <c r="M742" s="2" t="n">
-        <v>234.68</v>
+        <v>233.78</v>
       </c>
     </row>
     <row r="743">
@@ -45774,7 +45774,7 @@
         </is>
       </c>
       <c r="M743" s="2" t="n">
-        <v>1652.03</v>
+        <v>1645.65</v>
       </c>
     </row>
     <row r="744">
@@ -45835,7 +45835,7 @@
         </is>
       </c>
       <c r="M744" s="2" t="n">
-        <v>8917.889999999999</v>
+        <v>8883.469999999999</v>
       </c>
     </row>
     <row r="745">
@@ -45896,7 +45896,7 @@
         </is>
       </c>
       <c r="M745" s="2" t="n">
-        <v>448.66</v>
+        <v>446.92</v>
       </c>
     </row>
     <row r="746">
@@ -45957,7 +45957,7 @@
         </is>
       </c>
       <c r="M746" s="2" t="n">
-        <v>142.63</v>
+        <v>142.08</v>
       </c>
     </row>
     <row r="747">
@@ -46018,7 +46018,7 @@
         </is>
       </c>
       <c r="M747" s="2" t="n">
-        <v>408.76</v>
+        <v>407.18</v>
       </c>
     </row>
     <row r="748">
@@ -46079,7 +46079,7 @@
         </is>
       </c>
       <c r="M748" s="2" t="n">
-        <v>158.96</v>
+        <v>158.35</v>
       </c>
     </row>
     <row r="749">
@@ -46140,7 +46140,7 @@
         </is>
       </c>
       <c r="M749" s="2" t="n">
-        <v>275.66</v>
+        <v>274.6</v>
       </c>
     </row>
     <row r="750">
@@ -46201,7 +46201,7 @@
         </is>
       </c>
       <c r="M750" s="2" t="n">
-        <v>1870.55</v>
+        <v>1863.33</v>
       </c>
     </row>
     <row r="751">
@@ -46262,7 +46262,7 @@
         </is>
       </c>
       <c r="M751" s="2" t="n">
-        <v>3986.17</v>
+        <v>3970.79</v>
       </c>
     </row>
     <row r="752">
@@ -46323,7 +46323,7 @@
         </is>
       </c>
       <c r="M752" s="2" t="n">
-        <v>411.38</v>
+        <v>409.79</v>
       </c>
     </row>
     <row r="753">
@@ -46384,7 +46384,7 @@
         </is>
       </c>
       <c r="M753" s="2" t="n">
-        <v>259.38</v>
+        <v>258.38</v>
       </c>
     </row>
     <row r="754">
@@ -46445,7 +46445,7 @@
         </is>
       </c>
       <c r="M754" s="2" t="n">
-        <v>1220.34</v>
+        <v>1215.63</v>
       </c>
     </row>
     <row r="755">
@@ -46506,7 +46506,7 @@
         </is>
       </c>
       <c r="M755" s="2" t="n">
-        <v>348.2</v>
+        <v>346.86</v>
       </c>
     </row>
     <row r="756">
@@ -46567,7 +46567,7 @@
         </is>
       </c>
       <c r="M756" s="2" t="n">
-        <v>475.44</v>
+        <v>473.6</v>
       </c>
     </row>
     <row r="757">
@@ -46628,7 +46628,7 @@
         </is>
       </c>
       <c r="M757" s="2" t="n">
-        <v>69.37</v>
+        <v>69.09999999999999</v>
       </c>
     </row>
     <row r="758">
@@ -46689,7 +46689,7 @@
         </is>
       </c>
       <c r="M758" s="2" t="n">
-        <v>982.9</v>
+        <v>987.99</v>
       </c>
     </row>
     <row r="759">
@@ -46750,7 +46750,7 @@
         </is>
       </c>
       <c r="M759" s="2" t="n">
-        <v>296.53</v>
+        <v>298.06</v>
       </c>
     </row>
     <row r="760">
@@ -46811,7 +46811,7 @@
         </is>
       </c>
       <c r="M760" s="2" t="n">
-        <v>80736.96000000001</v>
+        <v>81154.97</v>
       </c>
     </row>
     <row r="761">
@@ -46872,7 +46872,7 @@
         </is>
       </c>
       <c r="M761" s="2" t="n">
-        <v>463.84</v>
+        <v>466.24</v>
       </c>
     </row>
     <row r="762">
@@ -46933,7 +46933,7 @@
         </is>
       </c>
       <c r="M762" s="2" t="n">
-        <v>737.73</v>
+        <v>741.55</v>
       </c>
     </row>
     <row r="763">
@@ -46994,7 +46994,7 @@
         </is>
       </c>
       <c r="M763" s="2" t="n">
-        <v>294.87</v>
+        <v>296.4</v>
       </c>
     </row>
     <row r="764">
@@ -47055,7 +47055,7 @@
         </is>
       </c>
       <c r="M764" s="2" t="n">
-        <v>4485.52</v>
+        <v>4508.75</v>
       </c>
     </row>
     <row r="765">
@@ -47116,7 +47116,7 @@
         </is>
       </c>
       <c r="M765" s="2" t="n">
-        <v>1525.43</v>
+        <v>1533.33</v>
       </c>
     </row>
     <row r="766">
@@ -47177,7 +47177,7 @@
         </is>
       </c>
       <c r="M766" s="2" t="n">
-        <v>374.11</v>
+        <v>376.05</v>
       </c>
     </row>
     <row r="767">
@@ -47238,7 +47238,7 @@
         </is>
       </c>
       <c r="M767" s="2" t="n">
-        <v>120.93</v>
+        <v>121.56</v>
       </c>
     </row>
     <row r="768">
@@ -47299,7 +47299,7 @@
         </is>
       </c>
       <c r="M768" s="2" t="n">
-        <v>1744.65</v>
+        <v>1753.68</v>
       </c>
     </row>
     <row r="769">
@@ -47360,7 +47360,7 @@
         </is>
       </c>
       <c r="M769" s="2" t="n">
-        <v>2497.91</v>
+        <v>2510.84</v>
       </c>
     </row>
     <row r="770">
@@ -47421,7 +47421,7 @@
         </is>
       </c>
       <c r="M770" s="2" t="n">
-        <v>6379.47</v>
+        <v>6412.5</v>
       </c>
     </row>
     <row r="771">
@@ -47482,7 +47482,7 @@
         </is>
       </c>
       <c r="M771" s="2" t="n">
-        <v>5788.07</v>
+        <v>5818.04</v>
       </c>
     </row>
     <row r="772">
@@ -47543,7 +47543,7 @@
         </is>
       </c>
       <c r="M772" s="2" t="n">
-        <v>239.79</v>
+        <v>241.03</v>
       </c>
     </row>
     <row r="773">
@@ -47604,7 +47604,7 @@
         </is>
       </c>
       <c r="M773" s="2" t="n">
-        <v>1104.38</v>
+        <v>1110.1</v>
       </c>
     </row>
     <row r="774">
@@ -47665,7 +47665,7 @@
         </is>
       </c>
       <c r="M774" s="2" t="n">
-        <v>160</v>
+        <v>160.83</v>
       </c>
     </row>
     <row r="775">
@@ -47726,7 +47726,7 @@
         </is>
       </c>
       <c r="M775" s="2" t="n">
-        <v>2880.37</v>
+        <v>2895.28</v>
       </c>
     </row>
     <row r="776">
@@ -47787,7 +47787,7 @@
         </is>
       </c>
       <c r="M776" s="2" t="n">
-        <v>491.45</v>
+        <v>493.99</v>
       </c>
     </row>
     <row r="777">
@@ -47848,7 +47848,7 @@
         </is>
       </c>
       <c r="M777" s="2" t="n">
-        <v>963.5700000000001</v>
+        <v>968.5599999999999</v>
       </c>
     </row>
     <row r="778">
@@ -47909,7 +47909,7 @@
         </is>
       </c>
       <c r="M778" s="2" t="n">
-        <v>248.25</v>
+        <v>249.54</v>
       </c>
     </row>
     <row r="779">
@@ -47970,7 +47970,7 @@
         </is>
       </c>
       <c r="M779" s="2" t="n">
-        <v>2658.8</v>
+        <v>2672.57</v>
       </c>
     </row>
     <row r="780">
@@ -48031,7 +48031,7 @@
         </is>
       </c>
       <c r="M780" s="2" t="n">
-        <v>535.0700000000001</v>
+        <v>537.84</v>
       </c>
     </row>
     <row r="781">
@@ -48092,7 +48092,7 @@
         </is>
       </c>
       <c r="M781" s="2" t="n">
-        <v>949.77</v>
+        <v>954.6900000000001</v>
       </c>
     </row>
     <row r="782">
@@ -48153,7 +48153,7 @@
         </is>
       </c>
       <c r="M782" s="2" t="n">
-        <v>836.5700000000001</v>
+        <v>840.9</v>
       </c>
     </row>
     <row r="783">
@@ -48214,7 +48214,7 @@
         </is>
       </c>
       <c r="M783" s="2" t="n">
-        <v>1347.02</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="784">
@@ -48275,7 +48275,7 @@
         </is>
       </c>
       <c r="M784" s="2" t="n">
-        <v>1254.85</v>
+        <v>1261.35</v>
       </c>
     </row>
     <row r="785">
@@ -48336,7 +48336,7 @@
         </is>
       </c>
       <c r="M785" s="2" t="n">
-        <v>519.89</v>
+        <v>522.58</v>
       </c>
     </row>
     <row r="786">
@@ -48397,7 +48397,7 @@
         </is>
       </c>
       <c r="M786" s="2" t="n">
-        <v>629.39</v>
+        <v>632.65</v>
       </c>
     </row>
     <row r="787">
@@ -48458,7 +48458,7 @@
         </is>
       </c>
       <c r="M787" s="2" t="n">
-        <v>842.09</v>
+        <v>846.45</v>
       </c>
     </row>
     <row r="788">
@@ -48519,7 +48519,7 @@
         </is>
       </c>
       <c r="M788" s="2" t="n">
-        <v>891.79</v>
+        <v>896.41</v>
       </c>
     </row>
     <row r="789">
@@ -48580,7 +48580,7 @@
         </is>
       </c>
       <c r="M789" s="2" t="n">
-        <v>19616</v>
+        <v>19717.56</v>
       </c>
     </row>
     <row r="790">
@@ -48641,7 +48641,7 @@
         </is>
       </c>
       <c r="M790" s="2" t="n">
-        <v>9937.18</v>
+        <v>9988.629999999999</v>
       </c>
     </row>
     <row r="791">
@@ -48702,7 +48702,7 @@
         </is>
       </c>
       <c r="M791" s="2" t="n">
-        <v>344.02</v>
+        <v>345.8</v>
       </c>
     </row>
     <row r="792">
@@ -48763,7 +48763,7 @@
         </is>
       </c>
       <c r="M792" s="2" t="n">
-        <v>897.3099999999999</v>
+        <v>901.96</v>
       </c>
     </row>
     <row r="793">
@@ -48824,7 +48824,7 @@
         </is>
       </c>
       <c r="M793" s="2" t="n">
-        <v>695.76</v>
+        <v>699.36</v>
       </c>
     </row>
     <row r="794">
@@ -48885,7 +48885,7 @@
         </is>
       </c>
       <c r="M794" s="2" t="n">
-        <v>6029.58</v>
+        <v>6060.79</v>
       </c>
     </row>
     <row r="795">
@@ -48946,7 +48946,7 @@
         </is>
       </c>
       <c r="M795" s="2" t="n">
-        <v>328</v>
+        <v>329.7</v>
       </c>
     </row>
     <row r="796">
@@ -49007,7 +49007,7 @@
         </is>
       </c>
       <c r="M796" s="2" t="n">
-        <v>423.63</v>
+        <v>425.82</v>
       </c>
     </row>
     <row r="797">
@@ -49068,7 +49068,7 @@
         </is>
       </c>
       <c r="M797" s="2" t="n">
-        <v>34951.12</v>
+        <v>35132.07</v>
       </c>
     </row>
     <row r="798">
@@ -49129,7 +49129,7 @@
         </is>
       </c>
       <c r="M798" s="2" t="n">
-        <v>384.21</v>
+        <v>384.58</v>
       </c>
     </row>
     <row r="799">
@@ -49190,7 +49190,7 @@
         </is>
       </c>
       <c r="M799" s="2" t="n">
-        <v>17085.35</v>
+        <v>17101.82</v>
       </c>
     </row>
     <row r="800">
@@ -49251,7 +49251,7 @@
         </is>
       </c>
       <c r="M800" s="2" t="n">
-        <v>4093.45</v>
+        <v>4097.39</v>
       </c>
     </row>
     <row r="801">
@@ -49312,7 +49312,7 @@
         </is>
       </c>
       <c r="M801" s="2" t="n">
-        <v>82</v>
+        <v>82.08</v>
       </c>
     </row>
     <row r="802">
@@ -49373,7 +49373,7 @@
         </is>
       </c>
       <c r="M802" s="2" t="n">
-        <v>1395.66</v>
+        <v>1397.01</v>
       </c>
     </row>
     <row r="803">
@@ -49434,7 +49434,7 @@
         </is>
       </c>
       <c r="M803" s="2" t="n">
-        <v>372.18</v>
+        <v>372.54</v>
       </c>
     </row>
     <row r="804">
@@ -49495,7 +49495,7 @@
         </is>
       </c>
       <c r="M804" s="2" t="n">
-        <v>9215.940000000001</v>
+        <v>9224.82</v>
       </c>
     </row>
     <row r="805">
@@ -49556,7 +49556,7 @@
         </is>
       </c>
       <c r="M805" s="2" t="n">
-        <v>854.79</v>
+        <v>855.62</v>
       </c>
     </row>
     <row r="806">
@@ -49617,7 +49617,7 @@
         </is>
       </c>
       <c r="M806" s="2" t="n">
-        <v>231.92</v>
+        <v>232.14</v>
       </c>
     </row>
     <row r="807">
@@ -49678,7 +49678,7 @@
         </is>
       </c>
       <c r="M807" s="2" t="n">
-        <v>354.84</v>
+        <v>355.18</v>
       </c>
     </row>
     <row r="808">
@@ -49739,7 +49739,7 @@
         </is>
       </c>
       <c r="M808" s="2" t="n">
-        <v>2628.43</v>
+        <v>2630.96</v>
       </c>
     </row>
     <row r="809">
@@ -49800,7 +49800,7 @@
         </is>
       </c>
       <c r="M809" s="2" t="n">
-        <v>1122.98</v>
+        <v>1124.07</v>
       </c>
     </row>
     <row r="810">
@@ -49861,7 +49861,7 @@
         </is>
       </c>
       <c r="M810" s="2" t="n">
-        <v>82.61</v>
+        <v>82.69</v>
       </c>
     </row>
     <row r="811">
@@ -49922,7 +49922,7 @@
         </is>
       </c>
       <c r="M811" s="2" t="n">
-        <v>168.97</v>
+        <v>169.13</v>
       </c>
     </row>
     <row r="812">
@@ -49983,7 +49983,7 @@
         </is>
       </c>
       <c r="M812" s="2" t="n">
-        <v>101.6</v>
+        <v>101.7</v>
       </c>
     </row>
     <row r="813">
@@ -50044,7 +50044,7 @@
         </is>
       </c>
       <c r="M813" s="2" t="n">
-        <v>470.74</v>
+        <v>471.2</v>
       </c>
     </row>
     <row r="814">
@@ -50105,7 +50105,7 @@
         </is>
       </c>
       <c r="M814" s="2" t="n">
-        <v>1213.44</v>
+        <v>1214.61</v>
       </c>
     </row>
     <row r="815">
@@ -50166,7 +50166,7 @@
         </is>
       </c>
       <c r="M815" s="2" t="n">
-        <v>463.84</v>
+        <v>464.29</v>
       </c>
     </row>
     <row r="816">
@@ -50227,7 +50227,7 @@
         </is>
       </c>
       <c r="M816" s="2" t="n">
-        <v>495.32</v>
+        <v>495.79</v>
       </c>
     </row>
     <row r="817">
@@ -50288,7 +50288,7 @@
         </is>
       </c>
       <c r="M817" s="2" t="n">
-        <v>5755.41</v>
+        <v>5760.95</v>
       </c>
     </row>
     <row r="818">
@@ -50349,7 +50349,7 @@
         </is>
       </c>
       <c r="M818" s="2" t="n">
-        <v>1087.82</v>
+        <v>1088.87</v>
       </c>
     </row>
     <row r="819">
@@ -50410,7 +50410,7 @@
         </is>
       </c>
       <c r="M819" s="2" t="n">
-        <v>279.13</v>
+        <v>279.4</v>
       </c>
     </row>
     <row r="820">
@@ -50471,7 +50471,7 @@
         </is>
       </c>
       <c r="M820" s="2" t="n">
-        <v>1740.07</v>
+        <v>1741.75</v>
       </c>
     </row>
     <row r="821">
@@ -50532,7 +50532,7 @@
         </is>
       </c>
       <c r="M821" s="2" t="n">
-        <v>93.87</v>
+        <v>93.95999999999999</v>
       </c>
     </row>
     <row r="822">
@@ -50593,7 +50593,7 @@
         </is>
       </c>
       <c r="M822" s="2" t="n">
-        <v>479.85</v>
+        <v>480.32</v>
       </c>
     </row>
     <row r="823">
@@ -50654,7 +50654,7 @@
         </is>
       </c>
       <c r="M823" s="2" t="n">
-        <v>6145.79</v>
+        <v>6151.71</v>
       </c>
     </row>
     <row r="824">
@@ -50715,7 +50715,7 @@
         </is>
       </c>
       <c r="M824" s="2" t="n">
-        <v>495.32</v>
+        <v>495.79</v>
       </c>
     </row>
     <row r="825">
@@ -50776,7 +50776,7 @@
         </is>
       </c>
       <c r="M825" s="2" t="n">
-        <v>292.33</v>
+        <v>292.61</v>
       </c>
     </row>
     <row r="826">
@@ -50837,7 +50837,7 @@
         </is>
       </c>
       <c r="M826" s="2" t="n">
-        <v>856.84</v>
+        <v>857.66</v>
       </c>
     </row>
     <row r="827">
@@ -50898,7 +50898,7 @@
         </is>
       </c>
       <c r="M827" s="2" t="n">
-        <v>330.28</v>
+        <v>330.6</v>
       </c>
     </row>
     <row r="828">
@@ -50959,7 +50959,7 @@
         </is>
       </c>
       <c r="M828" s="2" t="n">
-        <v>6723.97</v>
+        <v>6730.45</v>
       </c>
     </row>
     <row r="829">
@@ -51020,7 +51020,7 @@
         </is>
       </c>
       <c r="M829" s="2" t="n">
-        <v>57.98</v>
+        <v>58.04</v>
       </c>
     </row>
     <row r="830">
@@ -51081,7 +51081,7 @@
         </is>
       </c>
       <c r="M830" s="2" t="n">
-        <v>6078.81</v>
+        <v>6084.67</v>
       </c>
     </row>
     <row r="831">
@@ -51142,7 +51142,7 @@
         </is>
       </c>
       <c r="M831" s="2" t="n">
-        <v>2960.44</v>
+        <v>2963.29</v>
       </c>
     </row>
     <row r="832">
@@ -51203,7 +51203,7 @@
         </is>
       </c>
       <c r="M832" s="2" t="n">
-        <v>162.34</v>
+        <v>162.5</v>
       </c>
     </row>
     <row r="833">
@@ -51264,7 +51264,7 @@
         </is>
       </c>
       <c r="M833" s="2" t="n">
-        <v>2947.32</v>
+        <v>2950.16</v>
       </c>
     </row>
     <row r="834">
@@ -51325,7 +51325,7 @@
         </is>
       </c>
       <c r="M834" s="2" t="n">
-        <v>4843.27</v>
+        <v>4847.94</v>
       </c>
     </row>
     <row r="835">
@@ -51386,7 +51386,7 @@
         </is>
       </c>
       <c r="M835" s="2" t="n">
-        <v>202.52</v>
+        <v>202.72</v>
       </c>
     </row>
     <row r="836">
@@ -51447,7 +51447,7 @@
         </is>
       </c>
       <c r="M836" s="2" t="n">
-        <v>704.04</v>
+        <v>704.72</v>
       </c>
     </row>
     <row r="837">
@@ -51508,7 +51508,7 @@
         </is>
       </c>
       <c r="M837" s="2" t="n">
-        <v>3384.63</v>
+        <v>3387.89</v>
       </c>
     </row>
     <row r="838">
@@ -51569,7 +51569,7 @@
         </is>
       </c>
       <c r="M838" s="2" t="n">
-        <v>153</v>
+        <v>153.15</v>
       </c>
     </row>
     <row r="839">
@@ -51630,7 +51630,7 @@
         </is>
       </c>
       <c r="M839" s="2" t="n">
-        <v>2577.53</v>
+        <v>2580.01</v>
       </c>
     </row>
     <row r="840">
@@ -51691,7 +51691,7 @@
         </is>
       </c>
       <c r="M840" s="2" t="n">
-        <v>2548.95</v>
+        <v>2551.41</v>
       </c>
     </row>
     <row r="841">
@@ -51752,7 +51752,7 @@
         </is>
       </c>
       <c r="M841" s="2" t="n">
-        <v>1308.69</v>
+        <v>1309.95</v>
       </c>
     </row>
     <row r="842">
@@ -51813,7 +51813,7 @@
         </is>
       </c>
       <c r="M842" s="2" t="n">
-        <v>392.06</v>
+        <v>392.43</v>
       </c>
     </row>
     <row r="843">
@@ -51874,7 +51874,7 @@
         </is>
       </c>
       <c r="M843" s="2" t="n">
-        <v>341.25</v>
+        <v>341.58</v>
       </c>
     </row>
     <row r="844">
@@ -51935,7 +51935,7 @@
         </is>
       </c>
       <c r="M844" s="2" t="n">
-        <v>415.85</v>
+        <v>416.25</v>
       </c>
     </row>
     <row r="845">
@@ -51996,7 +51996,7 @@
         </is>
       </c>
       <c r="M845" s="2" t="n">
-        <v>926.4</v>
+        <v>927.29</v>
       </c>
     </row>
     <row r="846">
@@ -52057,7 +52057,7 @@
         </is>
       </c>
       <c r="M846" s="2" t="n">
-        <v>607.79</v>
+        <v>608.37</v>
       </c>
     </row>
     <row r="847">
@@ -52118,7 +52118,7 @@
         </is>
       </c>
       <c r="M847" s="2" t="n">
-        <v>187.75</v>
+        <v>187.93</v>
       </c>
     </row>
     <row r="848">
@@ -52179,7 +52179,7 @@
         </is>
       </c>
       <c r="M848" s="2" t="n">
-        <v>155.58</v>
+        <v>155.73</v>
       </c>
     </row>
     <row r="849">
@@ -52240,7 +52240,7 @@
         </is>
       </c>
       <c r="M849" s="2" t="n">
-        <v>485.38</v>
+        <v>485.84</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/gas-licuado-de-petroleo/feb-2026.xlsx
+++ b/docs/oc-mensuales/gas-licuado-de-petroleo/feb-2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC feb-2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC feb-2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -5795,7 +5795,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -6100,7 +6100,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -7320,7 +7320,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -7503,7 +7503,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -8235,7 +8235,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -8662,7 +8662,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -8845,7 +8845,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -9211,7 +9211,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -10126,7 +10126,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -10675,7 +10675,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -10919,7 +10919,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -11346,7 +11346,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -11651,7 +11651,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -12093,7 +12093,7 @@
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
@@ -12387,7 +12387,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -12448,7 +12448,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -12631,7 +12631,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -12936,7 +12936,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -13790,7 +13790,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -14095,7 +14095,7 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -14278,7 +14278,7 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -14644,7 +14644,7 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
@@ -14766,7 +14766,7 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
@@ -14888,7 +14888,7 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
@@ -15132,7 +15132,7 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
@@ -15437,7 +15437,7 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
@@ -15498,7 +15498,7 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
@@ -15925,7 +15925,7 @@
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
@@ -16962,7 +16962,7 @@
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
@@ -17206,7 +17206,7 @@
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
@@ -17450,7 +17450,7 @@
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
@@ -17511,7 +17511,7 @@
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
@@ -18304,7 +18304,7 @@
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
@@ -18975,7 +18975,7 @@
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
@@ -19524,7 +19524,7 @@
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
@@ -20439,7 +20439,7 @@
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I328" t="inlineStr">
@@ -20683,7 +20683,7 @@
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I332" t="inlineStr">
@@ -21537,7 +21537,7 @@
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
@@ -22452,7 +22452,7 @@
       </c>
       <c r="H361" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I361" t="inlineStr">
@@ -22574,7 +22574,7 @@
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I363" t="inlineStr">
@@ -22940,7 +22940,7 @@
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I369" t="inlineStr">
@@ -23306,7 +23306,7 @@
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I375" t="inlineStr">
@@ -23367,7 +23367,7 @@
       </c>
       <c r="H376" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I376" t="inlineStr">
@@ -23428,7 +23428,7 @@
       </c>
       <c r="H377" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I377" t="inlineStr">
@@ -23489,7 +23489,7 @@
       </c>
       <c r="H378" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I378" t="inlineStr">
@@ -23550,7 +23550,7 @@
       </c>
       <c r="H379" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I379" t="inlineStr">
@@ -25014,7 +25014,7 @@
       </c>
       <c r="H403" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I403" t="inlineStr">
@@ -25563,7 +25563,7 @@
       </c>
       <c r="H412" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I412" t="inlineStr">
@@ -26417,7 +26417,7 @@
       </c>
       <c r="H426" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I426" t="inlineStr">
@@ -27088,7 +27088,7 @@
       </c>
       <c r="H437" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I437" t="inlineStr">
@@ -27332,7 +27332,7 @@
       </c>
       <c r="H441" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I441" t="inlineStr">
@@ -27820,7 +27820,7 @@
       </c>
       <c r="H449" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I449" t="inlineStr">
@@ -28125,7 +28125,7 @@
       </c>
       <c r="H454" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I454" t="inlineStr">
@@ -28552,7 +28552,7 @@
       </c>
       <c r="H461" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I461" t="inlineStr">
@@ -28613,7 +28613,7 @@
       </c>
       <c r="H462" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I462" t="inlineStr">
@@ -28796,7 +28796,7 @@
       </c>
       <c r="H465" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I465" t="inlineStr">
@@ -29467,7 +29467,7 @@
       </c>
       <c r="H476" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I476" t="inlineStr">
@@ -29711,7 +29711,7 @@
       </c>
       <c r="H480" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I480" t="inlineStr">
@@ -29894,7 +29894,7 @@
       </c>
       <c r="H483" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I483" t="inlineStr">
@@ -30016,7 +30016,7 @@
       </c>
       <c r="H485" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I485" t="inlineStr">
@@ -30138,7 +30138,7 @@
       </c>
       <c r="H487" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I487" t="inlineStr">
@@ -30321,7 +30321,7 @@
       </c>
       <c r="H490" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I490" t="inlineStr">
@@ -30382,7 +30382,7 @@
       </c>
       <c r="H491" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I491" t="inlineStr">
@@ -30870,7 +30870,7 @@
       </c>
       <c r="H499" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I499" t="inlineStr">
@@ -31114,7 +31114,7 @@
       </c>
       <c r="H503" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I503" t="inlineStr">
@@ -31175,7 +31175,7 @@
       </c>
       <c r="H504" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I504" t="inlineStr">
@@ -31236,7 +31236,7 @@
       </c>
       <c r="H505" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I505" t="inlineStr">
@@ -31541,7 +31541,7 @@
       </c>
       <c r="H510" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I510" t="inlineStr">
@@ -31663,7 +31663,7 @@
       </c>
       <c r="H512" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I512" t="inlineStr">
@@ -31968,7 +31968,7 @@
       </c>
       <c r="H517" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I517" t="inlineStr">
@@ -32029,7 +32029,7 @@
       </c>
       <c r="H518" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I518" t="inlineStr">
@@ -32456,7 +32456,7 @@
       </c>
       <c r="H525" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I525" t="inlineStr">
@@ -32517,7 +32517,7 @@
       </c>
       <c r="H526" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I526" t="inlineStr">
@@ -33005,7 +33005,7 @@
       </c>
       <c r="H534" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I534" t="inlineStr">
@@ -33737,7 +33737,7 @@
       </c>
       <c r="H546" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I546" t="inlineStr">
@@ -33920,7 +33920,7 @@
       </c>
       <c r="H549" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I549" t="inlineStr">
@@ -33981,7 +33981,7 @@
       </c>
       <c r="H550" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I550" t="inlineStr">
@@ -34408,7 +34408,7 @@
       </c>
       <c r="H557" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I557" t="inlineStr">
@@ -34469,7 +34469,7 @@
       </c>
       <c r="H558" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I558" t="inlineStr">
@@ -34530,7 +34530,7 @@
       </c>
       <c r="H559" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I559" t="inlineStr">
@@ -34957,7 +34957,7 @@
       </c>
       <c r="H566" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I566" t="inlineStr">
@@ -35872,7 +35872,7 @@
       </c>
       <c r="H581" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I581" t="inlineStr">
@@ -36116,7 +36116,7 @@
       </c>
       <c r="H585" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I585" t="inlineStr">
@@ -36177,7 +36177,7 @@
       </c>
       <c r="H586" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I586" t="inlineStr">
@@ -36421,7 +36421,7 @@
       </c>
       <c r="H590" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I590" t="inlineStr">
@@ -36482,7 +36482,7 @@
       </c>
       <c r="H591" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I591" t="inlineStr">
@@ -36604,7 +36604,7 @@
       </c>
       <c r="H593" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I593" t="inlineStr">
@@ -36909,7 +36909,7 @@
       </c>
       <c r="H598" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I598" t="inlineStr">
@@ -37336,7 +37336,7 @@
       </c>
       <c r="H605" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I605" t="inlineStr">
@@ -37580,7 +37580,7 @@
       </c>
       <c r="H609" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I609" t="inlineStr">
@@ -37763,7 +37763,7 @@
       </c>
       <c r="H612" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I612" t="inlineStr">
@@ -37885,7 +37885,7 @@
       </c>
       <c r="H614" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I614" t="inlineStr">
@@ -37946,7 +37946,7 @@
       </c>
       <c r="H615" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I615" t="inlineStr">
@@ -38007,7 +38007,7 @@
       </c>
       <c r="H616" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I616" t="inlineStr">
@@ -38068,7 +38068,7 @@
       </c>
       <c r="H617" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I617" t="inlineStr">
@@ -38495,7 +38495,7 @@
       </c>
       <c r="H624" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I624" t="inlineStr">
@@ -38739,7 +38739,7 @@
       </c>
       <c r="H628" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I628" t="inlineStr">
@@ -38861,7 +38861,7 @@
       </c>
       <c r="H630" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I630" t="inlineStr">
@@ -39776,7 +39776,7 @@
       </c>
       <c r="H645" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I645" t="inlineStr">
@@ -39837,7 +39837,7 @@
       </c>
       <c r="H646" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I646" t="inlineStr">
@@ -40203,7 +40203,7 @@
       </c>
       <c r="H652" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I652" t="inlineStr">
@@ -40935,7 +40935,7 @@
       </c>
       <c r="H664" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I664" t="inlineStr">
@@ -40996,7 +40996,7 @@
       </c>
       <c r="H665" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I665" t="inlineStr">
@@ -41057,7 +41057,7 @@
       </c>
       <c r="H666" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I666" t="inlineStr">
@@ -41240,7 +41240,7 @@
       </c>
       <c r="H669" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I669" t="inlineStr">
@@ -41301,7 +41301,7 @@
       </c>
       <c r="H670" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I670" t="inlineStr">
@@ -41850,7 +41850,7 @@
       </c>
       <c r="H679" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I679" t="inlineStr">
@@ -42216,7 +42216,7 @@
       </c>
       <c r="H685" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I685" t="inlineStr">
@@ -42765,7 +42765,7 @@
       </c>
       <c r="H694" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I694" t="inlineStr">
@@ -43131,7 +43131,7 @@
       </c>
       <c r="H700" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I700" t="inlineStr">
@@ -43619,7 +43619,7 @@
       </c>
       <c r="H708" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I708" t="inlineStr">
@@ -44107,7 +44107,7 @@
       </c>
       <c r="H716" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I716" t="inlineStr">
@@ -44351,7 +44351,7 @@
       </c>
       <c r="H720" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I720" t="inlineStr">
@@ -44656,7 +44656,7 @@
       </c>
       <c r="H725" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I725" t="inlineStr">
@@ -44961,7 +44961,7 @@
       </c>
       <c r="H730" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I730" t="inlineStr">
@@ -45083,7 +45083,7 @@
       </c>
       <c r="H732" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I732" t="inlineStr">
@@ -45388,7 +45388,7 @@
       </c>
       <c r="H737" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I737" t="inlineStr">
@@ -45693,7 +45693,7 @@
       </c>
       <c r="H742" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I742" t="inlineStr">
@@ -46303,7 +46303,7 @@
       </c>
       <c r="H752" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I752" t="inlineStr">
@@ -46364,7 +46364,7 @@
       </c>
       <c r="H753" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I753" t="inlineStr">
@@ -46913,7 +46913,7 @@
       </c>
       <c r="H762" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I762" t="inlineStr">
@@ -47035,7 +47035,7 @@
       </c>
       <c r="H764" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I764" t="inlineStr">
@@ -47645,7 +47645,7 @@
       </c>
       <c r="H774" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I774" t="inlineStr">
@@ -48438,7 +48438,7 @@
       </c>
       <c r="H787" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I787" t="inlineStr">
@@ -49109,7 +49109,7 @@
       </c>
       <c r="H798" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I798" t="inlineStr">
@@ -49231,7 +49231,7 @@
       </c>
       <c r="H800" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I800" t="inlineStr">
@@ -49963,7 +49963,7 @@
       </c>
       <c r="H812" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I812" t="inlineStr">
@@ -50207,7 +50207,7 @@
       </c>
       <c r="H816" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I816" t="inlineStr">
@@ -50634,7 +50634,7 @@
       </c>
       <c r="H823" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I823" t="inlineStr">
@@ -50695,7 +50695,7 @@
       </c>
       <c r="H824" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I824" t="inlineStr">
@@ -51366,7 +51366,7 @@
       </c>
       <c r="H835" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I835" t="inlineStr">
@@ -51671,7 +51671,7 @@
       </c>
       <c r="H840" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I840" t="inlineStr">
@@ -51915,7 +51915,7 @@
       </c>
       <c r="H844" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I844" t="inlineStr">
@@ -51976,7 +51976,7 @@
       </c>
       <c r="H845" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I845" t="inlineStr">

--- a/docs/oc-mensuales/gas-licuado-de-petroleo/feb-2026.xlsx
+++ b/docs/oc-mensuales/gas-licuado-de-petroleo/feb-2026.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE CALDERA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -605,7 +605,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Iquique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -910,7 +910,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Metropolitana</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XVI ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SANTIAGO OESTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo del Centro de Cumpli</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - VIII Zona Bio Bio</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bienes y Servicios</t>
+          <t>Hospital de Melipilla</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Prefectura Coquimbo</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo Camino La Pólvora</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Gendarmería de Chile - Dirección Regional de Coquimbo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Temuco</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2740,7 +2740,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Talca</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2923,7 +2923,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>DESTACAMENTO IM Nº 1 LYNCH</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Valparaiso</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>DESTACAMENTO IM Nº 1 LYNCH</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3167,7 +3167,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3533,7 +3533,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3594,7 +3594,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Zona Bienestar "Valparaíso" Bienestar Social</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -4082,7 +4082,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4448,7 +4448,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS V ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4514,7 +4514,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4631,7 +4631,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE IQUIQUE</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4875,7 +4875,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hospital de Ancud</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5063,7 +5063,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -5119,7 +5119,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Metropolitana</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5180,7 +5180,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Temuco</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5973,7 +5973,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hospital de Peñaflor</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE P</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -6217,7 +6217,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>DIRECCION DE SEGURIDAD Y OPERACIONES MARITIMAS</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6278,7 +6278,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Retiro</t>
+          <t>ILUSTRE MUNICIPALIDAD DE RETIRO</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6339,7 +6339,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Gendarmería de Chile CET Antofagasta II Región</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6461,7 +6461,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SANTIAGO OESTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6522,7 +6522,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SANTIAGO OESTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6827,7 +6827,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo del CDP Talagante</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -6888,7 +6888,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -6949,7 +6949,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>JEFATURA ADMINISTRATIVA Y LOGISTICA DE LA GUARNICION COYHAIQUE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -7071,7 +7071,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -7132,7 +7132,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Comando de Personal</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7193,7 +7193,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE PUERTO MONTT</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7437,7 +7437,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SANTIAGO ESTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7498,7 +7498,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Concepcion</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7559,7 +7559,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Gendarmería de Chile Centro de Educación y Trabajo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -7620,7 +7620,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Gendarmería de Chile Centro de Educación y Trabajo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -7671,7 +7671,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -7681,7 +7681,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Reinserción Social Juvenil</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -7742,7 +7742,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SANTIAGO ESTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -7803,7 +7803,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Centro Educación y Trabajo Femenino Semiabierto St</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -7925,7 +7925,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -8108,7 +8108,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Zona de Bienestar Arica</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -8230,7 +8230,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -8291,7 +8291,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -8352,7 +8352,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>JEFATURA ADMINISTRATIVA Y LOGISTICA DE LA GUARNICION COYHAIQUE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -8413,7 +8413,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO DE BIENESTAR SOCIAL 1° Z.N.</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -8540,7 +8540,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Dirección Regional de Ñuble</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -8657,7 +8657,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO BIENESTAR SOCIAL IIA ZONA NAVAL</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -8718,7 +8718,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Talca</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -8840,7 +8840,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE TIERRA DEL F</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE TIERRA DEL FUEGO</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -8962,12 +8962,12 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Protección</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -9084,7 +9084,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -9511,7 +9511,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE TIERRA DEL F</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE TIERRA DEL FUEGO</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -9572,7 +9572,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo CCP Nueva Imperial</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -9633,7 +9633,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Instituto de Prevision Social</t>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -9755,7 +9755,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE PUERTO MONTT</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -9816,7 +9816,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL ADUANA DE PUERTO MONTT</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -9877,7 +9877,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Antofagasta</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -9999,7 +9999,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>FONDO PARA HOSPITALES DE CARABINEROS DE CHILE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -10060,7 +10060,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo Colina 1</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -10182,7 +10182,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>FISCALIZACION Y CONTROL</t>
+          <t>SUBSECRETARIA DE TRANSPORTES</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -10243,7 +10243,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VIII ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -10365,7 +10365,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Puerto Montt</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -10487,7 +10487,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE PUERTO MONTT</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -10548,7 +10548,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Comandancia en Jefe de la IV Zona Naval</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -10609,7 +10609,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SANTIAGO OESTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -10914,7 +10914,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>CORPORACION SOCIAL Y CULTURAL DE CONCEPCION- SEMCO</t>
+          <t>CORPORACION SOCIAL Y CULTURA DE CONCEPCION - SEMCO</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -10975,7 +10975,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Puerto Montt</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -11097,7 +11097,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Dirección Regional de Ñuble</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -11158,7 +11158,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Bienes y Servicios</t>
+          <t>Hospital de Melipilla</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -11219,7 +11219,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA METROPOLITANA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -11280,7 +11280,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Servicio Nacional del Adulto Mayor</t>
+          <t>SERVICIO NACIONAL DEL ADULTO MAYOR</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -11341,7 +11341,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Centro de Telecomunicaciones Navales (M)</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -11402,7 +11402,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Temuco</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -11524,7 +11524,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>I.Municipalidad de El Carmen</t>
+          <t>Ilustre Municipalidad de El Carmen</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -11585,7 +11585,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>I.Municipalidad de El Carmen</t>
+          <t>Ilustre Municipalidad de El Carmen</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -11707,7 +11707,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -12138,7 +12138,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Dirección Regional de Ñuble</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -12260,7 +12260,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -12321,7 +12321,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -12687,7 +12687,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -12748,7 +12748,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Valparaiso</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -12992,7 +12992,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Temuco</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -13053,7 +13053,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>DESTACAMENTO IM Nº 1 LYNCH</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -13297,7 +13297,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Zona Bienestar "Coyhaique" Bienestar Social</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -13358,7 +13358,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO DE BIENESTAR SOCIAL 1° Z.N.</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -13409,7 +13409,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
@@ -13480,7 +13480,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE PUERTO MONTT</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -13541,7 +13541,7 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE PUERTO MONTT</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -13724,7 +13724,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo de Gendarmería</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -13790,7 +13790,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -13846,7 +13846,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Metropolitana</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -13907,7 +13907,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección de Bienestar</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -14151,7 +14151,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -14278,7 +14278,7 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -14334,7 +14334,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>CENTRAL DE ATENCION PRIMARIA DE SALUD DE LA ARMADA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -14456,7 +14456,7 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Zona Bienestar "Región Metropolitana" - B Social</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -14517,7 +14517,7 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE PETORCA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA PETORCA</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -14578,7 +14578,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE PETORCA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA PETORCA</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -14639,7 +14639,7 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>BASE INFANTERIA DE MARINA TUMBES</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -14822,7 +14822,7 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Metropolitana</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -15005,7 +15005,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo del Centro de Cumpli</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -15249,7 +15249,7 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO DE BIENESTAR SOCIAL 1° Z.N.</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -15310,7 +15310,7 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE COQUIMBO</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -15371,7 +15371,7 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -15432,7 +15432,7 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VI ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -15554,7 +15554,7 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>gerencia</t>
+          <t>Corporación Municipal de Cultura de San Clemente</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -15615,7 +15615,7 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -15676,7 +15676,7 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PUBLICA DE ANDALIÉN CO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE ANDALIÉN COSTA</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -15859,7 +15859,7 @@
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Universidad de Aysen</t>
+          <t>UNIVERSIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -16103,7 +16103,7 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -16408,7 +16408,7 @@
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Zona Bienestar "Valparaíso" Bienestar Social</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -16469,7 +16469,7 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>COMANDANCIA EN JEFE DE LA PRIMERA ZONA NAVAL</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -16774,12 +16774,12 @@
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección de Bienestar</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
@@ -16835,7 +16835,7 @@
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -16896,7 +16896,7 @@
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Comando de Personal</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -17079,7 +17079,7 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>JEFATURA DE BIENESTAR (I.P)</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -17140,7 +17140,7 @@
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -17191,7 +17191,7 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
@@ -17262,7 +17262,7 @@
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -17323,7 +17323,7 @@
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Pinto Depto. de Salud</t>
+          <t>I MUNICIPALIDAD DE PINTO</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -17384,7 +17384,7 @@
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Desarrollo Productivo y T</t>
+          <t>Corporación Municipal de Desarrollo Productivo y Turismo de Molina</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -17445,7 +17445,7 @@
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Concepcion</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -17506,7 +17506,7 @@
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Concepcion</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -17628,7 +17628,7 @@
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Hospital de Queilen</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -17811,7 +17811,7 @@
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>JEFATURA DE BIENESTAR (I.P)</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -17994,7 +17994,7 @@
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Talca</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
@@ -18055,7 +18055,7 @@
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SANTIAGO OESTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
@@ -18116,7 +18116,7 @@
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>Academia Politécnica Naval</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
@@ -18177,7 +18177,7 @@
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>DIVISIÓN DE BIENESTAR SOCIAL</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -18299,7 +18299,7 @@
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>CORPORACIÓN SOCIAL Y CULTURAL DE CONCEPCIÓN - SEMC</t>
+          <t>CORPORACION SOCIAL Y CULTURA DE CONCEPCION - SEMCO</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
@@ -18360,7 +18360,7 @@
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SANTIAGO OESTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
@@ -18421,7 +18421,7 @@
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE SAN ANTONIO</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
@@ -18482,7 +18482,7 @@
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SANTIAGO OESTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
@@ -18543,7 +18543,7 @@
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo Colina 1</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
@@ -18604,7 +18604,7 @@
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO DE BIENESTAR SOCIAL 1° Z.N.</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -18848,7 +18848,7 @@
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo de Osorno</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
@@ -18909,7 +18909,7 @@
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
@@ -19092,7 +19092,7 @@
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo CDP Curacautín</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
@@ -19214,12 +19214,12 @@
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PUBLICA DE ANDALIÉN CO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE ANDALIÉN COSTA</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
@@ -19397,12 +19397,12 @@
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PUBLICA DE ANDALIÉN CO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE ANDALIÉN COSTA</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
@@ -19458,7 +19458,7 @@
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Chillan Viejo</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
@@ -19580,12 +19580,12 @@
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PUBLICA DE ANDALIÉN CO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE ANDALIÉN COSTA</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
@@ -19641,12 +19641,12 @@
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PUBLICA DE ANDALIÉN CO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE ANDALIÉN COSTA</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
@@ -19763,7 +19763,7 @@
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
@@ -19824,7 +19824,7 @@
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SANTIAGO ESTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
@@ -19946,7 +19946,7 @@
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SANTIAGO ESTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
@@ -20007,7 +20007,7 @@
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>Division de Bienestar Social</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
@@ -20068,7 +20068,7 @@
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
@@ -20129,7 +20129,7 @@
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>Division de Bienestar Social</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
@@ -20190,7 +20190,7 @@
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
@@ -20251,7 +20251,7 @@
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>Servicio de Salud Coquimbo Hospital de Ovalle</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE O</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
@@ -20312,7 +20312,7 @@
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VII ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
@@ -20373,7 +20373,7 @@
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VII ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
@@ -20495,7 +20495,7 @@
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
@@ -20556,7 +20556,7 @@
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE SAN ANTONIO</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
@@ -20617,7 +20617,7 @@
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS V ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
@@ -20678,7 +20678,7 @@
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>HOSPITAL DE LITUECHE</t>
+          <t>Hospital de Litueche</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
@@ -20800,7 +20800,7 @@
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE SAN ANTONIO</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
@@ -20983,7 +20983,7 @@
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SANTIAGO OESTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
@@ -21044,7 +21044,7 @@
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>DIRECCION REGIONAL XIV REGION DE LOS RIOS</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
@@ -21105,12 +21105,12 @@
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PUBLICA DE ANDALIÉN CO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE ANDALIÉN COSTA</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I339" t="inlineStr">
@@ -21410,7 +21410,7 @@
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>Dirección  de Salud Municipal Chillán</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
@@ -21654,7 +21654,7 @@
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>Hospital de Achao</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
@@ -21776,7 +21776,7 @@
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Talca</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
@@ -22020,7 +22020,7 @@
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>Superintendencia de Insolvencia y Reemprendimiento</t>
+          <t>SUPERINTENDENCIA DE INSOLVENCIA Y REEMPRENDIMIENTO</t>
         </is>
       </c>
       <c r="H354" t="inlineStr">
@@ -22142,7 +22142,7 @@
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Puerto Montt</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H356" t="inlineStr">
@@ -22203,7 +22203,7 @@
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE PUDAHUEL</t>
+          <t>MUNICIPALIDAD DE PUDAHUEL</t>
         </is>
       </c>
       <c r="H357" t="inlineStr">
@@ -22325,7 +22325,7 @@
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>SERVICIO DE BIENESTAR DEL PERSONAL CMPA</t>
+          <t>I MUNICIPALIDAD DE PUENTE ALTO</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
@@ -22508,7 +22508,7 @@
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUELLON</t>
+          <t>Ilustre Municipalidad De Quellón</t>
         </is>
       </c>
       <c r="H362" t="inlineStr">
@@ -22691,7 +22691,7 @@
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H365" t="inlineStr">
@@ -22874,7 +22874,7 @@
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>Iluste Municipalidad de Huechuraba</t>
+          <t>Municipalidad de Huechuraba</t>
         </is>
       </c>
       <c r="H368" t="inlineStr">
@@ -22935,7 +22935,7 @@
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>HOSPITAL COMUNITARIO CRISTINA CALDERON DE PUERTO WILLIAMS</t>
+          <t>SERVICIO DE SALUD MAGALLANES</t>
         </is>
       </c>
       <c r="H369" t="inlineStr">
@@ -23057,7 +23057,7 @@
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>Iª Brigada Aérea</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H371" t="inlineStr">
@@ -23118,7 +23118,7 @@
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H372" t="inlineStr">
@@ -23240,7 +23240,7 @@
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>Iª Brigada Aérea</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H374" t="inlineStr">
@@ -23301,7 +23301,7 @@
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XII ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H375" t="inlineStr">
@@ -23362,7 +23362,7 @@
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XII ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H376" t="inlineStr">
@@ -23606,7 +23606,7 @@
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H380" t="inlineStr">
@@ -23667,7 +23667,7 @@
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>Servicio Agricola y Ganadero</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H381" t="inlineStr">
@@ -23789,7 +23789,7 @@
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SANTIAGO ESTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H383" t="inlineStr">
@@ -23850,7 +23850,7 @@
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>- - -</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H384" t="inlineStr">
@@ -23972,7 +23972,7 @@
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>Comando de Personal</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H386" t="inlineStr">
@@ -24033,7 +24033,7 @@
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE PUERTO MONTT</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H387" t="inlineStr">
@@ -24094,7 +24094,7 @@
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Talca</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H388" t="inlineStr">
@@ -24155,7 +24155,7 @@
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Chillan Viejo</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
         </is>
       </c>
       <c r="H389" t="inlineStr">
@@ -24216,7 +24216,7 @@
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo del CDP Talagante</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H390" t="inlineStr">
@@ -24277,7 +24277,7 @@
       </c>
       <c r="G391" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SANTIAGO OESTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H391" t="inlineStr">
@@ -24338,7 +24338,7 @@
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>CORP MUNIC DE QUELLON PARA LA EDUC SALUD</t>
+          <t>Corporación Municipal de Quellón</t>
         </is>
       </c>
       <c r="H392" t="inlineStr">
@@ -24399,7 +24399,7 @@
       </c>
       <c r="G393" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DESARROLLO SOCIAL COLINA</t>
+          <t>Corporación Municipal de Desarrollo Social de Colina</t>
         </is>
       </c>
       <c r="H393" t="inlineStr">
@@ -24582,7 +24582,7 @@
       </c>
       <c r="G396" t="inlineStr">
         <is>
-          <t>Bienes y Servicios</t>
+          <t>Hospital de Melipilla</t>
         </is>
       </c>
       <c r="H396" t="inlineStr">
@@ -24643,7 +24643,7 @@
       </c>
       <c r="G397" t="inlineStr">
         <is>
-          <t>Dirección General de Carabineros de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H397" t="inlineStr">
@@ -24765,7 +24765,7 @@
       </c>
       <c r="G399" t="inlineStr">
         <is>
-          <t>Zona Bienestar "Valparaíso" Bienestar Social</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H399" t="inlineStr">
@@ -24948,7 +24948,7 @@
       </c>
       <c r="G402" t="inlineStr">
         <is>
-          <t>DIRECCION REGIONAL DE GENDARMERIA DE CHILE, REGION</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H402" t="inlineStr">
@@ -25314,7 +25314,7 @@
       </c>
       <c r="G408" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LUMACO</t>
+          <t>Ilustre Municipalidad de Lumaco</t>
         </is>
       </c>
       <c r="H408" t="inlineStr">
@@ -25497,7 +25497,7 @@
       </c>
       <c r="G411" t="inlineStr">
         <is>
-          <t>REGIMIENTO 12 "SANGRA"</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H411" t="inlineStr">
@@ -25558,7 +25558,7 @@
       </c>
       <c r="G412" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XII ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H412" t="inlineStr">
@@ -25680,7 +25680,7 @@
       </c>
       <c r="G414" t="inlineStr">
         <is>
-          <t>Dirección General de Aeronáutica Civil</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H414" t="inlineStr">
@@ -25863,7 +25863,7 @@
       </c>
       <c r="G417" t="inlineStr">
         <is>
-          <t>Salud</t>
+          <t>I MUNICIPALIDAD DE COIHUECO</t>
         </is>
       </c>
       <c r="H417" t="inlineStr">
@@ -26168,7 +26168,7 @@
       </c>
       <c r="G422" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE PUERTO MONTT</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H422" t="inlineStr">
@@ -26290,7 +26290,7 @@
       </c>
       <c r="G424" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H424" t="inlineStr">
@@ -26351,7 +26351,7 @@
       </c>
       <c r="G425" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SANTIAGO OESTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H425" t="inlineStr">
@@ -26534,7 +26534,7 @@
       </c>
       <c r="G428" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Temuco</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H428" t="inlineStr">
@@ -26595,7 +26595,7 @@
       </c>
       <c r="G429" t="inlineStr">
         <is>
-          <t>Regimiento Reforzado N° 1 "Calama"</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H429" t="inlineStr">
@@ -26646,7 +26646,7 @@
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F430" t="inlineStr">
@@ -26961,7 +26961,7 @@
       </c>
       <c r="G435" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Talca</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H435" t="inlineStr">
@@ -27022,7 +27022,7 @@
       </c>
       <c r="G436" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Valparaiso</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H436" t="inlineStr">
@@ -27144,7 +27144,7 @@
       </c>
       <c r="G438" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SANTIAGO OESTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H438" t="inlineStr">
@@ -27205,7 +27205,7 @@
       </c>
       <c r="G439" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE VALPARAISO</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H439" t="inlineStr">
@@ -27266,7 +27266,7 @@
       </c>
       <c r="G440" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H440" t="inlineStr">
@@ -27327,7 +27327,7 @@
       </c>
       <c r="G441" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Concepcion</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H441" t="inlineStr">
@@ -27632,7 +27632,7 @@
       </c>
       <c r="G446" t="inlineStr">
         <is>
-          <t>Zona Bienestar "Región Metropolitana" - B Social</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H446" t="inlineStr">
@@ -27759,7 +27759,7 @@
       </c>
       <c r="H448" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I448" t="inlineStr">
@@ -27937,7 +27937,7 @@
       </c>
       <c r="G451" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H451" t="inlineStr">
@@ -27998,7 +27998,7 @@
       </c>
       <c r="G452" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H452" t="inlineStr">
@@ -28120,7 +28120,7 @@
       </c>
       <c r="G454" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VIII ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H454" t="inlineStr">
@@ -28181,12 +28181,12 @@
       </c>
       <c r="G455" t="inlineStr">
         <is>
-          <t>IIª Brigada Aérea</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H455" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I455" t="inlineStr">
@@ -28425,7 +28425,7 @@
       </c>
       <c r="G459" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XIV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H459" t="inlineStr">
@@ -28486,7 +28486,7 @@
       </c>
       <c r="G460" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DESARROLLO SOCIAL COLINA</t>
+          <t>Corporación Municipal de Desarrollo Social de Colina</t>
         </is>
       </c>
       <c r="H460" t="inlineStr">
@@ -28608,7 +28608,7 @@
       </c>
       <c r="G462" t="inlineStr">
         <is>
-          <t>Division de Bienestar Social</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H462" t="inlineStr">
@@ -28852,7 +28852,7 @@
       </c>
       <c r="G466" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SANTIAGO ESTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H466" t="inlineStr">
@@ -29096,7 +29096,7 @@
       </c>
       <c r="G470" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H470" t="inlineStr">
@@ -29218,7 +29218,7 @@
       </c>
       <c r="G472" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SANTIAGO ESTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H472" t="inlineStr">
@@ -29462,7 +29462,7 @@
       </c>
       <c r="G476" t="inlineStr">
         <is>
-          <t>BASE INFANTERIA DE MARINA TUMBES</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H476" t="inlineStr">
@@ -29523,7 +29523,7 @@
       </c>
       <c r="G477" t="inlineStr">
         <is>
-          <t>Zona Bienestar "Valparaíso" Bienestar Social</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H477" t="inlineStr">
@@ -29584,7 +29584,7 @@
       </c>
       <c r="G478" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Puerto Montt</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H478" t="inlineStr">
@@ -29767,7 +29767,7 @@
       </c>
       <c r="G481" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE ANTOFAGASTA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H481" t="inlineStr">
@@ -29828,7 +29828,7 @@
       </c>
       <c r="G482" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo del Centro de Cumpli</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H482" t="inlineStr">
@@ -29889,7 +29889,7 @@
       </c>
       <c r="G483" t="inlineStr">
         <is>
-          <t>BASE INFANTERIA DE MARINA TUMBES</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H483" t="inlineStr">
@@ -29950,7 +29950,7 @@
       </c>
       <c r="G484" t="inlineStr">
         <is>
-          <t>SERVICIO DE BIENESTAR SALUD MUNICIPAL</t>
+          <t>I MUNICIPALIDAD DE LINARES</t>
         </is>
       </c>
       <c r="H484" t="inlineStr">
@@ -30194,7 +30194,7 @@
       </c>
       <c r="G488" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H488" t="inlineStr">
@@ -30255,7 +30255,7 @@
       </c>
       <c r="G489" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H489" t="inlineStr">
@@ -30316,7 +30316,7 @@
       </c>
       <c r="G490" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H490" t="inlineStr">
@@ -30499,7 +30499,7 @@
       </c>
       <c r="G493" t="inlineStr">
         <is>
-          <t>BASE NAVAL PUERTO MONTT</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H493" t="inlineStr">
@@ -30621,7 +30621,7 @@
       </c>
       <c r="G495" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H495" t="inlineStr">
@@ -30743,7 +30743,7 @@
       </c>
       <c r="G497" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H497" t="inlineStr">
@@ -30804,7 +30804,7 @@
       </c>
       <c r="G498" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE ESCUELA CABALLERIA QUI</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H498" t="inlineStr">
@@ -30865,7 +30865,7 @@
       </c>
       <c r="G499" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XII ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H499" t="inlineStr">
@@ -30926,7 +30926,7 @@
       </c>
       <c r="G500" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Temuco</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H500" t="inlineStr">
@@ -30992,7 +30992,7 @@
       </c>
       <c r="H501" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I501" t="inlineStr">
@@ -31048,7 +31048,7 @@
       </c>
       <c r="G502" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Antofagasta</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H502" t="inlineStr">
@@ -31292,7 +31292,7 @@
       </c>
       <c r="G506" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Temuco</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H506" t="inlineStr">
@@ -31475,7 +31475,7 @@
       </c>
       <c r="G509" t="inlineStr">
         <is>
-          <t>Zona de Bienestar Región Metropolitana</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H509" t="inlineStr">
@@ -31597,7 +31597,7 @@
       </c>
       <c r="G511" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Talca</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H511" t="inlineStr">
@@ -31663,7 +31663,7 @@
       </c>
       <c r="H512" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I512" t="inlineStr">
@@ -31780,7 +31780,7 @@
       </c>
       <c r="G514" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H514" t="inlineStr">
@@ -31963,7 +31963,7 @@
       </c>
       <c r="G517" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CORONEL DPTO ADMINIST</t>
+          <t>I MUNICIPALIDAD DE CORONEL</t>
         </is>
       </c>
       <c r="H517" t="inlineStr">
@@ -32085,7 +32085,7 @@
       </c>
       <c r="G519" t="inlineStr">
         <is>
-          <t>JEFATURA DE BIENESTAR (I.P)</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H519" t="inlineStr">
@@ -32390,7 +32390,7 @@
       </c>
       <c r="G524" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Metropolitana</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H524" t="inlineStr">
@@ -32451,7 +32451,7 @@
       </c>
       <c r="G525" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CORONEL DPTO ADMINIST</t>
+          <t>I MUNICIPALIDAD DE CORONEL</t>
         </is>
       </c>
       <c r="H525" t="inlineStr">
@@ -32573,7 +32573,7 @@
       </c>
       <c r="G527" t="inlineStr">
         <is>
-          <t>Zona de Bienestar Región Metropolitana</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H527" t="inlineStr">
@@ -32634,7 +32634,7 @@
       </c>
       <c r="G528" t="inlineStr">
         <is>
-          <t>DIRECCION REGIONAL DE GENDARMERIA DE CHILE, REGION</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H528" t="inlineStr">
@@ -32695,7 +32695,7 @@
       </c>
       <c r="G529" t="inlineStr">
         <is>
-          <t>Hospital de Queilen</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H529" t="inlineStr">
@@ -32761,7 +32761,7 @@
       </c>
       <c r="H530" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I530" t="inlineStr">
@@ -32817,7 +32817,7 @@
       </c>
       <c r="G531" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H531" t="inlineStr">
@@ -32883,7 +32883,7 @@
       </c>
       <c r="H532" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I532" t="inlineStr">
@@ -33000,7 +33000,7 @@
       </c>
       <c r="G534" t="inlineStr">
         <is>
-          <t>Dirección de Administración de Salud Municipal</t>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
         </is>
       </c>
       <c r="H534" t="inlineStr">
@@ -33061,7 +33061,7 @@
       </c>
       <c r="G535" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE ARICA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H535" t="inlineStr">
@@ -33122,7 +33122,7 @@
       </c>
       <c r="G536" t="inlineStr">
         <is>
-          <t>CORSABER</t>
+          <t>CORPORACION MUNICIPAL DE EDUCACION Y SALUD DE SAN BERNARDO</t>
         </is>
       </c>
       <c r="H536" t="inlineStr">
@@ -33183,7 +33183,7 @@
       </c>
       <c r="G537" t="inlineStr">
         <is>
-          <t>CORSABER</t>
+          <t>CORPORACION MUNICIPAL DE EDUCACION Y SALUD DE SAN BERNARDO</t>
         </is>
       </c>
       <c r="H537" t="inlineStr">
@@ -33244,7 +33244,7 @@
       </c>
       <c r="G538" t="inlineStr">
         <is>
-          <t>CORSABER</t>
+          <t>CORPORACION MUNICIPAL DE EDUCACION Y SALUD DE SAN BERNARDO</t>
         </is>
       </c>
       <c r="H538" t="inlineStr">
@@ -33305,7 +33305,7 @@
       </c>
       <c r="G539" t="inlineStr">
         <is>
-          <t>CORSABER</t>
+          <t>CORPORACION MUNICIPAL DE EDUCACION Y SALUD DE SAN BERNARDO</t>
         </is>
       </c>
       <c r="H539" t="inlineStr">
@@ -33488,7 +33488,7 @@
       </c>
       <c r="G542" t="inlineStr">
         <is>
-          <t>Division de Bienestar Social</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H542" t="inlineStr">
@@ -33539,7 +33539,7 @@
       </c>
       <c r="E543" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F543" t="inlineStr">
@@ -33549,7 +33549,7 @@
       </c>
       <c r="G543" t="inlineStr">
         <is>
-          <t>Division de Bienestar Social</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H543" t="inlineStr">
@@ -33610,7 +33610,7 @@
       </c>
       <c r="G544" t="inlineStr">
         <is>
-          <t>Division de Bienestar Social</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H544" t="inlineStr">
@@ -33671,7 +33671,7 @@
       </c>
       <c r="G545" t="inlineStr">
         <is>
-          <t>Academia Politécnica Naval</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H545" t="inlineStr">
@@ -33793,7 +33793,7 @@
       </c>
       <c r="G547" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H547" t="inlineStr">
@@ -33854,7 +33854,7 @@
       </c>
       <c r="G548" t="inlineStr">
         <is>
-          <t>Hospital de Castro</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H548" t="inlineStr">
@@ -34037,7 +34037,7 @@
       </c>
       <c r="G551" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Temuco</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H551" t="inlineStr">
@@ -34098,7 +34098,7 @@
       </c>
       <c r="G552" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Talca</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H552" t="inlineStr">
@@ -34159,7 +34159,7 @@
       </c>
       <c r="G553" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H553" t="inlineStr">
@@ -34342,7 +34342,7 @@
       </c>
       <c r="G556" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H556" t="inlineStr">
@@ -34586,7 +34586,7 @@
       </c>
       <c r="G560" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H560" t="inlineStr">
@@ -34647,7 +34647,7 @@
       </c>
       <c r="G561" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H561" t="inlineStr">
@@ -34830,7 +34830,7 @@
       </c>
       <c r="G564" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H564" t="inlineStr">
@@ -35074,7 +35074,7 @@
       </c>
       <c r="G568" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Valparaiso</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H568" t="inlineStr">
@@ -35135,7 +35135,7 @@
       </c>
       <c r="G569" t="inlineStr">
         <is>
-          <t>Bienes y Servicios</t>
+          <t>Hospital de Melipilla</t>
         </is>
       </c>
       <c r="H569" t="inlineStr">
@@ -35196,7 +35196,7 @@
       </c>
       <c r="G570" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo de Angol</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H570" t="inlineStr">
@@ -35257,7 +35257,7 @@
       </c>
       <c r="G571" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Temuco</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H571" t="inlineStr">
@@ -35379,7 +35379,7 @@
       </c>
       <c r="G573" t="inlineStr">
         <is>
-          <t>JEFATURA DE BIENESTAR (I.P)</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H573" t="inlineStr">
@@ -35440,7 +35440,7 @@
       </c>
       <c r="G574" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo del Centro de Cumpli</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H574" t="inlineStr">
@@ -35562,7 +35562,7 @@
       </c>
       <c r="G576" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Metropolitana</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H576" t="inlineStr">
@@ -35623,7 +35623,7 @@
       </c>
       <c r="G577" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H577" t="inlineStr">
@@ -35745,7 +35745,7 @@
       </c>
       <c r="G579" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Valparaiso</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H579" t="inlineStr">
@@ -36111,7 +36111,7 @@
       </c>
       <c r="G585" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VIII ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H585" t="inlineStr">
@@ -36172,7 +36172,7 @@
       </c>
       <c r="G586" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H586" t="inlineStr">
@@ -36416,7 +36416,7 @@
       </c>
       <c r="G590" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VIII ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H590" t="inlineStr">
@@ -36538,7 +36538,7 @@
       </c>
       <c r="G592" t="inlineStr">
         <is>
-          <t>JEFATURA ADMINISTRATIVA Y LOGISTICA DE LA GUARNICION COYHAIQUE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H592" t="inlineStr">
@@ -36843,7 +36843,7 @@
       </c>
       <c r="G597" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE LA FUERZA AEREA GRAL DR RAUL YAZIGI JAUREGUI</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H597" t="inlineStr">
@@ -36965,7 +36965,7 @@
       </c>
       <c r="G599" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo Prisión Arica</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H599" t="inlineStr">
@@ -37087,7 +37087,7 @@
       </c>
       <c r="G601" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Iquique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H601" t="inlineStr">
@@ -37148,7 +37148,7 @@
       </c>
       <c r="G602" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SANTIAGO OESTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H602" t="inlineStr">
@@ -37270,7 +37270,7 @@
       </c>
       <c r="G604" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Puerto Montt</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H604" t="inlineStr">
@@ -37331,7 +37331,7 @@
       </c>
       <c r="G605" t="inlineStr">
         <is>
-          <t>Dirección de Educación Municipal</t>
+          <t>I MUNICIPALIDAD DE TOME</t>
         </is>
       </c>
       <c r="H605" t="inlineStr">
@@ -37392,7 +37392,7 @@
       </c>
       <c r="G606" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H606" t="inlineStr">
@@ -37514,7 +37514,7 @@
       </c>
       <c r="G608" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Metropolitana</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H608" t="inlineStr">
@@ -37636,7 +37636,7 @@
       </c>
       <c r="G610" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Prefectura Arica</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H610" t="inlineStr">
@@ -37941,7 +37941,7 @@
       </c>
       <c r="G615" t="inlineStr">
         <is>
-          <t>I.MUNICIPALIDAD DE LOTA - SALUD</t>
+          <t>I MUNICIPALIDAD DE LOTA</t>
         </is>
       </c>
       <c r="H615" t="inlineStr">
@@ -38007,7 +38007,7 @@
       </c>
       <c r="H616" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I616" t="inlineStr">
@@ -38307,7 +38307,7 @@
       </c>
       <c r="G621" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo Colina 1</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H621" t="inlineStr">
@@ -38368,7 +38368,7 @@
       </c>
       <c r="G622" t="inlineStr">
         <is>
-          <t>Dirección Regional de Ñuble</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H622" t="inlineStr">
@@ -38673,7 +38673,7 @@
       </c>
       <c r="G627" t="inlineStr">
         <is>
-          <t>Dirección Regional de Ñuble</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H627" t="inlineStr">
@@ -38795,7 +38795,7 @@
       </c>
       <c r="G629" t="inlineStr">
         <is>
-          <t>Comandancia General del Cuerpo I.M.</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H629" t="inlineStr">
@@ -38978,7 +38978,7 @@
       </c>
       <c r="G632" t="inlineStr">
         <is>
-          <t>SERVICIO DEL PATRIMONIO</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H632" t="inlineStr">
@@ -39161,7 +39161,7 @@
       </c>
       <c r="G635" t="inlineStr">
         <is>
-          <t>ESCUELA NAVAL "ARTURO PRAT"</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H635" t="inlineStr">
@@ -39283,7 +39283,7 @@
       </c>
       <c r="G637" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Pesca y Acuicultura</t>
+          <t>SERV NACIONAL DE PESCA</t>
         </is>
       </c>
       <c r="H637" t="inlineStr">
@@ -39649,7 +39649,7 @@
       </c>
       <c r="G643" t="inlineStr">
         <is>
-          <t>DEPTO HABITABILIDAD COMANDANCIA EN JEFE DE 1 Z. N.</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H643" t="inlineStr">
@@ -39893,7 +39893,7 @@
       </c>
       <c r="G647" t="inlineStr">
         <is>
-          <t>Gendarmería de Chile - Dirección Regional de Coquimbo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H647" t="inlineStr">
@@ -40076,7 +40076,7 @@
       </c>
       <c r="G650" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Temuco</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H650" t="inlineStr">
@@ -40503,7 +40503,7 @@
       </c>
       <c r="G657" t="inlineStr">
         <is>
-          <t>Zona de Bienestar Iquique</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H657" t="inlineStr">
@@ -40625,7 +40625,7 @@
       </c>
       <c r="G659" t="inlineStr">
         <is>
-          <t>SAMU</t>
+          <t>Centro Metropolitano de Atención Prehospitalaria</t>
         </is>
       </c>
       <c r="H659" t="inlineStr">
@@ -40686,7 +40686,7 @@
       </c>
       <c r="G660" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IX ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H660" t="inlineStr">
@@ -40747,7 +40747,7 @@
       </c>
       <c r="G661" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo del Centro de Cumpli</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H661" t="inlineStr">
@@ -40930,7 +40930,7 @@
       </c>
       <c r="G664" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XII ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H664" t="inlineStr">
@@ -41174,7 +41174,7 @@
       </c>
       <c r="G668" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Iquique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H668" t="inlineStr">
@@ -41301,7 +41301,7 @@
       </c>
       <c r="H670" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I670" t="inlineStr">
@@ -42028,7 +42028,7 @@
       </c>
       <c r="G682" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H682" t="inlineStr">
@@ -42089,7 +42089,7 @@
       </c>
       <c r="G683" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Talca</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H683" t="inlineStr">
@@ -42333,7 +42333,7 @@
       </c>
       <c r="G687" t="inlineStr">
         <is>
-          <t>Dirección Regional de Ñuble</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H687" t="inlineStr">
@@ -42577,7 +42577,7 @@
       </c>
       <c r="G691" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VII ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H691" t="inlineStr">
@@ -42638,7 +42638,7 @@
       </c>
       <c r="G692" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SANTIAGO ESTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H692" t="inlineStr">
@@ -42882,7 +42882,7 @@
       </c>
       <c r="G696" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SANTIAGO ESTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H696" t="inlineStr">
@@ -43065,7 +43065,7 @@
       </c>
       <c r="G699" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Metropolitana</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H699" t="inlineStr">
@@ -43187,7 +43187,7 @@
       </c>
       <c r="G701" t="inlineStr">
         <is>
-          <t>- - -</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H701" t="inlineStr">
@@ -43309,7 +43309,7 @@
       </c>
       <c r="G703" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H703" t="inlineStr">
@@ -43370,7 +43370,7 @@
       </c>
       <c r="G704" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SANTIAGO OESTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H704" t="inlineStr">
@@ -43431,7 +43431,7 @@
       </c>
       <c r="G705" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS III ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H705" t="inlineStr">
@@ -43614,7 +43614,7 @@
       </c>
       <c r="G708" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - VIII Zona Bio Bio</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H708" t="inlineStr">
@@ -43858,7 +43858,7 @@
       </c>
       <c r="G712" t="inlineStr">
         <is>
-          <t>Jefatura Adm y log Campo Militar Valdivia</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H712" t="inlineStr">
@@ -43980,7 +43980,7 @@
       </c>
       <c r="G714" t="inlineStr">
         <is>
-          <t>Jefatura Adm y log Campo Militar Valdivia</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H714" t="inlineStr">
@@ -44041,7 +44041,7 @@
       </c>
       <c r="G715" t="inlineStr">
         <is>
-          <t>I. MUNICIPALIDAD DE SAN NICOLÁS D. EDUCACIÓN</t>
+          <t>I MUNICIPALIDAD DE SAN NICOLAS</t>
         </is>
       </c>
       <c r="H715" t="inlineStr">
@@ -44224,7 +44224,7 @@
       </c>
       <c r="G718" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H718" t="inlineStr">
@@ -44285,7 +44285,7 @@
       </c>
       <c r="G719" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS X ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H719" t="inlineStr">
@@ -44468,7 +44468,7 @@
       </c>
       <c r="G722" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE COQUIMBO</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H722" t="inlineStr">
@@ -44529,7 +44529,7 @@
       </c>
       <c r="G723" t="inlineStr">
         <is>
-          <t>I. MUNICIPALIDAD DE SAN NICOLÁS D. EDUCACIÓN</t>
+          <t>I MUNICIPALIDAD DE SAN NICOLAS</t>
         </is>
       </c>
       <c r="H723" t="inlineStr">
@@ -44590,7 +44590,7 @@
       </c>
       <c r="G724" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Puerto Montt</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H724" t="inlineStr">
@@ -44712,7 +44712,7 @@
       </c>
       <c r="G726" t="inlineStr">
         <is>
-          <t>Comandancia en Jefe de la IV Zona Naval</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H726" t="inlineStr">
@@ -44834,7 +44834,7 @@
       </c>
       <c r="G728" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SANTIAGO OESTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H728" t="inlineStr">
@@ -45200,7 +45200,7 @@
       </c>
       <c r="G734" t="inlineStr">
         <is>
-          <t>Regimiento Reforzado N° 1 "Calama"</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H734" t="inlineStr">
@@ -45261,7 +45261,7 @@
       </c>
       <c r="G735" t="inlineStr">
         <is>
-          <t>Division de Bienestar Social</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H735" t="inlineStr">
@@ -45383,7 +45383,7 @@
       </c>
       <c r="G737" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VIII ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H737" t="inlineStr">
@@ -45444,7 +45444,7 @@
       </c>
       <c r="G738" t="inlineStr">
         <is>
-          <t>JEFATURA ADMINISTRATIVA Y LOGISTICA CAMPO MILITAR PENALOLEN</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H738" t="inlineStr">
@@ -45627,7 +45627,7 @@
       </c>
       <c r="G741" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VII ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H741" t="inlineStr">
@@ -45688,7 +45688,7 @@
       </c>
       <c r="G742" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VI ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H742" t="inlineStr">
@@ -45749,7 +45749,7 @@
       </c>
       <c r="G743" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H743" t="inlineStr">
@@ -45810,7 +45810,7 @@
       </c>
       <c r="G744" t="inlineStr">
         <is>
-          <t>JEFATURA ADMINISTRATIVA Y LOGISTICA DE LA GUARNICION COYHAIQUE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H744" t="inlineStr">
@@ -45871,7 +45871,7 @@
       </c>
       <c r="G745" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H745" t="inlineStr">
@@ -45932,7 +45932,7 @@
       </c>
       <c r="G746" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XVI ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H746" t="inlineStr">
@@ -45993,7 +45993,7 @@
       </c>
       <c r="G747" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H747" t="inlineStr">
@@ -46054,7 +46054,7 @@
       </c>
       <c r="G748" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H748" t="inlineStr">
@@ -46176,7 +46176,7 @@
       </c>
       <c r="G750" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo Colina 1</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H750" t="inlineStr">
@@ -46420,7 +46420,7 @@
       </c>
       <c r="G754" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Temuco</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H754" t="inlineStr">
@@ -46542,7 +46542,7 @@
       </c>
       <c r="G756" t="inlineStr">
         <is>
-          <t>Dirección Regional de Ñuble</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H756" t="inlineStr">
@@ -46725,7 +46725,7 @@
       </c>
       <c r="G759" t="inlineStr">
         <is>
-          <t>Centro Educación y Trabajo Régimen Cerrado CP Aric</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H759" t="inlineStr">
@@ -46791,7 +46791,7 @@
       </c>
       <c r="H760" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I760" t="inlineStr">
@@ -46908,7 +46908,7 @@
       </c>
       <c r="G762" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Concepcion</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H762" t="inlineStr">
@@ -47091,7 +47091,7 @@
       </c>
       <c r="G765" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Reinserción Social Juvenil</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H765" t="inlineStr">
@@ -47152,7 +47152,7 @@
       </c>
       <c r="G766" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo del CDP Talagante</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H766" t="inlineStr">
@@ -47274,7 +47274,7 @@
       </c>
       <c r="G768" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Río Negro - Educación</t>
+          <t>I MUNICIPALIDAD DE RIO NEGRO</t>
         </is>
       </c>
       <c r="H768" t="inlineStr">
@@ -47518,7 +47518,7 @@
       </c>
       <c r="G772" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Pesca y Acuicultura</t>
+          <t>SERV NACIONAL DE PESCA</t>
         </is>
       </c>
       <c r="H772" t="inlineStr">
@@ -47579,7 +47579,7 @@
       </c>
       <c r="G773" t="inlineStr">
         <is>
-          <t>Zona Bienestar "Valparaíso" Bienestar Social</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H773" t="inlineStr">
@@ -47823,7 +47823,7 @@
       </c>
       <c r="G777" t="inlineStr">
         <is>
-          <t>Zona Bienestar "Iquique" Bienestar Social</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H777" t="inlineStr">
@@ -48067,7 +48067,7 @@
       </c>
       <c r="G781" t="inlineStr">
         <is>
-          <t>ESCUELA DE FORMACIÓN DE CARABINEROS LOS ANDES</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H781" t="inlineStr">
@@ -48128,7 +48128,7 @@
       </c>
       <c r="G782" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H782" t="inlineStr">
@@ -48189,7 +48189,7 @@
       </c>
       <c r="G783" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H783" t="inlineStr">
@@ -48250,7 +48250,7 @@
       </c>
       <c r="G784" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H784" t="inlineStr">
@@ -48311,7 +48311,7 @@
       </c>
       <c r="G785" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H785" t="inlineStr">
@@ -48433,7 +48433,7 @@
       </c>
       <c r="G787" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Concepcion</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H787" t="inlineStr">
@@ -48494,7 +48494,7 @@
       </c>
       <c r="G788" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H788" t="inlineStr">
@@ -48738,7 +48738,7 @@
       </c>
       <c r="G792" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS V ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H792" t="inlineStr">
@@ -48982,7 +48982,7 @@
       </c>
       <c r="G796" t="inlineStr">
         <is>
-          <t>FONDO PARA HOSPITALES DE CARABINEROS DE CHILE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H796" t="inlineStr">
@@ -49714,7 +49714,7 @@
       </c>
       <c r="G808" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Metropolitana</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H808" t="inlineStr">
@@ -50080,7 +50080,7 @@
       </c>
       <c r="G814" t="inlineStr">
         <is>
-          <t>Bienes y Servicios</t>
+          <t>Hospital de Melipilla</t>
         </is>
       </c>
       <c r="H814" t="inlineStr">
@@ -50141,7 +50141,7 @@
       </c>
       <c r="G815" t="inlineStr">
         <is>
-          <t>Gendarmería de Chile - Dirección Regional de Coquimbo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H815" t="inlineStr">
@@ -50446,7 +50446,7 @@
       </c>
       <c r="G820" t="inlineStr">
         <is>
-          <t>DIRECCION DE SALUD</t>
+          <t>CORP MUNICIPAL MELIPILLA PARA LA ED SALUD</t>
         </is>
       </c>
       <c r="H820" t="inlineStr">
@@ -50690,7 +50690,7 @@
       </c>
       <c r="G824" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H824" t="inlineStr">
@@ -50751,7 +50751,7 @@
       </c>
       <c r="G825" t="inlineStr">
         <is>
-          <t>DIRECCION DE SALUD</t>
+          <t>CORP MUNICIPAL MELIPILLA PARA LA ED SALUD</t>
         </is>
       </c>
       <c r="H825" t="inlineStr">
@@ -50939,7 +50939,7 @@
       </c>
       <c r="H828" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I828" t="inlineStr">
@@ -51178,7 +51178,7 @@
       </c>
       <c r="G832" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H832" t="inlineStr">
@@ -51300,7 +51300,7 @@
       </c>
       <c r="G834" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H834" t="inlineStr">
@@ -51361,7 +51361,7 @@
       </c>
       <c r="G835" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H835" t="inlineStr">
@@ -51422,7 +51422,7 @@
       </c>
       <c r="G836" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - IX Zona Araucania</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H836" t="inlineStr">
@@ -51483,7 +51483,7 @@
       </c>
       <c r="G837" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H837" t="inlineStr">
@@ -51605,7 +51605,7 @@
       </c>
       <c r="G839" t="inlineStr">
         <is>
-          <t>BASE AERONAVAL CONCON</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H839" t="inlineStr">
@@ -51788,7 +51788,7 @@
       </c>
       <c r="G842" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H842" t="inlineStr">
@@ -51910,7 +51910,7 @@
       </c>
       <c r="G844" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Penco - Educación</t>
+          <t>I MUNICIPALIDAD DE PENCO</t>
         </is>
       </c>
       <c r="H844" t="inlineStr">
@@ -51971,7 +51971,7 @@
       </c>
       <c r="G845" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Penco - Educación</t>
+          <t>I MUNICIPALIDAD DE PENCO</t>
         </is>
       </c>
       <c r="H845" t="inlineStr">
@@ -52093,7 +52093,7 @@
       </c>
       <c r="G847" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Temuco</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H847" t="inlineStr">
@@ -52154,7 +52154,7 @@
       </c>
       <c r="G848" t="inlineStr">
         <is>
-          <t>Zona Bienestar "Coyhaique" Bienestar Social</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H848" t="inlineStr">
@@ -52215,7 +52215,7 @@
       </c>
       <c r="G849" t="inlineStr">
         <is>
-          <t>Hospital de Peñaflor</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE P</t>
         </is>
       </c>
       <c r="H849" t="inlineStr">

--- a/docs/oc-mensuales/gas-licuado-de-petroleo/feb-2026.xlsx
+++ b/docs/oc-mensuales/gas-licuado-de-petroleo/feb-2026.xlsx
@@ -4109,7 +4109,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -9959,7 +9959,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -13729,7 +13729,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
@@ -14964,7 +14964,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
@@ -16914,7 +16914,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
@@ -22634,7 +22634,7 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
@@ -28809,7 +28809,7 @@
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F437" t="inlineStr">
@@ -33229,7 +33229,7 @@
       </c>
       <c r="E505" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F505" t="inlineStr">
@@ -35764,7 +35764,7 @@
       </c>
       <c r="E544" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F544" t="inlineStr">
@@ -41224,7 +41224,7 @@
       </c>
       <c r="E628" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F628" t="inlineStr">
@@ -45514,7 +45514,7 @@
       </c>
       <c r="E694" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F694" t="inlineStr">
@@ -47984,7 +47984,7 @@
       </c>
       <c r="E732" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F732" t="inlineStr">
@@ -52014,7 +52014,7 @@
       </c>
       <c r="E794" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F794" t="inlineStr">
@@ -54224,7 +54224,7 @@
       </c>
       <c r="E828" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F828" t="inlineStr">
